--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="712">
   <si>
     <t/>
   </si>
@@ -1613,12 +1613,6 @@
   </si>
   <si>
     <t>ROSE/B GULA HLS 500</t>
-  </si>
-  <si>
-    <t>20096173</t>
-  </si>
-  <si>
-    <t>IDM GULA HALUS 250G</t>
   </si>
   <si>
     <t>10000509</t>
@@ -2545,7 +2539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F333"/>
+  <dimension ref="A1:F332"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -7569,10 +7563,10 @@
         <v>527</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7589,10 +7583,10 @@
         <v>527</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7606,30 +7600,30 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="B254" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="C254" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="E254" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>5</v>
@@ -7646,10 +7640,10 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>5</v>
@@ -7666,13 +7660,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7686,10 +7680,10 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>26</v>
@@ -7706,13 +7700,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7726,33 +7720,33 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>84</v>
+        <v>553</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>555</v>
+        <v>26</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7766,13 +7760,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7786,13 +7780,13 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -7806,10 +7800,10 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>26</v>
@@ -7826,30 +7820,30 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>542</v>
+        <v>564</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>175</v>
+        <v>4</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D265" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="C265" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D265" s="1" t="s">
-        <v>566</v>
-      </c>
       <c r="E265" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>84</v>
@@ -7866,10 +7860,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>84</v>
@@ -7886,10 +7880,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>84</v>
@@ -7906,33 +7900,33 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>84</v>
+        <v>573</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>575</v>
+        <v>84</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7946,13 +7940,13 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -7966,30 +7960,30 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D272" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="C272" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D272" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="E272" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>15</v>
@@ -8006,10 +8000,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>15</v>
@@ -8026,10 +8020,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>15</v>
@@ -8046,13 +8040,13 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -8066,10 +8060,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>26</v>
@@ -8086,10 +8080,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>26</v>
@@ -8106,13 +8100,13 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -8126,33 +8120,33 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>15</v>
+        <v>598</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D280" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="B280" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="C280" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="E280" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>600</v>
+        <v>15</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -8166,10 +8160,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>15</v>
@@ -8186,10 +8180,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>15</v>
@@ -8206,10 +8200,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>15</v>
@@ -8226,10 +8220,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>15</v>
@@ -8246,10 +8240,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>15</v>
@@ -8266,10 +8260,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>15</v>
@@ -8286,10 +8280,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>15</v>
@@ -8306,13 +8300,13 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8326,13 +8320,13 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8346,13 +8340,13 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8366,13 +8360,13 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8386,10 +8380,10 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>599</v>
+        <v>625</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>181</v>
+        <v>4</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>15</v>
@@ -8397,22 +8391,22 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D293" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="B293" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="C293" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="E293" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8426,13 +8420,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8446,10 +8440,10 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>15</v>
@@ -8466,10 +8460,10 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>15</v>
@@ -8486,13 +8480,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8506,13 +8500,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8526,10 +8520,10 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>15</v>
@@ -8546,13 +8540,13 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8566,30 +8560,30 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D302" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>646</v>
-      </c>
       <c r="E302" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>26</v>
@@ -8606,10 +8600,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>26</v>
@@ -8626,13 +8620,13 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8646,10 +8640,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>15</v>
@@ -8666,10 +8660,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>15</v>
@@ -8686,10 +8680,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>15</v>
@@ -8706,10 +8700,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>15</v>
@@ -8726,10 +8720,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>15</v>
@@ -8746,13 +8740,13 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -8766,30 +8760,30 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>646</v>
+        <v>665</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D312" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="C312" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D312" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="E312" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>15</v>
@@ -8806,13 +8800,13 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -8826,13 +8820,13 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>84</v>
+        <v>443</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -8846,30 +8840,30 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>443</v>
+        <v>15</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D316" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="B316" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>676</v>
-      </c>
       <c r="E316" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>15</v>
@@ -8886,13 +8880,13 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -8906,10 +8900,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>84</v>
@@ -8926,13 +8920,13 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -8946,13 +8940,13 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -8966,30 +8960,30 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="B322" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>689</v>
-      </c>
       <c r="E322" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>84</v>
@@ -9006,10 +9000,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>84</v>
@@ -9026,10 +9020,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>84</v>
@@ -9046,10 +9040,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>84</v>
@@ -9066,10 +9060,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>84</v>
@@ -9086,10 +9080,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>84</v>
@@ -9097,19 +9091,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>702</v>
-      </c>
       <c r="E328" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>84</v>
@@ -9126,10 +9120,10 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>84</v>
@@ -9146,13 +9140,13 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9166,10 +9160,10 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>15</v>
@@ -9177,41 +9171,21 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D332" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="B332" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>711</v>
-      </c>
       <c r="E332" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A333" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="B333" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="E333" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F333" s="1" t="s">
         <v>84</v>
       </c>
     </row>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="713">
   <si>
     <t/>
   </si>
@@ -538,177 +538,171 @@
     <t>ABC SAUS TIRAM 135</t>
   </si>
   <si>
+    <t>20071507</t>
+  </si>
+  <si>
+    <t>MAGGI SAUS TIRAM 150</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
-    <t>20071507</t>
-  </si>
-  <si>
-    <t>MAGGI SAUS TIRAM 150</t>
+    <t>20117166</t>
+  </si>
+  <si>
+    <t>MAESTRO SS TIRAM 270</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>20117166</t>
-  </si>
-  <si>
-    <t>MAESTRO SS TIRAM 270</t>
+    <t>20015850</t>
+  </si>
+  <si>
+    <t>INDOFOOD SBL PDS 275</t>
+  </si>
+  <si>
+    <t>20027097</t>
+  </si>
+  <si>
+    <t>INDOFOOD SMBL EXT275</t>
+  </si>
+  <si>
+    <t>20115489</t>
+  </si>
+  <si>
+    <t>INDOFOOD SMB DHSY275</t>
+  </si>
+  <si>
+    <t>20027096</t>
+  </si>
+  <si>
+    <t>INDOFOOD SAUS TMT275</t>
+  </si>
+  <si>
+    <t>20064412</t>
+  </si>
+  <si>
+    <t>ABC SAMBAL ASLI 270</t>
+  </si>
+  <si>
+    <t>20063027</t>
+  </si>
+  <si>
+    <t>ABC SMBL EXT.PDS 270</t>
+  </si>
+  <si>
+    <t>20132492</t>
+  </si>
+  <si>
+    <t>ABC SBL EXTRM PDS270</t>
+  </si>
+  <si>
+    <t>10003362</t>
+  </si>
+  <si>
+    <t>ABC SBL.EXT PEDAS335</t>
+  </si>
+  <si>
+    <t>10013041</t>
+  </si>
+  <si>
+    <t>INDO/F SAMBAL E/P335</t>
+  </si>
+  <si>
+    <t>10012917</t>
+  </si>
+  <si>
+    <t>INDO/F SMBAL BGK 335</t>
+  </si>
+  <si>
+    <t>20036241</t>
+  </si>
+  <si>
+    <t>2BLIBIS SAUS CABE335</t>
+  </si>
+  <si>
+    <t>20036344</t>
+  </si>
+  <si>
+    <t>2BLIBIS SAUS CABE135</t>
+  </si>
+  <si>
+    <t>10000212</t>
+  </si>
+  <si>
+    <t>ABC SAMBAL 130ML</t>
+  </si>
+  <si>
+    <t>10036708</t>
+  </si>
+  <si>
+    <t>ABC SBL.EXT PEDAS130</t>
+  </si>
+  <si>
+    <t>10000320</t>
+  </si>
+  <si>
+    <t>ABC SAUCE TOMAT130ML</t>
+  </si>
+  <si>
+    <t>20115632</t>
+  </si>
+  <si>
+    <t>INDOFOOD SMB DHSY135</t>
+  </si>
+  <si>
+    <t>20010272</t>
+  </si>
+  <si>
+    <t>INDOFOOD SMB EXT 135</t>
+  </si>
+  <si>
+    <t>10002989</t>
+  </si>
+  <si>
+    <t>INDOFOOD SBL PDS 135</t>
+  </si>
+  <si>
+    <t>20009269</t>
+  </si>
+  <si>
+    <t>DELMONTE EXT.HOT 135</t>
+  </si>
+  <si>
+    <t>20036194</t>
+  </si>
+  <si>
+    <t>DELMONTE KETCHUP 135</t>
+  </si>
+  <si>
+    <t>20091863</t>
+  </si>
+  <si>
+    <t>MMSUKA HOT LAVA 130</t>
+  </si>
+  <si>
+    <t>20091864</t>
+  </si>
+  <si>
+    <t>MMSUKA HOT LAVA 260</t>
+  </si>
+  <si>
+    <t>20141501</t>
+  </si>
+  <si>
+    <t>2 BELIBIS PDS LD 235</t>
+  </si>
+  <si>
+    <t>20141500</t>
+  </si>
+  <si>
+    <t>2 BELIBIS EX/PDS 235</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>20015850</t>
-  </si>
-  <si>
-    <t>INDOFOOD SBL PDS 275</t>
-  </si>
-  <si>
-    <t>20027097</t>
-  </si>
-  <si>
-    <t>INDOFOOD SMBL EXT275</t>
-  </si>
-  <si>
-    <t>20115489</t>
-  </si>
-  <si>
-    <t>INDOFOOD SMB DHSY275</t>
-  </si>
-  <si>
-    <t>20027096</t>
-  </si>
-  <si>
-    <t>INDOFOOD SAUS TMT275</t>
-  </si>
-  <si>
-    <t>20064412</t>
-  </si>
-  <si>
-    <t>ABC SAMBAL ASLI 270</t>
-  </si>
-  <si>
-    <t>20063027</t>
-  </si>
-  <si>
-    <t>ABC SMBL EXT.PDS 270</t>
-  </si>
-  <si>
-    <t>20132492</t>
-  </si>
-  <si>
-    <t>ABC SBL EXTRM PDS270</t>
-  </si>
-  <si>
-    <t>10000116</t>
-  </si>
-  <si>
-    <t>ABC SAMBAL BTL 335ML</t>
-  </si>
-  <si>
-    <t>10003362</t>
-  </si>
-  <si>
-    <t>ABC SBL.EXT PEDAS335</t>
-  </si>
-  <si>
-    <t>10013041</t>
-  </si>
-  <si>
-    <t>INDO/F SAMBAL E/P335</t>
-  </si>
-  <si>
-    <t>10012917</t>
-  </si>
-  <si>
-    <t>INDO/F SMBAL BGK 335</t>
-  </si>
-  <si>
-    <t>20036241</t>
-  </si>
-  <si>
-    <t>2BLIBIS SAUS CABE335</t>
-  </si>
-  <si>
-    <t>20036344</t>
-  </si>
-  <si>
-    <t>2BLIBIS SAUS CABE135</t>
-  </si>
-  <si>
-    <t>10000212</t>
-  </si>
-  <si>
-    <t>ABC SAMBAL 130ML</t>
-  </si>
-  <si>
-    <t>10036708</t>
-  </si>
-  <si>
-    <t>ABC SBL.EXT PEDAS130</t>
-  </si>
-  <si>
-    <t>10000320</t>
-  </si>
-  <si>
-    <t>ABC SAUCE TOMAT130ML</t>
-  </si>
-  <si>
-    <t>20115632</t>
-  </si>
-  <si>
-    <t>INDOFOOD SMB DHSY135</t>
-  </si>
-  <si>
-    <t>20010272</t>
-  </si>
-  <si>
-    <t>INDOFOOD SMB EXT 135</t>
-  </si>
-  <si>
-    <t>10002989</t>
-  </si>
-  <si>
-    <t>INDOFOOD SBL PDS 135</t>
-  </si>
-  <si>
-    <t>20009269</t>
-  </si>
-  <si>
-    <t>DELMONTE EXT.HOT 135</t>
-  </si>
-  <si>
-    <t>20036194</t>
-  </si>
-  <si>
-    <t>DELMONTE KETCHUP 135</t>
-  </si>
-  <si>
-    <t>20091863</t>
-  </si>
-  <si>
-    <t>MMSUKA HOT LAVA 130</t>
-  </si>
-  <si>
-    <t>20091864</t>
-  </si>
-  <si>
-    <t>MMSUKA HOT LAVA 260</t>
-  </si>
-  <si>
-    <t>20141501</t>
-  </si>
-  <si>
-    <t>2 BELIBIS PDS LD 235</t>
-  </si>
-  <si>
-    <t>20141500</t>
-  </si>
-  <si>
-    <t>2 BELIBIS EX/PDS 235</t>
-  </si>
-  <si>
     <t>20132660</t>
   </si>
   <si>
@@ -2027,6 +2021,15 @@
   </si>
   <si>
     <t>IDM M/GORENG 2L</t>
+  </si>
+  <si>
+    <t>20142102</t>
+  </si>
+  <si>
+    <t>GRANDCO MYK GRG1.8L</t>
+  </si>
+  <si>
+    <t>,(E-3B)</t>
   </si>
   <si>
     <t>10012338</t>
@@ -4103,7 +4106,7 @@
         <v>96</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>15</v>
@@ -4123,7 +4126,7 @@
         <v>96</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -4131,10 +4134,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -4143,7 +4146,7 @@
         <v>96</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -4151,10 +4154,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -4163,7 +4166,7 @@
         <v>96</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>26</v>
@@ -4171,10 +4174,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -4191,10 +4194,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -4211,10 +4214,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -4231,10 +4234,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -4251,10 +4254,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -4271,10 +4274,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -4291,10 +4294,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -4311,10 +4314,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -4323,7 +4326,7 @@
         <v>99</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -4331,10 +4334,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -4343,18 +4346,18 @@
         <v>99</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -4363,7 +4366,7 @@
         <v>99</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>26</v>
@@ -4371,10 +4374,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -4383,27 +4386,27 @@
         <v>99</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -4411,10 +4414,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>207</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -4423,7 +4426,7 @@
         <v>102</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -4431,10 +4434,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -4443,7 +4446,7 @@
         <v>102</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -4451,10 +4454,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -4463,7 +4466,7 @@
         <v>102</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -4471,10 +4474,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -4483,18 +4486,18 @@
         <v>102</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -4503,7 +4506,7 @@
         <v>102</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>26</v>
@@ -4511,10 +4514,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -4523,7 +4526,7 @@
         <v>102</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>26</v>
@@ -4531,10 +4534,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -4543,7 +4546,7 @@
         <v>102</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>26</v>
@@ -4551,10 +4554,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -4563,7 +4566,7 @@
         <v>102</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>26</v>
@@ -4571,10 +4574,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -4583,18 +4586,18 @@
         <v>102</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -4603,7 +4606,7 @@
         <v>102</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>15</v>
@@ -4611,10 +4614,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -4623,18 +4626,18 @@
         <v>102</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -4643,7 +4646,7 @@
         <v>102</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -4663,7 +4666,7 @@
         <v>102</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -4671,10 +4674,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -4683,18 +4686,18 @@
         <v>102</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -4703,7 +4706,7 @@
         <v>102</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>26</v>
@@ -4711,22 +4714,22 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>240</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4740,10 +4743,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4760,13 +4763,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4780,10 +4783,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>26</v>
@@ -4800,10 +4803,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>26</v>
@@ -4820,10 +4823,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>26</v>
@@ -4840,13 +4843,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4860,13 +4863,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4880,13 +4883,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4900,13 +4903,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4920,13 +4923,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4940,10 +4943,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>15</v>
@@ -4960,10 +4963,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>15</v>
@@ -4980,10 +4983,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>15</v>
@@ -5000,10 +5003,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>15</v>
@@ -5020,10 +5023,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>15</v>
@@ -5040,10 +5043,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>15</v>
@@ -5060,10 +5063,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>15</v>
@@ -5080,10 +5083,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>15</v>
@@ -5100,13 +5103,13 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -5120,13 +5123,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -5140,10 +5143,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>15</v>
@@ -5160,10 +5163,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>15</v>
@@ -5180,13 +5183,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -5200,10 +5203,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>26</v>
@@ -5220,13 +5223,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -5240,13 +5243,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -5260,10 +5263,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>47</v>
@@ -5280,10 +5283,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>47</v>
@@ -5300,10 +5303,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>47</v>
@@ -5320,10 +5323,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>47</v>
@@ -5340,13 +5343,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>234</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -5360,33 +5363,33 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>26</v>
+        <v>305</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5400,7 +5403,7 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>4</v>
@@ -5420,7 +5423,7 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>4</v>
@@ -5440,7 +5443,7 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>4</v>
@@ -5460,13 +5463,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5480,13 +5483,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -5500,7 +5503,7 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>21</v>
@@ -5520,7 +5523,7 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>21</v>
@@ -5540,7 +5543,7 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>21</v>
@@ -5560,7 +5563,7 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>21</v>
@@ -5580,13 +5583,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>26</v>
+        <v>305</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5600,13 +5603,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5620,13 +5623,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5640,13 +5643,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5660,7 +5663,7 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>8</v>
@@ -5680,7 +5683,7 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>8</v>
@@ -5700,7 +5703,7 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>8</v>
@@ -5720,7 +5723,7 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>8</v>
@@ -5740,7 +5743,7 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>8</v>
@@ -5760,13 +5763,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>26</v>
+        <v>305</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5780,13 +5783,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>307</v>
+        <v>15</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5800,13 +5803,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5820,7 +5823,7 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>11</v>
@@ -5840,7 +5843,7 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>11</v>
@@ -5860,13 +5863,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5880,13 +5883,13 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5900,7 +5903,7 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>11</v>
@@ -5920,13 +5923,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5940,10 +5943,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5960,13 +5963,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5980,10 +5983,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>15</v>
@@ -6000,10 +6003,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>15</v>
@@ -6020,13 +6023,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6040,13 +6043,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>26</v>
+        <v>305</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -6060,13 +6063,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6080,33 +6083,33 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>240</v>
+        <v>378</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>307</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6120,13 +6123,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6140,10 +6143,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>15</v>
@@ -6160,13 +6163,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6180,13 +6183,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>26</v>
+        <v>305</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6200,13 +6203,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>307</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6220,13 +6223,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>305</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6240,13 +6243,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>307</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6260,10 +6263,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -6271,19 +6274,19 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -6300,10 +6303,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -6320,10 +6323,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -6340,10 +6343,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -6360,13 +6363,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6380,10 +6383,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>15</v>
@@ -6400,10 +6403,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>15</v>
@@ -6420,10 +6423,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>15</v>
@@ -6440,13 +6443,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6460,33 +6463,33 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6500,13 +6503,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6520,10 +6523,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -6540,13 +6543,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6560,10 +6563,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>15</v>
@@ -6580,33 +6583,33 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>15</v>
+        <v>431</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>433</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6620,13 +6623,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6640,13 +6643,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6660,33 +6663,33 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>15</v>
+        <v>441</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B207" s="1" t="s">
+      <c r="E207" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F207" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F207" s="1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6700,13 +6703,13 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>443</v>
+        <v>26</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6720,10 +6723,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>26</v>
@@ -6740,13 +6743,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6760,13 +6763,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6780,13 +6783,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6800,13 +6803,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6820,10 +6823,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>26</v>
@@ -6840,10 +6843,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>26</v>
@@ -6860,10 +6863,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>26</v>
@@ -6880,10 +6883,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>26</v>
@@ -6900,33 +6903,33 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>175</v>
+        <v>4</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>26</v>
+        <v>467</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6940,13 +6943,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6960,13 +6963,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6980,13 +6983,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>469</v>
+        <v>84</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7000,7 +7003,7 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>21</v>
@@ -7020,7 +7023,7 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>21</v>
@@ -7040,7 +7043,7 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>21</v>
@@ -7060,13 +7063,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7080,7 +7083,7 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>8</v>
@@ -7100,7 +7103,7 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>8</v>
@@ -7120,7 +7123,7 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>8</v>
@@ -7140,10 +7143,10 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>5</v>
@@ -7160,7 +7163,7 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>11</v>
@@ -7180,7 +7183,7 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>11</v>
@@ -7200,7 +7203,7 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>11</v>
@@ -7220,10 +7223,10 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>5</v>
@@ -7240,7 +7243,7 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>31</v>
@@ -7260,7 +7263,7 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>31</v>
@@ -7280,7 +7283,7 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>31</v>
@@ -7300,7 +7303,7 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>31</v>
@@ -7320,7 +7323,7 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>31</v>
@@ -7340,33 +7343,33 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>468</v>
+        <v>512</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D241" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C241" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D241" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="E241" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7380,10 +7383,10 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>5</v>
@@ -7400,10 +7403,10 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>5</v>
@@ -7420,13 +7423,13 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7440,13 +7443,13 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7460,30 +7463,30 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D247" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="C247" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D247" s="1" t="s">
-        <v>527</v>
-      </c>
       <c r="E247" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>5</v>
@@ -7500,10 +7503,10 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>5</v>
@@ -7520,13 +7523,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7540,13 +7543,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7560,13 +7563,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7580,30 +7583,30 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D253" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="C253" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D253" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="E253" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>5</v>
@@ -7620,10 +7623,10 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>5</v>
@@ -7640,13 +7643,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7660,10 +7663,10 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>26</v>
@@ -7680,13 +7683,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7700,33 +7703,33 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>84</v>
+        <v>551</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>553</v>
+        <v>26</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7740,13 +7743,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7760,13 +7763,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7780,10 +7783,10 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>26</v>
@@ -7800,30 +7803,30 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>540</v>
+        <v>562</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>175</v>
+        <v>4</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D264" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="C264" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>564</v>
-      </c>
       <c r="E264" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>84</v>
@@ -7840,10 +7843,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>84</v>
@@ -7860,10 +7863,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>84</v>
@@ -7880,33 +7883,33 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>84</v>
+        <v>571</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>573</v>
+        <v>84</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7920,13 +7923,13 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7940,30 +7943,30 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="C271" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="E271" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>15</v>
@@ -7980,10 +7983,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>15</v>
@@ -8000,10 +8003,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>15</v>
@@ -8020,13 +8023,13 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -8040,10 +8043,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>26</v>
@@ -8060,10 +8063,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>26</v>
@@ -8080,13 +8083,13 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -8100,33 +8103,33 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>15</v>
+        <v>596</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D279" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B279" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="C279" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>597</v>
-      </c>
       <c r="E279" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>598</v>
+        <v>15</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -8140,10 +8143,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>15</v>
@@ -8160,10 +8163,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>15</v>
@@ -8180,10 +8183,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>15</v>
@@ -8200,10 +8203,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>15</v>
@@ -8220,10 +8223,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>15</v>
@@ -8240,10 +8243,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>15</v>
@@ -8260,7 +8263,7 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>96</v>
@@ -8280,13 +8283,13 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>99</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -8300,13 +8303,13 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8320,13 +8323,13 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8340,13 +8343,13 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8360,10 +8363,10 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>597</v>
+        <v>623</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>181</v>
+        <v>4</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>15</v>
@@ -8371,22 +8374,22 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="C292" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="E292" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8400,13 +8403,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8420,10 +8423,10 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F294" s="1" t="s">
         <v>15</v>
@@ -8440,10 +8443,10 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>15</v>
@@ -8460,13 +8463,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8480,13 +8483,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8500,10 +8503,10 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>15</v>
@@ -8520,13 +8523,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8540,30 +8543,30 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="E301" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>26</v>
@@ -8580,10 +8583,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>26</v>
@@ -8600,13 +8603,13 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -8620,10 +8623,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>15</v>
@@ -8640,10 +8643,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>15</v>
@@ -8660,10 +8663,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>15</v>
@@ -8680,10 +8683,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>15</v>
@@ -8700,10 +8703,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>15</v>
@@ -8720,13 +8723,13 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -8740,30 +8743,30 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>644</v>
+        <v>663</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>665</v>
-      </c>
       <c r="E311" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>15</v>
@@ -8780,13 +8783,13 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -8800,13 +8803,13 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>84</v>
+        <v>441</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -8820,27 +8823,27 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>443</v>
+        <v>672</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>4</v>
@@ -8851,16 +8854,16 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D316" s="1" t="s">
         <v>675</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>674</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>21</v>
@@ -8871,16 +8874,16 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>8</v>
@@ -8891,16 +8894,16 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>11</v>
@@ -8911,16 +8914,16 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>31</v>
@@ -8931,16 +8934,16 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>14</v>
@@ -8951,16 +8954,16 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>4</v>
@@ -8971,16 +8974,16 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>688</v>
-      </c>
-      <c r="B322" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>687</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>21</v>
@@ -8991,16 +8994,16 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>8</v>
@@ -9011,16 +9014,16 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>11</v>
@@ -9031,16 +9034,16 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>31</v>
@@ -9051,16 +9054,16 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>14</v>
@@ -9071,16 +9074,16 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>4</v>
@@ -9091,16 +9094,16 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>701</v>
-      </c>
-      <c r="B328" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>700</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>21</v>
@@ -9111,16 +9114,16 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>8</v>
@@ -9131,16 +9134,16 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>11</v>
@@ -9151,16 +9154,16 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>4</v>
@@ -9171,16 +9174,16 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D332" s="1" t="s">
         <v>710</v>
-      </c>
-      <c r="B332" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>709</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>21</v>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="715">
   <si>
     <t/>
   </si>
@@ -334,150 +334,150 @@
     <t>PRONAS NS GRG SP 110</t>
   </si>
   <si>
+    <t>20134507</t>
+  </si>
+  <si>
+    <t>TUDUNG BMB NS UDUK27</t>
+  </si>
+  <si>
+    <t>20134777</t>
+  </si>
+  <si>
+    <t>SASA KARI JPG ORI 40</t>
+  </si>
+  <si>
+    <t>20136577</t>
+  </si>
+  <si>
+    <t>TUDUNG BMB PRLDK 50G</t>
+  </si>
+  <si>
+    <t>20136743</t>
+  </si>
+  <si>
+    <t>TDUNG BMB NP.RDNG 27</t>
+  </si>
+  <si>
+    <t>20134778</t>
+  </si>
+  <si>
+    <t>SASA KARI JPG PDS 40</t>
+  </si>
+  <si>
+    <t>20137258</t>
+  </si>
+  <si>
+    <t>RASA/M GULAI AYAM40G</t>
+  </si>
+  <si>
+    <t>20138072</t>
+  </si>
+  <si>
+    <t>RASA/M OPOR AYAM 40G</t>
+  </si>
+  <si>
+    <t>20138843</t>
+  </si>
+  <si>
+    <t>R/MASA SYR LODEH 25G</t>
+  </si>
+  <si>
+    <t>20025563</t>
+  </si>
+  <si>
+    <t>SASA BMB LUMUR AYM26</t>
+  </si>
+  <si>
+    <t>20057290</t>
+  </si>
+  <si>
+    <t>SASA BU AYAM KNG 25G</t>
+  </si>
+  <si>
     <t>20059859</t>
   </si>
   <si>
     <t>KOBE BMB N/GRG PDS20</t>
   </si>
   <si>
+    <t>20136397</t>
+  </si>
+  <si>
+    <t>KB BMB AYM LNGKS 80G</t>
+  </si>
+  <si>
+    <t>10007775</t>
+  </si>
+  <si>
+    <t>A/SAJIKU NASI G.AY20</t>
+  </si>
+  <si>
+    <t>10013821</t>
+  </si>
+  <si>
+    <t>A/SAJIKU NASI G.PD20</t>
+  </si>
+  <si>
+    <t>10013823</t>
+  </si>
+  <si>
+    <t>A/SAJIKU BB.AYM GR24</t>
+  </si>
+  <si>
+    <t>20103449</t>
+  </si>
+  <si>
+    <t>SAJIKU NSI GRG SPL20</t>
+  </si>
+  <si>
+    <t>10035898</t>
+  </si>
+  <si>
+    <t>A/MASAKO AYAM 100GR</t>
+  </si>
+  <si>
+    <t>20038548</t>
+  </si>
+  <si>
+    <t>MASAKO SAPI 250GR</t>
+  </si>
+  <si>
+    <t>20038549</t>
+  </si>
+  <si>
+    <t>A/MASAKO AYAM 250GR</t>
+  </si>
+  <si>
     <t>20098663</t>
   </si>
   <si>
     <t>TOTOLE KLD JMUR 40G</t>
   </si>
   <si>
-    <t>20103449</t>
-  </si>
-  <si>
-    <t>SAJIKU NSI GRG SPL20</t>
-  </si>
-  <si>
-    <t>20134777</t>
-  </si>
-  <si>
-    <t>SASA KARI JPG ORI 40</t>
-  </si>
-  <si>
-    <t>20134778</t>
-  </si>
-  <si>
-    <t>SASA KARI JPG PDS 40</t>
-  </si>
-  <si>
-    <t>10007775</t>
-  </si>
-  <si>
-    <t>A/SAJIKU NASI G.AY20</t>
-  </si>
-  <si>
-    <t>10035898</t>
-  </si>
-  <si>
-    <t>A/MASAKO AYAM 100GR</t>
-  </si>
-  <si>
     <t>10035899</t>
   </si>
   <si>
     <t>A/MASAKO SAPI 100GR</t>
   </si>
   <si>
+    <t>20135316</t>
+  </si>
+  <si>
+    <t>LARISST BMB JMR 40G</t>
+  </si>
+  <si>
     <t>20104719</t>
   </si>
   <si>
     <t>TOTOLE KLD JMUR 80G</t>
   </si>
   <si>
-    <t>20136397</t>
-  </si>
-  <si>
-    <t>KB BMB AYM LNGKS 80G</t>
-  </si>
-  <si>
-    <t>20136577</t>
-  </si>
-  <si>
-    <t>TUDUNG BMB PRLDK 50G</t>
-  </si>
-  <si>
-    <t>20138072</t>
-  </si>
-  <si>
-    <t>RASA/M OPOR AYAM 40G</t>
-  </si>
-  <si>
-    <t>10013821</t>
-  </si>
-  <si>
-    <t>A/SAJIKU NASI G.PD20</t>
-  </si>
-  <si>
-    <t>20038549</t>
-  </si>
-  <si>
-    <t>A/MASAKO AYAM 250GR</t>
-  </si>
-  <si>
-    <t>20057290</t>
-  </si>
-  <si>
-    <t>SASA BU AYAM KNG 25G</t>
-  </si>
-  <si>
-    <t>20135316</t>
-  </si>
-  <si>
-    <t>LARISST BMB JMR 40G</t>
-  </si>
-  <si>
-    <t>20136743</t>
-  </si>
-  <si>
-    <t>TDUNG BMB NP.RDNG 27</t>
-  </si>
-  <si>
-    <t>20137258</t>
-  </si>
-  <si>
-    <t>RASA/M GULAI AYAM40G</t>
-  </si>
-  <si>
     <t>20138371</t>
   </si>
   <si>
     <t>MAGGI MAGIC LZT 80G</t>
   </si>
   <si>
-    <t>10013823</t>
-  </si>
-  <si>
-    <t>A/SAJIKU BB.AYM GR24</t>
-  </si>
-  <si>
-    <t>20025563</t>
-  </si>
-  <si>
-    <t>SASA BMB LUMUR AYM26</t>
-  </si>
-  <si>
-    <t>20038548</t>
-  </si>
-  <si>
-    <t>MASAKO SAPI 250GR</t>
-  </si>
-  <si>
-    <t>20134507</t>
-  </si>
-  <si>
-    <t>TUDUNG BMB NS UDUK27</t>
-  </si>
-  <si>
-    <t>20138843</t>
-  </si>
-  <si>
-    <t>R/MASA SYR LODEH 25G</t>
-  </si>
-  <si>
     <t>10006884</t>
   </si>
   <si>
@@ -766,66 +766,66 @@
     <t>DELMONTE SAMBL 24X8</t>
   </si>
   <si>
+    <t>10031438</t>
+  </si>
+  <si>
+    <t>SASA SMB X.HOT 24X8G</t>
+  </si>
+  <si>
+    <t>20036865</t>
+  </si>
+  <si>
+    <t>ABC SMAL TERASI 10'S</t>
+  </si>
+  <si>
+    <t>20054028</t>
+  </si>
+  <si>
+    <t>INDO/F SMBL BLDO 200</t>
+  </si>
+  <si>
+    <t>20048582</t>
+  </si>
+  <si>
+    <t>FINNA SMBL/T ULG 10S</t>
+  </si>
+  <si>
+    <t>20012187</t>
+  </si>
+  <si>
+    <t>INDOFOOD SBL PDS 24S</t>
+  </si>
+  <si>
+    <t>20133690</t>
+  </si>
+  <si>
+    <t>SEDAAP KALDU AYAM250</t>
+  </si>
+  <si>
+    <t>20133691</t>
+  </si>
+  <si>
+    <t>SEDAAP KALDU SAPI250</t>
+  </si>
+  <si>
+    <t>20129197</t>
+  </si>
+  <si>
+    <t>KOBE BMB NS UDK 3X15</t>
+  </si>
+  <si>
+    <t>20135466</t>
+  </si>
+  <si>
+    <t>KOBE BMB NS KNNG3X15</t>
+  </si>
+  <si>
     <t>20135428</t>
   </si>
   <si>
     <t>KOBE BMB RNDANG 3X20</t>
   </si>
   <si>
-    <t>10031438</t>
-  </si>
-  <si>
-    <t>SASA SMB X.HOT 24X8G</t>
-  </si>
-  <si>
-    <t>20036865</t>
-  </si>
-  <si>
-    <t>ABC SMAL TERASI 10'S</t>
-  </si>
-  <si>
-    <t>20054028</t>
-  </si>
-  <si>
-    <t>INDO/F SMBL BLDO 200</t>
-  </si>
-  <si>
-    <t>20048582</t>
-  </si>
-  <si>
-    <t>FINNA SMBL/T ULG 10S</t>
-  </si>
-  <si>
-    <t>20012187</t>
-  </si>
-  <si>
-    <t>INDOFOOD SBL PDS 24S</t>
-  </si>
-  <si>
-    <t>20133690</t>
-  </si>
-  <si>
-    <t>SEDAAP KALDU AYAM250</t>
-  </si>
-  <si>
-    <t>20133691</t>
-  </si>
-  <si>
-    <t>SEDAAP KALDU SAPI250</t>
-  </si>
-  <si>
-    <t>20129197</t>
-  </si>
-  <si>
-    <t>KOBE BMB NS UDK 3X15</t>
-  </si>
-  <si>
-    <t>20135466</t>
-  </si>
-  <si>
-    <t>KOBE BMB NS KNNG3X15</t>
-  </si>
-  <si>
     <t>20128243</t>
   </si>
   <si>
@@ -922,6 +922,144 @@
     <t>INDOFOOD RENDANG 50G</t>
   </si>
   <si>
+    <t>10002766</t>
+  </si>
+  <si>
+    <t>INDOFOOD RAWON 50G</t>
+  </si>
+  <si>
+    <t>10002768</t>
+  </si>
+  <si>
+    <t>INDOFOOD OPOR AYM 45</t>
+  </si>
+  <si>
+    <t>10002915</t>
+  </si>
+  <si>
+    <t>INDOFOOD SOTO AYM45G</t>
+  </si>
+  <si>
+    <t>10002767</t>
+  </si>
+  <si>
+    <t>INDOFOOD GULAI 45G</t>
+  </si>
+  <si>
+    <t>10036780</t>
+  </si>
+  <si>
+    <t>INDOFOOD KARE 45G</t>
+  </si>
+  <si>
+    <t>20133254</t>
+  </si>
+  <si>
+    <t>INDOFOOD SEMUR 50G</t>
+  </si>
+  <si>
+    <t>20139390</t>
+  </si>
+  <si>
+    <t>INDO RACIK BALADO 55</t>
+  </si>
+  <si>
+    <t>20013616</t>
+  </si>
+  <si>
+    <t>INDOFD RACIK N.GRG20</t>
+  </si>
+  <si>
+    <t>20013617</t>
+  </si>
+  <si>
+    <t>INDOFD RACIK S.ASM33</t>
+  </si>
+  <si>
+    <t>20036783</t>
+  </si>
+  <si>
+    <t>INDOFD RCK IKN GRG20</t>
+  </si>
+  <si>
+    <t>20133255</t>
+  </si>
+  <si>
+    <t>INDOFOOD AYM MNTGA50</t>
+  </si>
+  <si>
+    <t>20013341</t>
+  </si>
+  <si>
+    <t>BAMBOE RENDANG 35G</t>
+  </si>
+  <si>
+    <t>20014281</t>
+  </si>
+  <si>
+    <t>INDOF RACIK AYM.GR26</t>
+  </si>
+  <si>
+    <t>20023890</t>
+  </si>
+  <si>
+    <t>INDOFD RACIK S.SOP20</t>
+  </si>
+  <si>
+    <t>20113574</t>
+  </si>
+  <si>
+    <t>INDF RCK NSGOR SS 3S</t>
+  </si>
+  <si>
+    <t>10040150</t>
+  </si>
+  <si>
+    <t>INDOF/TBR BK BBQ 25G</t>
+  </si>
+  <si>
+    <t>10040157</t>
+  </si>
+  <si>
+    <t>INDOF TBR BK KEJU25G</t>
+  </si>
+  <si>
+    <t>20013345</t>
+  </si>
+  <si>
+    <t>BAMBOE NASI GRG 40G</t>
+  </si>
+  <si>
+    <t>20140677</t>
+  </si>
+  <si>
+    <t>IND TABURI GAS PD 25</t>
+  </si>
+  <si>
+    <t>20013333</t>
+  </si>
+  <si>
+    <t>BAMBOE BUMBU RAWON54</t>
+  </si>
+  <si>
+    <t>20021359</t>
+  </si>
+  <si>
+    <t>BAMBOE SOTO MADURA40</t>
+  </si>
+  <si>
+    <t>20077364</t>
+  </si>
+  <si>
+    <t>BAMBOE BMB TOM YUM60</t>
+  </si>
+  <si>
+    <t>20139801</t>
+  </si>
+  <si>
+    <t>ROYCO RENDANG 45G</t>
+  </si>
+  <si>
     <t>10005820</t>
   </si>
   <si>
@@ -931,64 +1069,22 @@
     <t>RT,(E-0.5B)</t>
   </si>
   <si>
-    <t>20013341</t>
-  </si>
-  <si>
-    <t>BAMBOE RENDANG 35G</t>
-  </si>
-  <si>
-    <t>20013345</t>
-  </si>
-  <si>
-    <t>BAMBOE NASI GRG 40G</t>
-  </si>
-  <si>
-    <t>20036783</t>
-  </si>
-  <si>
-    <t>INDOFD RCK IKN GRG20</t>
-  </si>
-  <si>
-    <t>20139390</t>
-  </si>
-  <si>
-    <t>INDO RACIK BALADO 55</t>
-  </si>
-  <si>
-    <t>20139801</t>
-  </si>
-  <si>
-    <t>ROYCO RENDANG 45G</t>
-  </si>
-  <si>
-    <t>10002767</t>
-  </si>
-  <si>
-    <t>INDOFOOD GULAI 45G</t>
-  </si>
-  <si>
-    <t>10002768</t>
-  </si>
-  <si>
-    <t>INDOFOOD OPOR AYM 45</t>
-  </si>
-  <si>
-    <t>10040150</t>
-  </si>
-  <si>
-    <t>INDOF/TBR BK BBQ 25G</t>
-  </si>
-  <si>
-    <t>20014281</t>
-  </si>
-  <si>
-    <t>INDOF RACIK AYM.GR26</t>
-  </si>
-  <si>
-    <t>20021359</t>
-  </si>
-  <si>
-    <t>BAMBOE SOTO MADURA40</t>
+    <t>20139784</t>
+  </si>
+  <si>
+    <t>ROYCO SOTO AYAM 40G</t>
+  </si>
+  <si>
+    <t>20139802</t>
+  </si>
+  <si>
+    <t>ROYCO OPOR AYAM 45G</t>
+  </si>
+  <si>
+    <t>20084469</t>
+  </si>
+  <si>
+    <t>ROYCO KALDU AYAM 220</t>
   </si>
   <si>
     <t>20084470</t>
@@ -997,102 +1093,6 @@
     <t>ROYCO KALDU SAPI 220</t>
   </si>
   <si>
-    <t>20133255</t>
-  </si>
-  <si>
-    <t>INDOFOOD AYM MNTGA50</t>
-  </si>
-  <si>
-    <t>20139784</t>
-  </si>
-  <si>
-    <t>ROYCO SOTO AYAM 40G</t>
-  </si>
-  <si>
-    <t>10002915</t>
-  </si>
-  <si>
-    <t>INDOFOOD SOTO AYM45G</t>
-  </si>
-  <si>
-    <t>10036780</t>
-  </si>
-  <si>
-    <t>INDOFOOD KARE 45G</t>
-  </si>
-  <si>
-    <t>10040157</t>
-  </si>
-  <si>
-    <t>INDOF TBR BK KEJU25G</t>
-  </si>
-  <si>
-    <t>20013617</t>
-  </si>
-  <si>
-    <t>INDOFD RACIK S.ASM33</t>
-  </si>
-  <si>
-    <t>20023890</t>
-  </si>
-  <si>
-    <t>INDOFD RACIK S.SOP20</t>
-  </si>
-  <si>
-    <t>20077364</t>
-  </si>
-  <si>
-    <t>BAMBOE BMB TOM YUM60</t>
-  </si>
-  <si>
-    <t>20084469</t>
-  </si>
-  <si>
-    <t>ROYCO KALDU AYAM 220</t>
-  </si>
-  <si>
-    <t>20139802</t>
-  </si>
-  <si>
-    <t>ROYCO OPOR AYAM 45G</t>
-  </si>
-  <si>
-    <t>10002766</t>
-  </si>
-  <si>
-    <t>INDOFOOD RAWON 50G</t>
-  </si>
-  <si>
-    <t>20013333</t>
-  </si>
-  <si>
-    <t>BAMBOE BUMBU RAWON54</t>
-  </si>
-  <si>
-    <t>20013616</t>
-  </si>
-  <si>
-    <t>INDOFD RACIK N.GRG20</t>
-  </si>
-  <si>
-    <t>20113574</t>
-  </si>
-  <si>
-    <t>INDF RCK NSGOR SS 3S</t>
-  </si>
-  <si>
-    <t>20133254</t>
-  </si>
-  <si>
-    <t>INDOFOOD SEMUR 50G</t>
-  </si>
-  <si>
-    <t>20140677</t>
-  </si>
-  <si>
-    <t>IND TABURI GAS PD 25</t>
-  </si>
-  <si>
     <t>10022534</t>
   </si>
   <si>
@@ -1417,48 +1417,54 @@
     <t>RT,(E-7.5B)</t>
   </si>
   <si>
+    <t>20069634</t>
+  </si>
+  <si>
+    <t>BOLA/D AGAR HIJAU 7G</t>
+  </si>
+  <si>
+    <t>20069636</t>
+  </si>
+  <si>
+    <t>BOLA/D AGAR COKLAT7G</t>
+  </si>
+  <si>
+    <t>10036815</t>
+  </si>
+  <si>
+    <t>SW.GLB AGAR COKL. 7G</t>
+  </si>
+  <si>
+    <t>10036819</t>
+  </si>
+  <si>
+    <t>SW.GLB AGAR MERAH 7G</t>
+  </si>
+  <si>
     <t>20069632</t>
   </si>
   <si>
     <t>BOLA/D AGAR MERAH 7G</t>
   </si>
   <si>
-    <t>20069634</t>
-  </si>
-  <si>
-    <t>BOLA/D AGAR HIJAU 7G</t>
-  </si>
-  <si>
-    <t>20069636</t>
-  </si>
-  <si>
-    <t>BOLA/D AGAR COKLAT7G</t>
-  </si>
-  <si>
-    <t>10036815</t>
-  </si>
-  <si>
-    <t>SW.GLB AGAR COKL. 7G</t>
-  </si>
-  <si>
     <t>10036817</t>
   </si>
   <si>
     <t>SW.GLB AGAR PUTIH 7G</t>
   </si>
   <si>
-    <t>10036819</t>
-  </si>
-  <si>
-    <t>SW.GLB AGAR MERAH 7G</t>
-  </si>
-  <si>
     <t>10036821</t>
   </si>
   <si>
     <t>SW.GLB AGAR HIJAU 7G</t>
   </si>
   <si>
+    <t>20046858</t>
+  </si>
+  <si>
+    <t>NUTRIJEL PWD GRAPE15</t>
+  </si>
+  <si>
     <t>10016716</t>
   </si>
   <si>
@@ -1477,18 +1483,24 @@
     <t>NUTRIJELL CINCAU 15G</t>
   </si>
   <si>
-    <t>20046858</t>
-  </si>
-  <si>
-    <t>NUTRIJEL PWD GRAPE15</t>
-  </si>
-  <si>
     <t>10016718</t>
   </si>
   <si>
     <t>NUTRIJEL PWD.LECI 15</t>
   </si>
   <si>
+    <t>20040435</t>
+  </si>
+  <si>
+    <t>MY VLA INST.VANILA60</t>
+  </si>
+  <si>
+    <t>20076797</t>
+  </si>
+  <si>
+    <t>NUTRIJELL KLP MD 15G</t>
+  </si>
+  <si>
     <t>10016719</t>
   </si>
   <si>
@@ -1501,10 +1513,10 @@
     <t>NUTRIJEL POWD.CKT 25</t>
   </si>
   <si>
-    <t>20076797</t>
-  </si>
-  <si>
-    <t>NUTRIJELL KLP MD 15G</t>
+    <t>20040434</t>
+  </si>
+  <si>
+    <t>MY VLA INST.COKLAT63</t>
   </si>
   <si>
     <t>10023618</t>
@@ -1519,16 +1531,10 @@
     <t>AR AGAR PWDR COK 22G</t>
   </si>
   <si>
-    <t>20040434</t>
-  </si>
-  <si>
-    <t>MY VLA INST.COKLAT63</t>
-  </si>
-  <si>
-    <t>20040435</t>
-  </si>
-  <si>
-    <t>MY VLA INST.VANILA60</t>
+    <t>20141199</t>
+  </si>
+  <si>
+    <t>NUTRIJELL KOPI 20G</t>
   </si>
   <si>
     <t>20134767</t>
@@ -1537,12 +1543,6 @@
     <t>NUTRIJELL DRK.CHO 24</t>
   </si>
   <si>
-    <t>20141199</t>
-  </si>
-  <si>
-    <t>NUTRIJELL KOPI 20G</t>
-  </si>
-  <si>
     <t>20026090</t>
   </si>
   <si>
@@ -1693,15 +1693,21 @@
     <t>BOTAN MACKEREL 425G</t>
   </si>
   <si>
+    <t>20138100</t>
+  </si>
+  <si>
+    <t>FVTA MRGN TUB 200G</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
     <t>20029222</t>
   </si>
   <si>
     <t>PRONAS CORNED BEEF50</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>10000135</t>
   </si>
   <si>
@@ -1750,12 +1756,6 @@
     <t>27</t>
   </si>
   <si>
-    <t>20138100</t>
-  </si>
-  <si>
-    <t>FVTA MRGN TUB 200G</t>
-  </si>
-  <si>
     <t>10005073</t>
   </si>
   <si>
@@ -1828,6 +1828,12 @@
     <t>KRAFT QUICK MELT 165</t>
   </si>
   <si>
+    <t>20141197</t>
+  </si>
+  <si>
+    <t>PRO CHIZ Q.MELT 160G</t>
+  </si>
+  <si>
     <t>20058306</t>
   </si>
   <si>
@@ -1927,10 +1933,10 @@
     <t>EMINA CHS SLC MOZA5S</t>
   </si>
   <si>
-    <t>20141197</t>
-  </si>
-  <si>
-    <t>PRO CHIZ Q.MELT 160G</t>
+    <t>20135049</t>
+  </si>
+  <si>
+    <t>EMINA CHS SLC CD 10S</t>
   </si>
   <si>
     <t>20099766</t>
@@ -1990,12 +1996,6 @@
     <t>KEWPIE MAYO ORGN 150</t>
   </si>
   <si>
-    <t>20135049</t>
-  </si>
-  <si>
-    <t>EMINA CHS SLC CD 10S</t>
-  </si>
-  <si>
     <t>10000181</t>
   </si>
   <si>
@@ -2023,6 +2023,12 @@
     <t>IDM M/GORENG 2L</t>
   </si>
   <si>
+    <t>20142108</t>
+  </si>
+  <si>
+    <t>MP MINYAK GRNG1800ML</t>
+  </si>
+  <si>
     <t>20142102</t>
   </si>
   <si>
@@ -2053,22 +2059,55 @@
     <t>SANIA M/GR REF 1000</t>
   </si>
   <si>
+    <t>10008469</t>
+  </si>
+  <si>
+    <t>BARCO MINYAK GR/RF1L</t>
+  </si>
+  <si>
+    <t>20018272</t>
+  </si>
+  <si>
+    <t>IKAN DORANG PCH 950</t>
+  </si>
+  <si>
+    <t>20139800</t>
+  </si>
+  <si>
+    <t>KARA MNYK KLP PCH 1L</t>
+  </si>
+  <si>
+    <t>20037566</t>
+  </si>
+  <si>
+    <t>SOVIA MNYK GR PCH 2L</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20120993</t>
+  </si>
+  <si>
+    <t>HARUMAS MNYAK PCH 2L</t>
+  </si>
+  <si>
+    <t>20140913</t>
+  </si>
+  <si>
+    <t>SOVIA MNYK GR PCH1.8</t>
+  </si>
+  <si>
     <t>20077116</t>
   </si>
   <si>
     <t>SOVIA MNYK GR PCH 1L</t>
   </si>
   <si>
-    <t>10008469</t>
-  </si>
-  <si>
-    <t>BARCO MINYAK GR/RF1L</t>
-  </si>
-  <si>
-    <t>20139800</t>
-  </si>
-  <si>
-    <t>KARA MNYK KLP PCH 1L</t>
+    <t>20113694</t>
+  </si>
+  <si>
+    <t>HAPPY SOYA OIL PCH1L</t>
   </si>
   <si>
     <t>10010805</t>
@@ -2077,46 +2116,13 @@
     <t>SANIA MNYK GR PCH 2L</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20037566</t>
-  </si>
-  <si>
-    <t>SOVIA MNYK GR PCH 2L</t>
-  </si>
-  <si>
-    <t>20120993</t>
-  </si>
-  <si>
-    <t>HARUMAS MNYAK PCH 2L</t>
-  </si>
-  <si>
-    <t>20113694</t>
-  </si>
-  <si>
-    <t>HAPPY SOYA OIL PCH1L</t>
-  </si>
-  <si>
-    <t>20018272</t>
-  </si>
-  <si>
-    <t>IKAN DORANG PCH 950</t>
-  </si>
-  <si>
-    <t>20140913</t>
-  </si>
-  <si>
-    <t>SOVIA MNYK GR PCH1.8</t>
+    <t>34</t>
   </si>
   <si>
     <t>10005838</t>
   </si>
   <si>
     <t>FILMA MINYAK GR RF2L</t>
-  </si>
-  <si>
-    <t>34</t>
   </si>
   <si>
     <t>20016512</t>
@@ -2542,7 +2548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F332"/>
+  <dimension ref="A1:F334"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3469,7 +3475,7 @@
         <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3489,7 +3495,7 @@
         <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3529,7 +3535,7 @@
         <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3546,7 +3552,7 @@
         <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>26</v>
@@ -3609,7 +3615,7 @@
         <v>21</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3626,7 +3632,7 @@
         <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -3646,10 +3652,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3666,10 +3672,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3686,7 +3692,7 @@
         <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>15</v>
@@ -3706,7 +3712,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>15</v>
@@ -3726,7 +3732,7 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>15</v>
@@ -3746,10 +3752,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3766,10 +3772,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3786,7 +3792,7 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>15</v>
@@ -3806,7 +3812,7 @@
         <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>15</v>
@@ -3826,10 +3832,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3846,10 +3852,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3866,10 +3872,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3886,10 +3892,10 @@
         <v>18</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3906,10 +3912,10 @@
         <v>18</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3926,10 +3932,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -4849,7 +4855,7 @@
         <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4869,7 +4875,7 @@
         <v>21</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4889,7 +4895,7 @@
         <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4909,7 +4915,7 @@
         <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -5369,15 +5375,15 @@
         <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>305</v>
+        <v>26</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>307</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
@@ -5394,10 +5400,10 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>309</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
@@ -5414,10 +5420,10 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
@@ -5426,7 +5432,7 @@
         <v>232</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>26</v>
@@ -5434,10 +5440,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
@@ -5446,7 +5452,7 @@
         <v>232</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>26</v>
@@ -5454,10 +5460,10 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
@@ -5466,18 +5472,18 @@
         <v>232</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
@@ -5494,10 +5500,10 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>319</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
@@ -5506,7 +5512,7 @@
         <v>232</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>26</v>
@@ -5514,10 +5520,10 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>321</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
@@ -5526,7 +5532,7 @@
         <v>232</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>26</v>
@@ -5534,10 +5540,10 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
@@ -5546,7 +5552,7 @@
         <v>232</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>26</v>
@@ -5554,10 +5560,10 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
@@ -5566,7 +5572,7 @@
         <v>232</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>26</v>
@@ -5574,10 +5580,10 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
@@ -5586,18 +5592,18 @@
         <v>232</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>305</v>
+        <v>26</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
@@ -5606,7 +5612,7 @@
         <v>232</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>26</v>
@@ -5614,10 +5620,10 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>331</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
@@ -5626,18 +5632,18 @@
         <v>232</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
@@ -5646,18 +5652,18 @@
         <v>232</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
@@ -5666,7 +5672,7 @@
         <v>232</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>26</v>
@@ -5674,10 +5680,10 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
@@ -5686,7 +5692,7 @@
         <v>232</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>26</v>
@@ -5694,10 +5700,10 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
@@ -5706,7 +5712,7 @@
         <v>232</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>26</v>
@@ -5714,10 +5720,10 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>341</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
@@ -5726,7 +5732,7 @@
         <v>232</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>26</v>
@@ -5734,10 +5740,10 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
@@ -5746,7 +5752,7 @@
         <v>232</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>26</v>
@@ -5754,10 +5760,10 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
@@ -5766,18 +5772,18 @@
         <v>232</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>305</v>
+        <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
@@ -5786,18 +5792,18 @@
         <v>232</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
@@ -5806,18 +5812,18 @@
         <v>232</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
@@ -5826,10 +5832,10 @@
         <v>232</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>26</v>
+        <v>351</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5846,10 +5852,10 @@
         <v>232</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5866,10 +5872,10 @@
         <v>232</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5886,10 +5892,10 @@
         <v>232</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>26</v>
+        <v>351</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5906,10 +5912,10 @@
         <v>232</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>26</v>
+        <v>351</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -6049,7 +6055,7 @@
         <v>21</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>305</v>
+        <v>351</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -6069,7 +6075,7 @@
         <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>305</v>
+        <v>351</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6189,7 +6195,7 @@
         <v>14</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>305</v>
+        <v>351</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6229,7 +6235,7 @@
         <v>18</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>305</v>
+        <v>351</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6966,10 +6972,10 @@
         <v>466</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>467</v>
+        <v>84</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -7009,7 +7015,7 @@
         <v>21</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>84</v>
+        <v>467</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7026,7 +7032,7 @@
         <v>466</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>84</v>
@@ -7046,7 +7052,7 @@
         <v>466</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>84</v>
@@ -7086,7 +7092,7 @@
         <v>466</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>5</v>
@@ -7106,7 +7112,7 @@
         <v>466</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>5</v>
@@ -7126,7 +7132,7 @@
         <v>466</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>5</v>
@@ -7146,7 +7152,7 @@
         <v>466</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>5</v>
@@ -7166,7 +7172,7 @@
         <v>466</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>5</v>
@@ -7186,7 +7192,7 @@
         <v>466</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>5</v>
@@ -7206,7 +7212,7 @@
         <v>466</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>5</v>
@@ -7226,7 +7232,7 @@
         <v>466</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>5</v>
@@ -7246,7 +7252,7 @@
         <v>466</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>5</v>
@@ -7266,7 +7272,7 @@
         <v>466</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>5</v>
@@ -7286,7 +7292,7 @@
         <v>466</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>5</v>
@@ -7306,7 +7312,7 @@
         <v>466</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>5</v>
@@ -7326,7 +7332,7 @@
         <v>466</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>5</v>
@@ -7809,7 +7815,7 @@
         <v>4</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7889,15 +7895,15 @@
         <v>31</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>571</v>
+        <v>84</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>572</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>573</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
@@ -7906,10 +7912,10 @@
         <v>562</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>84</v>
+        <v>573</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7929,7 +7935,7 @@
         <v>18</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7943,30 +7949,30 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="C271" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="E271" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>15</v>
@@ -7974,19 +7980,19 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>581</v>
+        <v>560</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>15</v>
@@ -7994,19 +8000,19 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>15</v>
@@ -8014,39 +8020,39 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>26</v>
@@ -8054,19 +8060,19 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>26</v>
@@ -8074,50 +8080,50 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>595</v>
+        <v>580</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>596</v>
+        <v>15</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
@@ -8126,18 +8132,18 @@
         <v>595</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>15</v>
+        <v>596</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
@@ -8146,7 +8152,7 @@
         <v>595</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>15</v>
@@ -8154,10 +8160,10 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
@@ -8166,7 +8172,7 @@
         <v>595</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>15</v>
@@ -8174,10 +8180,10 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
@@ -8186,7 +8192,7 @@
         <v>595</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>15</v>
@@ -8194,10 +8200,10 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
@@ -8206,7 +8212,7 @@
         <v>595</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>15</v>
@@ -8214,10 +8220,10 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
@@ -8226,18 +8232,18 @@
         <v>595</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
@@ -8246,7 +8252,7 @@
         <v>595</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>15</v>
@@ -8254,10 +8260,10 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
@@ -8266,7 +8272,7 @@
         <v>595</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>15</v>
@@ -8274,10 +8280,10 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
@@ -8286,18 +8292,18 @@
         <v>595</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
@@ -8306,7 +8312,7 @@
         <v>595</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>15</v>
@@ -8314,10 +8320,10 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
@@ -8326,7 +8332,7 @@
         <v>595</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>26</v>
@@ -8334,10 +8340,10 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
@@ -8346,7 +8352,7 @@
         <v>595</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>15</v>
@@ -8354,59 +8360,59 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>4</v>
+        <v>180</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>21</v>
+        <v>229</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>15</v>
@@ -8414,39 +8420,39 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>15</v>
@@ -8454,39 +8460,39 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>15</v>
@@ -8494,79 +8500,79 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>26</v>
@@ -8574,19 +8580,19 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>26</v>
@@ -8594,59 +8600,59 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>15</v>
@@ -8654,19 +8660,19 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>15</v>
@@ -8674,19 +8680,19 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>15</v>
@@ -8694,19 +8700,19 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>15</v>
@@ -8714,39 +8720,39 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>663</v>
+        <v>644</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>15</v>
@@ -8754,10 +8760,10 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
@@ -8766,7 +8772,7 @@
         <v>663</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>15</v>
@@ -8774,10 +8780,10 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
@@ -8786,18 +8792,18 @@
         <v>663</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>3</v>
@@ -8806,18 +8812,18 @@
         <v>663</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>441</v>
+        <v>84</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>3</v>
@@ -8826,27 +8832,27 @@
         <v>663</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>672</v>
+        <v>441</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>15</v>
@@ -8854,119 +8860,119 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>15</v>
+        <v>674</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>84</v>
@@ -8974,39 +8980,39 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>84</v>
@@ -9014,19 +9020,19 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>84</v>
@@ -9034,19 +9040,19 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>84</v>
@@ -9054,19 +9060,19 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>84</v>
@@ -9074,19 +9080,19 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>84</v>
@@ -9094,10 +9100,10 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>3</v>
@@ -9106,7 +9112,7 @@
         <v>701</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>84</v>
@@ -9114,10 +9120,10 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
@@ -9126,7 +9132,7 @@
         <v>701</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>84</v>
@@ -9134,10 +9140,10 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
@@ -9146,49 +9152,89 @@
         <v>701</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="E332" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F332" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B333" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="B332" s="1" t="s">
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="C332" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="E332" s="1" t="s">
+      <c r="E333" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F333" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="E334" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F332" s="1" t="s">
+      <c r="F334" s="1" t="s">
         <v>84</v>
       </c>
     </row>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -1750,7 +1750,7 @@
     <t>10000210</t>
   </si>
   <si>
-    <t>BLUE BAND CUP 250G</t>
+    <t>BLUE BAND CUP 230G</t>
   </si>
   <si>
     <t>27</t>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="713">
   <si>
     <t/>
   </si>
@@ -1913,12 +1913,6 @@
   </si>
   <si>
     <t>PRO CHIZ Q.MELT 5'S</t>
-  </si>
-  <si>
-    <t>20103166</t>
-  </si>
-  <si>
-    <t>MEG KEJU SRBGN 10'S</t>
   </si>
   <si>
     <t>20096979</t>
@@ -2548,7 +2542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F334"/>
+  <dimension ref="A1:F333"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -8512,10 +8506,10 @@
         <v>625</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8532,7 +8526,7 @@
         <v>625</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>15</v>
@@ -8552,10 +8546,10 @@
         <v>625</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8569,10 +8563,10 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>26</v>
@@ -8580,19 +8574,19 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D302" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="E302" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>26</v>
@@ -8609,10 +8603,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>26</v>
@@ -8629,13 +8623,13 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8649,10 +8643,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>15</v>
@@ -8669,10 +8663,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>15</v>
@@ -8689,10 +8683,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>15</v>
@@ -8709,10 +8703,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>15</v>
@@ -8729,10 +8723,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>15</v>
@@ -8749,10 +8743,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>644</v>
+        <v>661</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>15</v>
@@ -8760,19 +8754,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>663</v>
-      </c>
       <c r="E311" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>15</v>
@@ -8789,13 +8783,13 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -8809,13 +8803,13 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>84</v>
+        <v>441</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -8829,13 +8823,13 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>441</v>
+        <v>15</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -8849,50 +8843,50 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>15</v>
+        <v>672</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>674</v>
+        <v>15</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D317" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="B317" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="C317" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>677</v>
-      </c>
       <c r="E317" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>15</v>
@@ -8909,13 +8903,13 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -8929,13 +8923,13 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -8949,13 +8943,13 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -8969,13 +8963,13 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -8989,30 +8983,30 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D323" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="B323" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="C323" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D323" s="1" t="s">
-        <v>690</v>
-      </c>
       <c r="E323" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>84</v>
@@ -9029,10 +9023,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>84</v>
@@ -9049,10 +9043,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>84</v>
@@ -9069,10 +9063,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>84</v>
@@ -9089,10 +9083,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>84</v>
@@ -9100,19 +9094,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="E328" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>84</v>
@@ -9129,10 +9123,10 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>84</v>
@@ -9149,10 +9143,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>84</v>
@@ -9169,13 +9163,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9189,10 +9183,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>15</v>
@@ -9200,41 +9194,21 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="B333" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>712</v>
-      </c>
       <c r="E333" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A334" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="B334" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="C334" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D334" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="E334" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F334" s="1" t="s">
         <v>84</v>
       </c>
     </row>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="720">
   <si>
     <t/>
   </si>
@@ -1081,6 +1081,12 @@
     <t>ROYCO OPOR AYAM 45G</t>
   </si>
   <si>
+    <t>20142447</t>
+  </si>
+  <si>
+    <t>ROYCO KALDU SAPI 210</t>
+  </si>
+  <si>
     <t>20084469</t>
   </si>
   <si>
@@ -1093,6 +1099,12 @@
     <t>ROYCO KALDU SAPI 220</t>
   </si>
   <si>
+    <t>20142448</t>
+  </si>
+  <si>
+    <t>ROYCO KALDU AYAM 210</t>
+  </si>
+  <si>
     <t>10022534</t>
   </si>
   <si>
@@ -2137,13 +2149,22 @@
     <t>BIMOLI SPECIAL RF.2L</t>
   </si>
   <si>
+    <t>20093727</t>
+  </si>
+  <si>
+    <t>JUJUR MNYK GRG 2L</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>RT,(E-4.5B)</t>
+  </si>
+  <si>
     <t>10008989</t>
   </si>
   <si>
     <t>BIMOLI MYK.GRG REF2L</t>
-  </si>
-  <si>
-    <t>35</t>
   </si>
   <si>
     <t>10003974</t>
@@ -2542,7 +2563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F333"/>
+  <dimension ref="A1:F336"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -5886,10 +5907,10 @@
         <v>232</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>351</v>
+        <v>15</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5923,13 +5944,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>5</v>
+        <v>351</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5943,13 +5964,13 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5966,10 +5987,10 @@
         <v>235</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5986,10 +6007,10 @@
         <v>235</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -6006,7 +6027,7 @@
         <v>235</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>15</v>
@@ -6023,13 +6044,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6043,13 +6064,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>351</v>
+        <v>15</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -6066,10 +6087,10 @@
         <v>238</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>351</v>
+        <v>26</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6083,50 +6104,50 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>378</v>
+        <v>238</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>15</v>
+        <v>351</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>378</v>
+        <v>238</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>26</v>
+        <v>351</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>15</v>
@@ -6143,13 +6164,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6163,13 +6184,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6183,13 +6204,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>351</v>
+        <v>15</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6203,13 +6224,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6223,10 +6244,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>351</v>
@@ -6243,10 +6264,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -6263,30 +6284,30 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>351</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -6294,19 +6315,19 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -6323,10 +6344,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -6343,10 +6364,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -6363,13 +6384,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6383,13 +6404,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6403,10 +6424,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>15</v>
@@ -6423,10 +6444,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>15</v>
@@ -6443,13 +6464,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6463,53 +6484,53 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="E198" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6523,13 +6544,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6543,13 +6564,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6563,13 +6584,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6583,53 +6604,53 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>431</v>
+        <v>15</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F204" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F204" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6643,13 +6664,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6663,53 +6684,53 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>441</v>
+        <v>84</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>441</v>
+        <v>15</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="E208" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6723,13 +6744,13 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>26</v>
+        <v>445</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6743,13 +6764,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6763,10 +6784,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>26</v>
@@ -6783,13 +6804,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6803,10 +6824,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>26</v>
@@ -6823,13 +6844,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6843,10 +6864,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>26</v>
@@ -6863,10 +6884,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>26</v>
@@ -6883,10 +6904,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>26</v>
@@ -6903,53 +6924,53 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>466</v>
+        <v>444</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>467</v>
+        <v>26</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>466</v>
+        <v>444</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>467</v>
+        <v>26</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6963,13 +6984,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>84</v>
+        <v>471</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -6983,13 +7004,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>84</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7003,13 +7024,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>467</v>
+        <v>84</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7023,10 +7044,10 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>84</v>
@@ -7043,13 +7064,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>84</v>
+        <v>471</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7063,13 +7084,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7083,13 +7104,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7103,10 +7124,10 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>5</v>
@@ -7123,7 +7144,7 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>11</v>
@@ -7143,10 +7164,10 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>5</v>
@@ -7163,10 +7184,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>5</v>
@@ -7183,7 +7204,7 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>31</v>
@@ -7203,10 +7224,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>5</v>
@@ -7223,10 +7244,10 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>5</v>
@@ -7243,7 +7264,7 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>14</v>
@@ -7263,10 +7284,10 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>5</v>
@@ -7283,10 +7304,10 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>5</v>
@@ -7303,7 +7324,7 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>36</v>
@@ -7323,10 +7344,10 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>5</v>
@@ -7343,30 +7364,30 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>512</v>
+        <v>470</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>512</v>
+        <v>470</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>5</v>
@@ -7374,22 +7395,22 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B242" s="1" t="s">
+      <c r="C242" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C242" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>512</v>
-      </c>
       <c r="E242" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7403,10 +7424,10 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>5</v>
@@ -7423,13 +7444,13 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7443,13 +7464,13 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7463,50 +7484,50 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>527</v>
-      </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="B248" s="1" t="s">
+      <c r="C248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C248" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>525</v>
-      </c>
       <c r="E248" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>5</v>
@@ -7523,13 +7544,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7543,13 +7564,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7563,10 +7584,10 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>26</v>
@@ -7583,50 +7604,50 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="B254" s="1" t="s">
+      <c r="C254" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="C254" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="E254" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>5</v>
@@ -7643,13 +7664,13 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7663,13 +7684,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7683,13 +7704,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7703,53 +7724,53 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>551</v>
+        <v>26</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B260" s="1" t="s">
+      <c r="C260" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F260" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="C260" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D260" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="E260" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F260" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7763,10 +7784,10 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>26</v>
@@ -7783,13 +7804,13 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -7803,53 +7824,53 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>564</v>
-      </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="B265" s="1" t="s">
+      <c r="C265" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D265" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="C265" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D265" s="1" t="s">
-        <v>562</v>
-      </c>
       <c r="E265" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7863,10 +7884,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>84</v>
@@ -7883,10 +7904,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>84</v>
@@ -7903,30 +7924,30 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>573</v>
+        <v>84</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B269" s="1" t="s">
-        <v>575</v>
-      </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>84</v>
@@ -7934,22 +7955,22 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="B270" s="1" t="s">
+      <c r="C270" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F270" s="1" t="s">
         <v>577</v>
-      </c>
-      <c r="C270" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D270" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="E270" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F270" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -7963,50 +7984,50 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>561</v>
+        <v>581</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>15</v>
@@ -8014,19 +8035,19 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>583</v>
+        <v>564</v>
       </c>
       <c r="B274" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D274" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="C274" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D274" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="E274" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>15</v>
@@ -8043,13 +8064,13 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -8063,13 +8084,13 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -8083,10 +8104,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>26</v>
@@ -8103,13 +8124,13 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -8123,30 +8144,30 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>596</v>
+        <v>26</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>15</v>
@@ -8154,22 +8175,22 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D281" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B281" s="1" t="s">
+      <c r="E281" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F281" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="C281" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="E281" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F281" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -8183,10 +8204,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>15</v>
@@ -8203,10 +8224,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>15</v>
@@ -8223,13 +8244,13 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8243,10 +8264,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>15</v>
@@ -8263,13 +8284,13 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8283,10 +8304,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>15</v>
@@ -8303,10 +8324,10 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>15</v>
@@ -8323,13 +8344,13 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8343,10 +8364,10 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>15</v>
@@ -8363,10 +8384,10 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>26</v>
@@ -8383,10 +8404,10 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>15</v>
@@ -8403,50 +8424,50 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>625</v>
+        <v>599</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>4</v>
+        <v>180</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>625</v>
+        <v>599</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>21</v>
+        <v>229</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B295" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="B295" s="1" t="s">
+      <c r="C295" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D295" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C295" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="E295" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>15</v>
@@ -8463,13 +8484,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8483,10 +8504,10 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>15</v>
@@ -8503,10 +8524,10 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>15</v>
@@ -8523,10 +8544,10 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>15</v>
@@ -8543,13 +8564,13 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8563,30 +8584,30 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>26</v>
@@ -8594,19 +8615,19 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B303" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="B303" s="1" t="s">
+      <c r="C303" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D303" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="C303" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>642</v>
-      </c>
       <c r="E303" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>26</v>
@@ -8623,13 +8644,13 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8643,13 +8664,13 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -8663,10 +8684,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>15</v>
@@ -8683,10 +8704,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>15</v>
@@ -8703,10 +8724,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>15</v>
@@ -8723,10 +8744,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>15</v>
@@ -8743,10 +8764,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>661</v>
+        <v>646</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>15</v>
@@ -8754,19 +8775,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>663</v>
-      </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>661</v>
+        <v>646</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>15</v>
@@ -8774,22 +8795,22 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="B312" s="1" t="s">
+      <c r="C312" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D312" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="C312" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D312" s="1" t="s">
-        <v>661</v>
-      </c>
       <c r="E312" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -8803,13 +8824,13 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>441</v>
+        <v>15</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -8823,13 +8844,13 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -8843,30 +8864,30 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>672</v>
+        <v>445</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B316" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="B316" s="1" t="s">
-        <v>674</v>
-      </c>
       <c r="C316" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>15</v>
@@ -8874,42 +8895,42 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="E317" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F317" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="B317" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="C317" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="E317" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F317" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="B318" s="1" t="s">
+      <c r="C318" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D318" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="C318" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>675</v>
-      </c>
       <c r="E318" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -8923,13 +8944,13 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -8943,10 +8964,10 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>84</v>
@@ -8963,13 +8984,13 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -8983,10 +9004,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>84</v>
@@ -8994,39 +9015,39 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B323" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="B323" s="1" t="s">
-        <v>690</v>
-      </c>
       <c r="C323" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="B324" s="1" t="s">
+      <c r="C324" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D324" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="C324" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D324" s="1" t="s">
-        <v>688</v>
-      </c>
       <c r="E324" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>84</v>
@@ -9043,10 +9064,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>84</v>
@@ -9063,10 +9084,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>84</v>
@@ -9083,10 +9104,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>84</v>
@@ -9094,19 +9115,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="C328" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>84</v>
@@ -9114,19 +9135,19 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="B329" s="1" t="s">
+      <c r="C329" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D329" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="C329" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>699</v>
-      </c>
       <c r="E329" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>84</v>
@@ -9143,10 +9164,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>84</v>
@@ -9163,13 +9184,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9183,32 +9204,92 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B333" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="B333" s="1" t="s">
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="E333" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F333" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="C333" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="E333" s="1" t="s">
+      <c r="B334" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="E334" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F334" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="E335" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F333" s="1" t="s">
+      <c r="F335" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="E336" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F336" s="1" t="s">
         <v>84</v>
       </c>
     </row>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -766,6 +766,12 @@
     <t>DELMONTE SAMBL 24X8</t>
   </si>
   <si>
+    <t>20012187</t>
+  </si>
+  <si>
+    <t>INDOFOOD SBL PDS 24S</t>
+  </si>
+  <si>
     <t>10031438</t>
   </si>
   <si>
@@ -788,12 +794,6 @@
   </si>
   <si>
     <t>FINNA SMBL/T ULG 10S</t>
-  </si>
-  <si>
-    <t>20012187</t>
-  </si>
-  <si>
-    <t>INDOFOOD SBL PDS 24S</t>
   </si>
   <si>
     <t>20133690</t>
@@ -4864,13 +4864,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4884,13 +4884,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4907,10 +4907,10 @@
         <v>180</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4927,10 +4927,10 @@
         <v>180</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4947,7 +4947,7 @@
         <v>180</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>15</v>
@@ -4967,7 +4967,7 @@
         <v>180</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>15</v>
@@ -4987,7 +4987,7 @@
         <v>180</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>15</v>
@@ -5007,7 +5007,7 @@
         <v>180</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>15</v>
@@ -5027,7 +5027,7 @@
         <v>180</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>15</v>
@@ -5047,7 +5047,7 @@
         <v>180</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>15</v>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2022" uniqueCount="722">
   <si>
     <t/>
   </si>
@@ -748,6 +748,12 @@
     <t>ABC SMBL EXT PDS 380</t>
   </si>
   <si>
+    <t>20142498</t>
+  </si>
+  <si>
+    <t>KZLR NYS GCHJG 150G</t>
+  </si>
+  <si>
     <t>20104152</t>
   </si>
   <si>
@@ -790,6 +796,12 @@
     <t>INDO/F SMBL BLDO 200</t>
   </si>
   <si>
+    <t>20142586</t>
+  </si>
+  <si>
+    <t>INDF SMB CBK LIMAU5S</t>
+  </si>
+  <si>
     <t>20048582</t>
   </si>
   <si>
@@ -826,6 +838,12 @@
     <t>KOBE BMB RNDANG 3X20</t>
   </si>
   <si>
+    <t>20142587</t>
+  </si>
+  <si>
+    <t>INDF SMB COBEK TER5S</t>
+  </si>
+  <si>
     <t>20128243</t>
   </si>
   <si>
@@ -880,12 +898,6 @@
     <t>KUPU2 LADA PTH BBK85</t>
   </si>
   <si>
-    <t>10036774</t>
-  </si>
-  <si>
-    <t>KUPU2 LADA HTM BBK83</t>
-  </si>
-  <si>
     <t>20134371</t>
   </si>
   <si>
@@ -1085,12 +1097,6 @@
   </si>
   <si>
     <t>ROYCO KALDU SAPI 210</t>
-  </si>
-  <si>
-    <t>20084469</t>
-  </si>
-  <si>
-    <t>ROYCO KALDU AYAM 220</t>
   </si>
   <si>
     <t>20084470</t>
@@ -2563,7 +2569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F336"/>
+  <dimension ref="A1:F337"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4870,7 +4876,7 @@
         <v>36</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4890,7 +4896,7 @@
         <v>18</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4904,13 +4910,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4927,10 +4933,10 @@
         <v>180</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4947,10 +4953,10 @@
         <v>180</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4967,7 +4973,7 @@
         <v>180</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>15</v>
@@ -4987,7 +4993,7 @@
         <v>180</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>15</v>
@@ -5007,7 +5013,7 @@
         <v>180</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>15</v>
@@ -5027,7 +5033,7 @@
         <v>180</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>15</v>
@@ -5047,7 +5053,7 @@
         <v>180</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>15</v>
@@ -5064,10 +5070,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>15</v>
@@ -5084,10 +5090,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>15</v>
@@ -5104,10 +5110,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>15</v>
@@ -5127,10 +5133,10 @@
         <v>229</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -5147,7 +5153,7 @@
         <v>229</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>15</v>
@@ -5167,7 +5173,7 @@
         <v>229</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>15</v>
@@ -5187,10 +5193,10 @@
         <v>229</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -5207,10 +5213,10 @@
         <v>229</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -5227,10 +5233,10 @@
         <v>229</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -5247,7 +5253,7 @@
         <v>229</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>15</v>
@@ -5267,10 +5273,10 @@
         <v>229</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -5287,10 +5293,10 @@
         <v>229</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -5307,7 +5313,7 @@
         <v>229</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>47</v>
@@ -5327,7 +5333,7 @@
         <v>229</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>47</v>
@@ -5347,7 +5353,7 @@
         <v>229</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>47</v>
@@ -5364,13 +5370,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>229</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -5384,13 +5390,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E141" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F141" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5447,7 +5453,7 @@
         <v>232</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>26</v>
@@ -5467,7 +5473,7 @@
         <v>232</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>26</v>
@@ -5527,7 +5533,7 @@
         <v>232</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>26</v>
@@ -5547,7 +5553,7 @@
         <v>232</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>26</v>
@@ -5607,7 +5613,7 @@
         <v>232</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>26</v>
@@ -5627,7 +5633,7 @@
         <v>232</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>26</v>
@@ -5670,7 +5676,7 @@
         <v>11</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5687,7 +5693,7 @@
         <v>232</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>26</v>
@@ -5707,10 +5713,10 @@
         <v>232</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5767,7 +5773,7 @@
         <v>232</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>26</v>
@@ -5787,7 +5793,7 @@
         <v>232</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>26</v>
@@ -5830,7 +5836,7 @@
         <v>14</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5847,18 +5853,18 @@
         <v>232</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>351</v>
+        <v>26</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>353</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
@@ -5867,7 +5873,7 @@
         <v>232</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>15</v>
@@ -5875,10 +5881,10 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>355</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
@@ -5890,7 +5896,7 @@
         <v>36</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>15</v>
+        <v>355</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5927,10 +5933,10 @@
         <v>232</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>351</v>
+        <v>15</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5947,10 +5953,10 @@
         <v>232</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>351</v>
+        <v>15</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5970,7 +5976,7 @@
         <v>18</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>15</v>
+        <v>355</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5984,13 +5990,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -6007,7 +6013,7 @@
         <v>235</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -6027,10 +6033,10 @@
         <v>235</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -6047,7 +6053,7 @@
         <v>235</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>15</v>
@@ -6067,7 +6073,7 @@
         <v>235</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>15</v>
@@ -6084,13 +6090,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6107,10 +6113,10 @@
         <v>238</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>351</v>
+        <v>26</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -6127,10 +6133,10 @@
         <v>238</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6144,33 +6150,33 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>382</v>
+        <v>238</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>15</v>
+        <v>355</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6184,13 +6190,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6204,10 +6210,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>15</v>
@@ -6224,13 +6230,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6244,13 +6250,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>351</v>
+        <v>26</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6264,13 +6270,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>5</v>
+        <v>355</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6284,13 +6290,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>351</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6304,13 +6310,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
+        <v>355</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6324,10 +6330,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -6335,19 +6341,19 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="E189" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -6364,10 +6370,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -6384,10 +6390,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -6404,10 +6410,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -6424,13 +6430,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6444,10 +6450,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>15</v>
@@ -6464,10 +6470,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>15</v>
@@ -6484,10 +6490,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>15</v>
@@ -6504,13 +6510,13 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6524,33 +6530,33 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="E199" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6564,13 +6570,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6584,10 +6590,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -6604,13 +6610,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6624,10 +6630,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>15</v>
@@ -6644,33 +6650,33 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>435</v>
+        <v>15</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F205" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F205" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6684,13 +6690,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6704,13 +6710,13 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6724,33 +6730,33 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>445</v>
+        <v>15</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B209" s="1" t="s">
+      <c r="E209" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F209" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6764,13 +6770,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>26</v>
+        <v>447</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6784,10 +6790,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>26</v>
@@ -6804,13 +6810,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6824,13 +6830,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6844,13 +6850,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6864,13 +6870,13 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6884,10 +6890,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>26</v>
@@ -6904,10 +6910,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>26</v>
@@ -6924,10 +6930,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>26</v>
@@ -6944,10 +6950,10 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>26</v>
@@ -6964,33 +6970,33 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>471</v>
+        <v>26</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>470</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -7004,13 +7010,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7024,13 +7030,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>84</v>
+        <v>473</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7044,7 +7050,7 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>21</v>
@@ -7064,13 +7070,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>471</v>
+        <v>84</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7084,13 +7090,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>84</v>
+        <v>473</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7104,7 +7110,7 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>8</v>
@@ -7124,13 +7130,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -7144,10 +7150,10 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>5</v>
@@ -7164,7 +7170,7 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>11</v>
@@ -7184,7 +7190,7 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>11</v>
@@ -7204,10 +7210,10 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>5</v>
@@ -7224,7 +7230,7 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>31</v>
@@ -7244,7 +7250,7 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>31</v>
@@ -7264,10 +7270,10 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>5</v>
@@ -7284,7 +7290,7 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>14</v>
@@ -7304,7 +7310,7 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>14</v>
@@ -7324,10 +7330,10 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>5</v>
@@ -7344,7 +7350,7 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>36</v>
@@ -7364,7 +7370,7 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>36</v>
@@ -7384,10 +7390,10 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>5</v>
@@ -7404,33 +7410,33 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>516</v>
+        <v>472</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="B243" s="1" t="s">
+      <c r="C243" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D243" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="C243" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="E243" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7444,10 +7450,10 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>5</v>
@@ -7464,10 +7470,10 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>5</v>
@@ -7484,13 +7490,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7504,13 +7510,13 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7524,30 +7530,30 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B249" s="1" t="s">
+      <c r="C249" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D249" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C249" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>529</v>
-      </c>
       <c r="E249" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>5</v>
@@ -7564,10 +7570,10 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>5</v>
@@ -7584,13 +7590,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7604,13 +7610,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7624,13 +7630,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7644,30 +7650,30 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="B255" s="1" t="s">
+      <c r="C255" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D255" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C255" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D255" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="E255" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>5</v>
@@ -7684,10 +7690,10 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>5</v>
@@ -7704,13 +7710,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7724,10 +7730,10 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>26</v>
@@ -7744,13 +7750,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7764,33 +7770,33 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>555</v>
+        <v>84</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="B261" s="1" t="s">
+      <c r="C261" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F261" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="C261" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="E261" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F261" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7804,13 +7810,13 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -7824,13 +7830,13 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7844,10 +7850,10 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>26</v>
@@ -7864,33 +7870,33 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>566</v>
+        <v>544</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B266" s="1" t="s">
+      <c r="C266" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D266" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="C266" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D266" s="1" t="s">
-        <v>566</v>
-      </c>
       <c r="E266" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7904,10 +7910,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>84</v>
@@ -7924,10 +7930,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>84</v>
@@ -7944,10 +7950,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>84</v>
@@ -7964,33 +7970,33 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>577</v>
+        <v>84</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F271" s="1" t="s">
         <v>579</v>
-      </c>
-      <c r="C271" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E271" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F271" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -8004,13 +8010,13 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -8024,30 +8030,30 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>15</v>
@@ -8055,19 +8061,19 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>585</v>
+        <v>566</v>
       </c>
       <c r="B275" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D275" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="C275" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="E275" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>15</v>
@@ -8084,10 +8090,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>15</v>
@@ -8104,13 +8110,13 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -8124,10 +8130,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>26</v>
@@ -8144,10 +8150,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>26</v>
@@ -8164,13 +8170,13 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -8184,33 +8190,33 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>600</v>
+        <v>15</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="B282" s="1" t="s">
+      <c r="E282" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F282" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="C282" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="E282" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F282" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -8224,10 +8230,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>15</v>
@@ -8244,10 +8250,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>15</v>
@@ -8264,10 +8270,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>15</v>
@@ -8284,13 +8290,13 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -8304,13 +8310,13 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -8324,10 +8330,10 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>15</v>
@@ -8344,10 +8350,10 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>15</v>
@@ -8364,10 +8370,10 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>15</v>
@@ -8384,13 +8390,13 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8404,13 +8410,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8424,13 +8430,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8444,13 +8450,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8464,10 +8470,10 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>629</v>
+        <v>601</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>4</v>
+        <v>229</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>15</v>
@@ -8475,22 +8481,22 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B296" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B296" s="1" t="s">
+      <c r="C296" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D296" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="C296" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D296" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="E296" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8504,13 +8510,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8524,10 +8530,10 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>15</v>
@@ -8544,10 +8550,10 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>15</v>
@@ -8564,10 +8570,10 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>15</v>
@@ -8584,10 +8590,10 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>15</v>
@@ -8604,13 +8610,13 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -8624,10 +8630,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>26</v>
@@ -8635,19 +8641,19 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B304" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B304" s="1" t="s">
+      <c r="C304" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D304" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="C304" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>646</v>
-      </c>
       <c r="E304" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>26</v>
@@ -8664,10 +8670,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>26</v>
@@ -8684,13 +8690,13 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -8704,10 +8710,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>15</v>
@@ -8724,10 +8730,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>15</v>
@@ -8744,10 +8750,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>15</v>
@@ -8764,10 +8770,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>15</v>
@@ -8784,10 +8790,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>15</v>
@@ -8804,10 +8810,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>15</v>
@@ -8815,19 +8821,19 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B313" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="B313" s="1" t="s">
+      <c r="C313" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D313" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="C313" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>665</v>
-      </c>
       <c r="E313" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>15</v>
@@ -8844,13 +8850,13 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -8864,13 +8870,13 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>445</v>
+        <v>84</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -8884,13 +8890,13 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>15</v>
+        <v>447</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -8904,50 +8910,50 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>676</v>
+        <v>15</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="B318" s="1" t="s">
+      <c r="C318" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="E318" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F318" s="1" t="s">
         <v>678</v>
-      </c>
-      <c r="C318" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E318" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F318" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="B319" s="1" t="s">
+      <c r="C319" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D319" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="C319" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>679</v>
-      </c>
       <c r="E319" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>15</v>
@@ -8964,13 +8970,13 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -8984,13 +8990,13 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -9004,13 +9010,13 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -9024,13 +9030,13 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -9044,30 +9050,30 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B325" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="B325" s="1" t="s">
+      <c r="C325" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D325" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="C325" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D325" s="1" t="s">
-        <v>692</v>
-      </c>
       <c r="E325" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>84</v>
@@ -9084,10 +9090,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>84</v>
@@ -9104,10 +9110,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>84</v>
@@ -9124,10 +9130,10 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>84</v>
@@ -9144,10 +9150,10 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>84</v>
@@ -9155,19 +9161,19 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B330" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B330" s="1" t="s">
+      <c r="C330" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D330" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="C330" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>703</v>
-      </c>
       <c r="E330" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>84</v>
@@ -9184,10 +9190,10 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>84</v>
@@ -9204,10 +9210,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>84</v>
@@ -9224,13 +9230,13 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -9244,33 +9250,33 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>715</v>
+        <v>15</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D335" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="B335" s="1" t="s">
+      <c r="E335" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F335" s="1" t="s">
         <v>717</v>
-      </c>
-      <c r="C335" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D335" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="E335" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F335" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -9284,12 +9290,32 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E336" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F336" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="E337" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F336" s="1" t="s">
+      <c r="F337" s="1" t="s">
         <v>84</v>
       </c>
     </row>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2022" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="724">
   <si>
     <t/>
   </si>
@@ -1121,6 +1121,12 @@
   </si>
   <si>
     <t>ABC KECAP MANIS 825G</t>
+  </si>
+  <si>
+    <t>20142624</t>
+  </si>
+  <si>
+    <t>ABC KCP HTM MNS 550G</t>
   </si>
   <si>
     <t>20123088</t>
@@ -2569,7 +2575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F337"/>
+  <dimension ref="A1:F338"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6056,7 +6062,7 @@
         <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6110,13 +6116,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -6133,10 +6139,10 @@
         <v>238</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>355</v>
+        <v>26</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6153,7 +6159,7 @@
         <v>238</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>355</v>
@@ -6170,33 +6176,33 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>384</v>
+        <v>238</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>15</v>
+        <v>355</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="E181" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6210,13 +6216,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6230,10 +6236,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>15</v>
@@ -6250,13 +6256,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6270,13 +6276,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>355</v>
+        <v>26</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6290,13 +6296,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>355</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6310,13 +6316,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>355</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6330,13 +6336,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
+        <v>355</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6350,10 +6356,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -6361,19 +6367,19 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="E190" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -6390,10 +6396,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -6410,10 +6416,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -6430,10 +6436,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -6450,13 +6456,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -6470,10 +6476,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>15</v>
@@ -6490,10 +6496,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>15</v>
@@ -6510,10 +6516,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>15</v>
@@ -6530,13 +6536,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6550,33 +6556,33 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6590,13 +6596,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6610,10 +6616,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -6630,13 +6636,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6650,10 +6656,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>15</v>
@@ -6670,33 +6676,33 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>437</v>
+        <v>15</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F206" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F206" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6710,13 +6716,13 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6730,13 +6736,13 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6750,33 +6756,33 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>447</v>
+        <v>15</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B210" s="1" t="s">
+      <c r="E210" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F210" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F210" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6790,13 +6796,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>26</v>
+        <v>449</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6810,10 +6816,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>26</v>
@@ -6830,13 +6836,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6850,13 +6856,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6870,13 +6876,13 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6890,13 +6896,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6910,10 +6916,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>26</v>
@@ -6930,10 +6936,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>26</v>
@@ -6950,10 +6956,10 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>26</v>
@@ -6970,10 +6976,10 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>26</v>
@@ -6990,33 +6996,33 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>473</v>
+        <v>26</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>472</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7030,13 +7036,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7050,13 +7056,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>84</v>
+        <v>475</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7070,7 +7076,7 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>21</v>
@@ -7090,13 +7096,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>473</v>
+        <v>84</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7110,13 +7116,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>84</v>
+        <v>475</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7130,7 +7136,7 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>8</v>
@@ -7150,13 +7156,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -7170,10 +7176,10 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>5</v>
@@ -7190,7 +7196,7 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>11</v>
@@ -7210,7 +7216,7 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>11</v>
@@ -7230,10 +7236,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>5</v>
@@ -7250,7 +7256,7 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>31</v>
@@ -7270,7 +7276,7 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>31</v>
@@ -7290,10 +7296,10 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>5</v>
@@ -7310,7 +7316,7 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>14</v>
@@ -7330,7 +7336,7 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>14</v>
@@ -7350,10 +7356,10 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>5</v>
@@ -7370,7 +7376,7 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>36</v>
@@ -7390,7 +7396,7 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>36</v>
@@ -7410,10 +7416,10 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>5</v>
@@ -7430,33 +7436,33 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>518</v>
+        <v>474</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="B244" s="1" t="s">
+      <c r="C244" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D244" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="C244" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>518</v>
-      </c>
       <c r="E244" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7470,10 +7476,10 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>5</v>
@@ -7490,10 +7496,10 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>5</v>
@@ -7510,13 +7516,13 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7530,13 +7536,13 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7550,30 +7556,30 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="B250" s="1" t="s">
+      <c r="C250" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D250" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="C250" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D250" s="1" t="s">
-        <v>531</v>
-      </c>
       <c r="E250" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>5</v>
@@ -7590,10 +7596,10 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>5</v>
@@ -7610,13 +7616,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7630,13 +7636,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7650,13 +7656,13 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7670,30 +7676,30 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="B256" s="1" t="s">
+      <c r="C256" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D256" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="C256" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D256" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="E256" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>5</v>
@@ -7710,10 +7716,10 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>5</v>
@@ -7730,13 +7736,13 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7750,10 +7756,10 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>26</v>
@@ -7770,13 +7776,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7790,33 +7796,33 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>557</v>
+        <v>84</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B262" s="1" t="s">
+      <c r="C262" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F262" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="E262" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F262" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -7830,13 +7836,13 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7850,13 +7856,13 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7870,10 +7876,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>26</v>
@@ -7890,33 +7896,33 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="B267" s="1" t="s">
+      <c r="C267" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D267" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="C267" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D267" s="1" t="s">
-        <v>568</v>
-      </c>
       <c r="E267" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7930,10 +7936,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>84</v>
@@ -7950,10 +7956,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>84</v>
@@ -7970,10 +7976,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>84</v>
@@ -7990,33 +7996,33 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>579</v>
+        <v>84</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="B272" s="1" t="s">
+      <c r="C272" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F272" s="1" t="s">
         <v>581</v>
-      </c>
-      <c r="C272" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D272" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="E272" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F272" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -8030,13 +8036,13 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -8050,30 +8056,30 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>15</v>
@@ -8081,19 +8087,19 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>587</v>
+        <v>568</v>
       </c>
       <c r="B276" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D276" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="C276" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="E276" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>15</v>
@@ -8110,10 +8116,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>15</v>
@@ -8130,13 +8136,13 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -8150,10 +8156,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>26</v>
@@ -8170,10 +8176,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>26</v>
@@ -8190,13 +8196,13 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -8210,33 +8216,33 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>602</v>
+        <v>15</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D283" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="B283" s="1" t="s">
+      <c r="E283" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F283" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="C283" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="E283" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F283" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8250,10 +8256,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>15</v>
@@ -8270,10 +8276,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>15</v>
@@ -8290,10 +8296,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>15</v>
@@ -8310,13 +8316,13 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -8330,13 +8336,13 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8350,10 +8356,10 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>15</v>
@@ -8370,10 +8376,10 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>15</v>
@@ -8390,10 +8396,10 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>15</v>
@@ -8410,13 +8416,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8430,13 +8436,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8450,13 +8456,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8470,13 +8476,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8490,10 +8496,10 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>631</v>
+        <v>603</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>4</v>
+        <v>229</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>15</v>
@@ -8501,22 +8507,22 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="B297" s="1" t="s">
+      <c r="C297" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D297" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="C297" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D297" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="E297" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8530,13 +8536,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8550,10 +8556,10 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>15</v>
@@ -8570,10 +8576,10 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>15</v>
@@ -8590,10 +8596,10 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>15</v>
@@ -8610,10 +8616,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>15</v>
@@ -8630,13 +8636,13 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -8650,10 +8656,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>648</v>
+        <v>633</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>26</v>
@@ -8661,19 +8667,19 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="B305" s="1" t="s">
+      <c r="C305" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D305" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="C305" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>648</v>
-      </c>
       <c r="E305" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>26</v>
@@ -8690,10 +8696,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>26</v>
@@ -8710,13 +8716,13 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -8730,10 +8736,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>15</v>
@@ -8750,10 +8756,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>15</v>
@@ -8770,10 +8776,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>15</v>
@@ -8790,10 +8796,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>15</v>
@@ -8810,10 +8816,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>15</v>
@@ -8830,10 +8836,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>15</v>
@@ -8841,19 +8847,19 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B314" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B314" s="1" t="s">
+      <c r="C314" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D314" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C314" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D314" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="E314" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>15</v>
@@ -8870,13 +8876,13 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -8890,13 +8896,13 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>447</v>
+        <v>84</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -8910,13 +8916,13 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>15</v>
+        <v>449</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -8930,50 +8936,50 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>678</v>
+        <v>15</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="B319" s="1" t="s">
+      <c r="C319" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="E319" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F319" s="1" t="s">
         <v>680</v>
-      </c>
-      <c r="C319" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="E319" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F319" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="B320" s="1" t="s">
+      <c r="C320" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D320" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="C320" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>681</v>
-      </c>
       <c r="E320" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>15</v>
@@ -8990,13 +8996,13 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -9010,13 +9016,13 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -9030,13 +9036,13 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -9050,13 +9056,13 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -9070,30 +9076,30 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B326" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="B326" s="1" t="s">
+      <c r="C326" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D326" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="C326" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D326" s="1" t="s">
-        <v>694</v>
-      </c>
       <c r="E326" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>84</v>
@@ -9110,10 +9116,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>84</v>
@@ -9130,10 +9136,10 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>84</v>
@@ -9150,10 +9156,10 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>84</v>
@@ -9170,10 +9176,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>84</v>
@@ -9181,19 +9187,19 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B331" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="B331" s="1" t="s">
+      <c r="C331" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D331" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="C331" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="E331" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>84</v>
@@ -9210,10 +9216,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>84</v>
@@ -9230,10 +9236,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>84</v>
@@ -9250,13 +9256,13 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -9270,33 +9276,33 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>717</v>
+        <v>15</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D336" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="B336" s="1" t="s">
+      <c r="E336" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F336" s="1" t="s">
         <v>719</v>
-      </c>
-      <c r="C336" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D336" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="E336" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F336" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -9310,12 +9316,32 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E337" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F337" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="E338" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F337" s="1" t="s">
+      <c r="F338" s="1" t="s">
         <v>84</v>
       </c>
     </row>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="725">
   <si>
     <t/>
   </si>
@@ -40,66 +40,60 @@
     <t>3</t>
   </si>
   <si>
-    <t>20117918</t>
-  </si>
-  <si>
-    <t>LA FONTE LASAGNA 230</t>
+    <t>10027768</t>
+  </si>
+  <si>
+    <t>L/F SPAG SAUS BLG117</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10016520</t>
+  </si>
+  <si>
+    <t>PAZTO MAKARN KEJU 63</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20039011</t>
+  </si>
+  <si>
+    <t>MMSUKA S.KRM AYM 55G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20137017</t>
+  </si>
+  <si>
+    <t>DLMONTE CRBNARA 180G</t>
+  </si>
+  <si>
+    <t>20039621</t>
+  </si>
+  <si>
+    <t>PRONAS SC BOLG SP315</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20066050</t>
+  </si>
+  <si>
+    <t>DELMONTE SPG.SAUS250</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10027768</t>
-  </si>
-  <si>
-    <t>L/F SPAG SAUS BLG117</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10016520</t>
-  </si>
-  <si>
-    <t>PAZTO MAKARN KEJU 63</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20039011</t>
-  </si>
-  <si>
-    <t>MMSUKA S.KRM AYM 55G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20137017</t>
-  </si>
-  <si>
-    <t>DLMONTE CRBNARA 180G</t>
-  </si>
-  <si>
-    <t>20039621</t>
-  </si>
-  <si>
-    <t>PRONAS SC BOLG SP315</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20066050</t>
-  </si>
-  <si>
-    <t>DELMONTE SPG.SAUS250</t>
-  </si>
-  <si>
     <t>20066052</t>
   </si>
   <si>
@@ -472,12 +466,6 @@
     <t>TOTOLE KLD JMUR 80G</t>
   </si>
   <si>
-    <t>20138371</t>
-  </si>
-  <si>
-    <t>MAGGI MAGIC LZT 80G</t>
-  </si>
-  <si>
     <t>10006884</t>
   </si>
   <si>
@@ -1099,12 +1087,6 @@
     <t>ROYCO KALDU SAPI 210</t>
   </si>
   <si>
-    <t>20084470</t>
-  </si>
-  <si>
-    <t>ROYCO KALDU SAPI 220</t>
-  </si>
-  <si>
     <t>20142448</t>
   </si>
   <si>
@@ -1643,6 +1625,27 @@
   </si>
   <si>
     <t>P/TANI TAPIOKA 500G</t>
+  </si>
+  <si>
+    <t>20061785</t>
+  </si>
+  <si>
+    <t>IDM POP CORN PCK200G</t>
+  </si>
+  <si>
+    <t>20000412</t>
+  </si>
+  <si>
+    <t>IDM KACANG HIJAU 500</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20141513</t>
+  </si>
+  <si>
+    <t>IDM KCG TNH KPS 250G</t>
   </si>
   <si>
     <t>10036569</t>
@@ -2662,15 +2665,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -2679,10 +2682,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2696,13 +2699,13 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2716,33 +2719,33 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2756,13 +2759,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2776,33 +2779,33 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2816,33 +2819,33 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2856,13 +2859,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2879,10 +2882,10 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2899,10 +2902,10 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2919,30 +2922,30 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2956,13 +2959,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2976,13 +2979,13 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2996,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3016,13 +3019,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3036,13 +3039,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,13 +3059,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -3076,13 +3079,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -3096,10 +3099,10 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -3116,13 +3119,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -3136,13 +3139,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -3156,13 +3159,13 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3176,13 +3179,13 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3196,13 +3199,13 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3216,13 +3219,13 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3236,13 +3239,13 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3256,13 +3259,13 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3276,33 +3279,33 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3316,13 +3319,13 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3336,33 +3339,33 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3376,70 +3379,70 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -3456,13 +3459,13 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3476,13 +3479,13 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3496,13 +3499,13 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3516,13 +3519,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3536,13 +3539,13 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3556,13 +3559,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F49" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3576,13 +3579,13 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F50" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3596,13 +3599,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3616,13 +3619,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3636,13 +3639,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3656,7 +3659,7 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>8</v>
@@ -3676,13 +3679,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3696,13 +3699,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3716,13 +3719,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3736,13 +3739,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3756,13 +3759,13 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3776,13 +3779,13 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3796,13 +3799,13 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3816,13 +3819,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3836,13 +3839,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3856,13 +3859,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3876,13 +3879,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3896,13 +3899,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3916,13 +3919,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3936,10 +3939,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3956,13 +3959,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3976,13 +3979,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3996,13 +3999,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -4016,13 +4019,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4036,13 +4039,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -4056,13 +4059,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4076,13 +4079,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -4096,13 +4099,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4116,13 +4119,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4136,73 +4139,73 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>177</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -4216,13 +4219,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -4236,13 +4239,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -4256,13 +4259,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4276,13 +4279,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4296,10 +4299,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -4316,10 +4319,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -4336,13 +4339,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -4356,13 +4359,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4376,13 +4379,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4396,13 +4399,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4416,10 +4419,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>177</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -4436,10 +4439,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -4456,10 +4459,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -4476,13 +4479,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4496,13 +4499,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4516,13 +4519,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -4536,13 +4539,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4556,13 +4559,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4576,13 +4579,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4596,13 +4599,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -4616,13 +4619,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4636,30 +4639,30 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -4667,82 +4670,82 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>235</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>238</v>
+        <v>18</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4756,13 +4759,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4776,13 +4779,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4796,13 +4799,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4816,13 +4819,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4836,13 +4839,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4856,13 +4859,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4876,13 +4879,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4896,13 +4899,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4916,13 +4919,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4936,13 +4939,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4956,13 +4959,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4976,13 +4979,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4996,13 +4999,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -5016,13 +5019,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -5036,13 +5039,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -5056,13 +5059,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -5076,13 +5079,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -5096,13 +5099,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -5116,13 +5119,13 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -5136,13 +5139,13 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -5156,13 +5159,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -5176,13 +5179,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -5196,13 +5199,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -5216,13 +5219,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -5236,13 +5239,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -5256,13 +5259,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -5276,13 +5279,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -5296,13 +5299,13 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>96</v>
+        <v>173</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -5316,13 +5319,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5336,13 +5339,13 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -5356,13 +5359,13 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -5376,13 +5379,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>229</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -5396,13 +5399,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>232</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5416,13 +5419,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5436,13 +5439,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -5456,13 +5459,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5476,13 +5479,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -5496,13 +5499,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5516,13 +5519,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -5536,13 +5539,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -5556,13 +5559,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -5576,13 +5579,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5596,13 +5599,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5616,13 +5619,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5636,13 +5639,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5656,13 +5659,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5676,13 +5679,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5696,13 +5699,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5716,13 +5719,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5736,13 +5739,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5756,13 +5759,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5776,13 +5779,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5796,13 +5799,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5816,13 +5819,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5836,13 +5839,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5856,53 +5859,53 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>26</v>
+        <v>351</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>355</v>
+        <v>12</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5916,13 +5919,13 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5936,13 +5939,13 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5956,13 +5959,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5976,13 +5979,13 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>355</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5996,13 +5999,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -6016,13 +6019,13 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -6036,13 +6039,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -6056,13 +6059,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6076,13 +6079,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -6096,13 +6099,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>15</v>
+        <v>351</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6116,13 +6119,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>15</v>
+        <v>351</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -6136,73 +6139,73 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>238</v>
+        <v>380</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>355</v>
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>238</v>
+        <v>380</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>355</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6216,13 +6219,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6236,13 +6239,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>15</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6256,13 +6259,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6276,13 +6279,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>26</v>
+        <v>351</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6296,13 +6299,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>355</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6316,10 +6319,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -6327,39 +6330,39 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>386</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>355</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -6367,19 +6370,19 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -6396,10 +6399,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -6416,13 +6419,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6436,13 +6439,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6456,13 +6459,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -6476,13 +6479,13 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6496,13 +6499,13 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6516,50 +6519,50 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="E198" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -6567,22 +6570,22 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6596,13 +6599,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6616,13 +6619,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6636,73 +6639,73 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>5</v>
+        <v>433</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>439</v>
+        <v>12</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6716,73 +6719,73 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>5</v>
+        <v>443</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="E208" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>449</v>
+        <v>23</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6796,13 +6799,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>449</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6816,13 +6819,13 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6836,13 +6839,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6856,13 +6859,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6876,13 +6879,13 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6896,13 +6899,13 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6916,13 +6919,13 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -6936,13 +6939,13 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>96</v>
+        <v>173</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6956,73 +6959,73 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>26</v>
+        <v>469</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B220" s="1" t="s">
+      <c r="E220" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F220" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F220" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>177</v>
+        <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>26</v>
+        <v>469</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>475</v>
+        <v>82</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7036,13 +7039,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>475</v>
+        <v>82</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7056,13 +7059,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7076,13 +7079,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7096,13 +7099,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7116,13 +7119,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>475</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7136,13 +7139,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -7156,13 +7159,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -7176,10 +7179,10 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>5</v>
@@ -7196,10 +7199,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>5</v>
@@ -7216,10 +7219,10 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>5</v>
@@ -7236,10 +7239,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>5</v>
@@ -7256,10 +7259,10 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>5</v>
@@ -7276,10 +7279,10 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>5</v>
@@ -7296,10 +7299,10 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>5</v>
@@ -7316,10 +7319,10 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>5</v>
@@ -7336,10 +7339,10 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>5</v>
@@ -7356,10 +7359,10 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>5</v>
@@ -7376,10 +7379,10 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>5</v>
@@ -7396,30 +7399,30 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>474</v>
+        <v>514</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="E242" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>5</v>
@@ -7427,19 +7430,19 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>474</v>
+        <v>514</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>5</v>
@@ -7447,22 +7450,22 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7476,13 +7479,13 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7496,13 +7499,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7516,10 +7519,10 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>5</v>
@@ -7527,62 +7530,62 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B248" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>520</v>
-      </c>
       <c r="E248" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7596,13 +7599,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7616,13 +7619,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7636,13 +7639,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7656,47 +7659,47 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>84</v>
+        <v>542</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>4</v>
@@ -7707,19 +7710,19 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="C257" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>546</v>
-      </c>
       <c r="E257" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>5</v>
@@ -7727,16 +7730,16 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>8</v>
@@ -7747,119 +7750,119 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>5</v>
@@ -7867,199 +7870,199 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D268" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="C268" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>570</v>
-      </c>
       <c r="E268" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>5</v>
@@ -8067,279 +8070,279 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D277" s="1" t="s">
         <v>589</v>
-      </c>
-      <c r="B277" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="C277" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>588</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>5</v>
@@ -8347,199 +8350,199 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D298" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="B298" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>633</v>
-      </c>
       <c r="E298" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>5</v>
@@ -8547,802 +8550,802 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D306" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="B306" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C306" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>650</v>
-      </c>
       <c r="E306" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D315" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B315" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="C315" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D315" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="E315" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D321" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="B321" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="C321" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>683</v>
-      </c>
       <c r="E321" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D327" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="B327" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="C327" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D327" s="1" t="s">
-        <v>696</v>
-      </c>
       <c r="E327" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D332" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="B332" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>707</v>
-      </c>
       <c r="E332" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -1882,13 +1882,13 @@
     <t>20113339</t>
   </si>
   <si>
-    <t>EMINA CHS MOZA 160G</t>
+    <t>EMINA CHS MOZA 150G</t>
   </si>
   <si>
     <t>20121028</t>
   </si>
   <si>
-    <t>EMINA SH.CHEESE 160G</t>
+    <t>EMINA SH.CHEESE 150G</t>
   </si>
   <si>
     <t>20137600</t>
@@ -1900,7 +1900,7 @@
     <t>20113338</t>
   </si>
   <si>
-    <t>EMINA CHSE MILD 160G</t>
+    <t>EMINA CHSE MILD 150G</t>
   </si>
   <si>
     <t>20140675</t>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -253,21 +253,21 @@
     <t>AJINOMOTO RP 5000,-</t>
   </si>
   <si>
-    <t>10000431</t>
-  </si>
-  <si>
-    <t>SASA BUMBU MSK 100GR</t>
+    <t>20123853</t>
+  </si>
+  <si>
+    <t>SASA 5.000 80G</t>
+  </si>
+  <si>
+    <t>10003696</t>
+  </si>
+  <si>
+    <t>SASA BUMBU MSK 250GR</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>10003696</t>
-  </si>
-  <si>
-    <t>SASA BUMBU MSK 250GR</t>
-  </si>
-  <si>
     <t>10003697</t>
   </si>
   <si>
@@ -1138,7 +1138,7 @@
     <t>10008819</t>
   </si>
   <si>
-    <t>BANGO KECAP MNS 700G</t>
+    <t>BANGO K MANIS 700 G</t>
   </si>
   <si>
     <t>20117107</t>
@@ -2041,7 +2041,7 @@
     <t>20043713</t>
   </si>
   <si>
-    <t>IDM M/GORENG 2L</t>
+    <t>IDM M/GORENG 2 L</t>
   </si>
   <si>
     <t>20142108</t>
@@ -2134,7 +2134,7 @@
     <t>10010805</t>
   </si>
   <si>
-    <t>SANIA MNYK GR PCH 2L</t>
+    <t>SANIA MYK GR PCH 2 L</t>
   </si>
   <si>
     <t>34</t>
@@ -2155,7 +2155,7 @@
     <t>10000442</t>
   </si>
   <si>
-    <t>FORTUNE MYK.GRG RF2L</t>
+    <t>FORTUNE MYK.GR R 2 L</t>
   </si>
   <si>
     <t>10012753</t>
@@ -3285,15 +3285,15 @@
         <v>26</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -3305,7 +3305,7 @@
         <v>29</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3385,7 +3385,7 @@
         <v>94</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -6685,7 +6685,7 @@
         <v>97</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -7025,7 +7025,7 @@
         <v>18</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7045,7 +7045,7 @@
         <v>18</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7085,7 +7085,7 @@
         <v>8</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7105,7 +7105,7 @@
         <v>8</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7405,7 +7405,7 @@
         <v>4</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7605,7 +7605,7 @@
         <v>29</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7805,7 +7805,7 @@
         <v>11</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7945,7 +7945,7 @@
         <v>18</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7965,7 +7965,7 @@
         <v>8</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7985,7 +7985,7 @@
         <v>26</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -8005,7 +8005,7 @@
         <v>29</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -8045,7 +8045,7 @@
         <v>15</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -8905,7 +8905,7 @@
         <v>8</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -9025,7 +9025,7 @@
         <v>8</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -9065,7 +9065,7 @@
         <v>29</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -9105,7 +9105,7 @@
         <v>4</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -9125,7 +9125,7 @@
         <v>18</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -9145,7 +9145,7 @@
         <v>8</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -9165,7 +9165,7 @@
         <v>26</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -9185,7 +9185,7 @@
         <v>29</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9205,7 +9205,7 @@
         <v>4</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9225,7 +9225,7 @@
         <v>18</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -9245,7 +9245,7 @@
         <v>8</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -9265,7 +9265,7 @@
         <v>26</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -9345,7 +9345,7 @@
         <v>8</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -1138,7 +1138,7 @@
     <t>10008819</t>
   </si>
   <si>
-    <t>BANGO K MANIS 700 G</t>
+    <t>BANGO KECAP MNS 700G</t>
   </si>
   <si>
     <t>20117107</t>
@@ -2041,7 +2041,7 @@
     <t>20043713</t>
   </si>
   <si>
-    <t>IDM M/GORENG 2 L</t>
+    <t>IDM M/GORENG 2L</t>
   </si>
   <si>
     <t>20142108</t>
@@ -2134,7 +2134,7 @@
     <t>10010805</t>
   </si>
   <si>
-    <t>SANIA MYK GR PCH 2 L</t>
+    <t>SANIA MNYK GR PCH 2L</t>
   </si>
   <si>
     <t>34</t>
@@ -2155,7 +2155,7 @@
     <t>10000442</t>
   </si>
   <si>
-    <t>FORTUNE MYK.GR R 2 L</t>
+    <t>FORTUNE MYK.GRG RF2L</t>
   </si>
   <si>
     <t>10012753</t>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -1063,7 +1063,7 @@
     <t>10005820</t>
   </si>
   <si>
-    <t>ROYCO KALDU AYAM 94G</t>
+    <t>ROYCO KALDU AYAM 90G</t>
   </si>
   <si>
     <t>RT,(E-0.5B)</t>
@@ -1138,13 +1138,13 @@
     <t>10008819</t>
   </si>
   <si>
-    <t>BANGO KECAP MNS 700G</t>
+    <t>BANGO KECAP MNS 685G</t>
   </si>
   <si>
     <t>20117107</t>
   </si>
   <si>
-    <t>BANGO KECAP MNS 735</t>
+    <t>BANGO KECAP MNS 920G</t>
   </si>
   <si>
     <t>20134927</t>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2034" uniqueCount="727">
   <si>
     <t/>
   </si>
@@ -1706,6 +1706,12 @@
   </si>
   <si>
     <t>MAYA SRDN TMTO 155G</t>
+  </si>
+  <si>
+    <t>20143150</t>
+  </si>
+  <si>
+    <t>MAYA TN MYK KDL185G</t>
   </si>
   <si>
     <t>10005980</t>
@@ -2578,7 +2584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F338"/>
+  <dimension ref="A1:F339"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -7885,7 +7891,7 @@
         <v>100</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7919,33 +7925,33 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="B268" s="1" t="s">
+      <c r="C268" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D268" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C268" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="E268" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7959,10 +7965,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>84</v>
@@ -7979,10 +7985,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>84</v>
@@ -7999,10 +8005,10 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>84</v>
@@ -8019,33 +8025,33 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>582</v>
+        <v>84</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B273" s="1" t="s">
+      <c r="C273" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F273" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="C273" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="E273" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F273" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -8059,13 +8065,13 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -8079,30 +8085,30 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>569</v>
+        <v>589</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>12</v>
@@ -8110,19 +8116,19 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>590</v>
+        <v>571</v>
       </c>
       <c r="B277" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D277" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="C277" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>589</v>
-      </c>
       <c r="E277" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>12</v>
@@ -8139,10 +8145,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>12</v>
@@ -8159,13 +8165,13 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -8179,10 +8185,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8199,10 +8205,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8219,13 +8225,13 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -8239,33 +8245,33 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>605</v>
+        <v>12</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D284" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B284" s="1" t="s">
+      <c r="E284" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F284" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="C284" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="E284" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F284" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8279,10 +8285,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>12</v>
@@ -8299,10 +8305,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>12</v>
@@ -8319,10 +8325,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>12</v>
@@ -8339,13 +8345,13 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -8359,13 +8365,13 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8379,10 +8385,10 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>12</v>
@@ -8399,10 +8405,10 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>12</v>
@@ -8419,10 +8425,10 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>12</v>
@@ -8439,13 +8445,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8459,13 +8465,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8479,13 +8485,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8499,13 +8505,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8519,10 +8525,10 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>634</v>
+        <v>606</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>12</v>
@@ -8530,22 +8536,22 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="B298" s="1" t="s">
+      <c r="C298" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D298" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="C298" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>634</v>
-      </c>
       <c r="E298" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8559,13 +8565,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8579,10 +8585,10 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>12</v>
@@ -8599,10 +8605,10 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>12</v>
@@ -8619,10 +8625,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>12</v>
@@ -8639,10 +8645,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>12</v>
@@ -8659,13 +8665,13 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8679,10 +8685,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>651</v>
+        <v>636</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8690,19 +8696,19 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B306" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="B306" s="1" t="s">
+      <c r="C306" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D306" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="C306" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>651</v>
-      </c>
       <c r="E306" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8719,10 +8725,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8739,13 +8745,13 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -8759,10 +8765,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>12</v>
@@ -8779,10 +8785,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>12</v>
@@ -8799,10 +8805,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>12</v>
@@ -8819,10 +8825,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>12</v>
@@ -8839,10 +8845,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>12</v>
@@ -8859,10 +8865,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>670</v>
+        <v>653</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>12</v>
@@ -8870,19 +8876,19 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B315" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="B315" s="1" t="s">
+      <c r="C315" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D315" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="C315" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D315" s="1" t="s">
-        <v>670</v>
-      </c>
       <c r="E315" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>12</v>
@@ -8899,13 +8905,13 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -8919,13 +8925,13 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>443</v>
+        <v>84</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -8939,13 +8945,13 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>12</v>
+        <v>443</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -8959,50 +8965,50 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>681</v>
+        <v>12</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="B320" s="1" t="s">
+      <c r="C320" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="E320" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F320" s="1" t="s">
         <v>683</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="E320" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F320" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B321" s="1" t="s">
+      <c r="C321" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D321" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="C321" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>684</v>
-      </c>
       <c r="E321" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>12</v>
@@ -9019,13 +9025,13 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -9039,13 +9045,13 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -9059,13 +9065,13 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -9079,13 +9085,13 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -9099,30 +9105,30 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B327" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="B327" s="1" t="s">
+      <c r="C327" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D327" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="C327" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D327" s="1" t="s">
-        <v>697</v>
-      </c>
       <c r="E327" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>84</v>
@@ -9139,10 +9145,10 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>84</v>
@@ -9159,10 +9165,10 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>84</v>
@@ -9179,10 +9185,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>84</v>
@@ -9199,10 +9205,10 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>84</v>
@@ -9210,19 +9216,19 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B332" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="B332" s="1" t="s">
+      <c r="C332" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D332" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="C332" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>708</v>
-      </c>
       <c r="E332" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>84</v>
@@ -9239,10 +9245,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>84</v>
@@ -9259,10 +9265,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>84</v>
@@ -9279,13 +9285,13 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -9299,33 +9305,33 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>720</v>
+        <v>12</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D337" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B337" s="1" t="s">
+      <c r="E337" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F337" s="1" t="s">
         <v>722</v>
-      </c>
-      <c r="C337" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D337" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="E337" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F337" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -9339,12 +9345,32 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F338" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="E339" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F339" s="1" t="s">
         <v>84</v>
       </c>
     </row>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2034" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="730">
   <si>
     <t/>
   </si>
@@ -1345,12 +1345,6 @@
     <t>PT,(E-0.5B)</t>
   </si>
   <si>
-    <t>20115331</t>
-  </si>
-  <si>
-    <t>IDM SANTAN KELAPA 65</t>
-  </si>
-  <si>
     <t>10022118</t>
   </si>
   <si>
@@ -1375,6 +1369,15 @@
     <t>SUN KARA SANTAN 200</t>
   </si>
   <si>
+    <t>20138647</t>
+  </si>
+  <si>
+    <t>SUN KARA TPK 110ML</t>
+  </si>
+  <si>
+    <t>,(E-2B)</t>
+  </si>
+  <si>
     <t>10036806</t>
   </si>
   <si>
@@ -2186,6 +2189,12 @@
   </si>
   <si>
     <t>BIMOLI MYK.GRG REF2L</t>
+  </si>
+  <si>
+    <t>20140636</t>
+  </si>
+  <si>
+    <t>TROPICAL MNYK BTL1.5</t>
   </si>
   <si>
     <t>10003974</t>
@@ -2584,7 +2593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F339"/>
+  <dimension ref="A1:F340"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6748,10 +6757,10 @@
         <v>442</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>443</v>
+        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6768,7 +6777,7 @@
         <v>442</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6788,10 +6797,10 @@
         <v>442</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6808,10 +6817,10 @@
         <v>442</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6828,18 +6837,18 @@
         <v>442</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>23</v>
+        <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
@@ -6848,7 +6857,7 @@
         <v>442</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6856,10 +6865,10 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
@@ -6868,7 +6877,7 @@
         <v>442</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>23</v>
@@ -6876,10 +6885,10 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
@@ -6888,7 +6897,7 @@
         <v>442</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>23</v>
@@ -6896,10 +6905,10 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
@@ -6908,7 +6917,7 @@
         <v>442</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -6916,10 +6925,10 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
@@ -6928,7 +6937,7 @@
         <v>442</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -6936,10 +6945,10 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
@@ -6948,7 +6957,7 @@
         <v>442</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>23</v>
@@ -6956,76 +6965,76 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>18</v>
@@ -7036,16 +7045,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>18</v>
@@ -7056,36 +7065,36 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>8</v>
@@ -7096,16 +7105,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>8</v>
@@ -7116,16 +7125,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>8</v>
@@ -7136,16 +7145,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>26</v>
@@ -7156,16 +7165,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>26</v>
@@ -7176,16 +7185,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>26</v>
@@ -7196,16 +7205,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>29</v>
@@ -7216,16 +7225,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>29</v>
@@ -7236,16 +7245,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>29</v>
@@ -7256,16 +7265,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>11</v>
@@ -7276,16 +7285,16 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>11</v>
@@ -7296,16 +7305,16 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>11</v>
@@ -7316,16 +7325,16 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>34</v>
@@ -7336,16 +7345,16 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>34</v>
@@ -7356,16 +7365,16 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>34</v>
@@ -7376,16 +7385,16 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>15</v>
@@ -7396,16 +7405,16 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>4</v>
@@ -7416,16 +7425,16 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>514</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>18</v>
@@ -7436,16 +7445,16 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>8</v>
@@ -7456,16 +7465,16 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>26</v>
@@ -7476,16 +7485,16 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>29</v>
@@ -7496,16 +7505,16 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>11</v>
@@ -7516,16 +7525,16 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>4</v>
@@ -7536,16 +7545,16 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>18</v>
@@ -7556,16 +7565,16 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>8</v>
@@ -7576,16 +7585,16 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>26</v>
@@ -7596,16 +7605,16 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>29</v>
@@ -7616,16 +7625,16 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>11</v>
@@ -7636,16 +7645,16 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>34</v>
@@ -7656,36 +7665,36 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>94</v>
@@ -7696,16 +7705,16 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>4</v>
@@ -7716,16 +7725,16 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="B257" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="C257" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>547</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>18</v>
@@ -7736,16 +7745,16 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>8</v>
@@ -7756,16 +7765,16 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>26</v>
@@ -7776,16 +7785,16 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>29</v>
@@ -7796,16 +7805,16 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>11</v>
@@ -7816,36 +7825,36 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>94</v>
@@ -7856,16 +7865,16 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>97</v>
@@ -7876,16 +7885,16 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>100</v>
@@ -7896,16 +7905,16 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>173</v>
@@ -7916,16 +7925,16 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>176</v>
@@ -7936,16 +7945,16 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>4</v>
@@ -7956,16 +7965,16 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="C269" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>573</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>18</v>
@@ -7976,16 +7985,16 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>8</v>
@@ -7996,16 +8005,16 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>26</v>
@@ -8016,16 +8025,16 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>29</v>
@@ -8036,36 +8045,36 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>15</v>
@@ -8076,16 +8085,16 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>94</v>
@@ -8096,16 +8105,16 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>4</v>
@@ -8116,16 +8125,16 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>18</v>
@@ -8136,16 +8145,16 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D278" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="B278" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="C278" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>591</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>8</v>
@@ -8156,16 +8165,16 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>26</v>
@@ -8176,16 +8185,16 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>29</v>
@@ -8196,16 +8205,16 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>11</v>
@@ -8216,16 +8225,16 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>34</v>
@@ -8236,16 +8245,16 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>15</v>
@@ -8256,36 +8265,36 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>18</v>
@@ -8296,16 +8305,16 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>8</v>
@@ -8316,16 +8325,16 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>26</v>
@@ -8336,16 +8345,16 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>29</v>
@@ -8356,16 +8365,16 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>11</v>
@@ -8376,16 +8385,16 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>34</v>
@@ -8396,16 +8405,16 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>15</v>
@@ -8416,16 +8425,16 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>94</v>
@@ -8436,16 +8445,16 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>97</v>
@@ -8456,16 +8465,16 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>100</v>
@@ -8476,16 +8485,16 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>173</v>
@@ -8496,16 +8505,16 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>176</v>
@@ -8516,16 +8525,16 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>225</v>
@@ -8536,16 +8545,16 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>4</v>
@@ -8556,16 +8565,16 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D299" s="1" t="s">
         <v>637</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>636</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>18</v>
@@ -8576,16 +8585,16 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>8</v>
@@ -8596,16 +8605,16 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>26</v>
@@ -8616,16 +8625,16 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>29</v>
@@ -8636,16 +8645,16 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>34</v>
@@ -8656,16 +8665,16 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>15</v>
@@ -8676,16 +8685,16 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>94</v>
@@ -8696,16 +8705,16 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>4</v>
@@ -8716,16 +8725,16 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D307" s="1" t="s">
         <v>654</v>
-      </c>
-      <c r="B307" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="C307" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>653</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>18</v>
@@ -8736,16 +8745,16 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>8</v>
@@ -8756,16 +8765,16 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>26</v>
@@ -8776,16 +8785,16 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>29</v>
@@ -8796,16 +8805,16 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>11</v>
@@ -8816,16 +8825,16 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>34</v>
@@ -8836,16 +8845,16 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>15</v>
@@ -8856,16 +8865,16 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>94</v>
@@ -8876,16 +8885,16 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>4</v>
@@ -8896,16 +8905,16 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D316" s="1" t="s">
         <v>673</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>672</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>18</v>
@@ -8916,16 +8925,16 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>8</v>
@@ -8936,16 +8945,16 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>26</v>
@@ -8956,16 +8965,16 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>29</v>
@@ -8976,36 +8985,36 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>4</v>
@@ -9016,16 +9025,16 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>687</v>
-      </c>
-      <c r="B322" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>686</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>18</v>
@@ -9036,16 +9045,16 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>8</v>
@@ -9056,16 +9065,16 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>26</v>
@@ -9076,16 +9085,16 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>29</v>
@@ -9096,16 +9105,16 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>11</v>
@@ -9116,16 +9125,16 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>4</v>
@@ -9136,16 +9145,16 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="B328" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>699</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>18</v>
@@ -9156,16 +9165,16 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>8</v>
@@ -9176,16 +9185,16 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>26</v>
@@ -9196,16 +9205,16 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>29</v>
@@ -9216,16 +9225,16 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>4</v>
@@ -9236,16 +9245,16 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>711</v>
-      </c>
-      <c r="B333" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>710</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>18</v>
@@ -9256,16 +9265,16 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>8</v>
@@ -9276,16 +9285,16 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>26</v>
@@ -9296,16 +9305,16 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>29</v>
@@ -9316,36 +9325,36 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>18</v>
@@ -9356,21 +9365,41 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E339" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F339" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="E340" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F339" s="1" t="s">
+      <c r="F340" s="1" t="s">
         <v>84</v>
       </c>
     </row>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="732">
   <si>
     <t/>
   </si>
@@ -1235,6 +1235,12 @@
   </si>
   <si>
     <t>NUTRI/J PUDNG B/C130</t>
+  </si>
+  <si>
+    <t>20143399</t>
+  </si>
+  <si>
+    <t>NRJL PDG SUSU COCO90</t>
   </si>
   <si>
     <t>20132655</t>
@@ -2593,7 +2599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F340"/>
+  <dimension ref="A1:F341"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6440,7 +6446,7 @@
         <v>11</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6520,7 +6526,7 @@
         <v>97</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6534,33 +6540,33 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="E198" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6574,13 +6580,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6594,10 +6600,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -6614,13 +6620,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6634,10 +6640,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>12</v>
@@ -6654,33 +6660,33 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>433</v>
+        <v>12</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F204" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F204" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6694,13 +6700,13 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6714,13 +6720,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6734,33 +6740,33 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>443</v>
+        <v>12</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="E208" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6774,10 +6780,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6794,13 +6800,13 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6814,13 +6820,13 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6834,33 +6840,33 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>454</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F213" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F213" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6874,13 +6880,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6894,10 +6900,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>23</v>
@@ -6914,10 +6920,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -6934,10 +6940,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -6954,10 +6960,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>23</v>
@@ -6974,33 +6980,33 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>470</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -7014,13 +7020,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -7034,13 +7040,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>84</v>
+        <v>472</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7054,7 +7060,7 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>18</v>
@@ -7074,13 +7080,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>470</v>
+        <v>84</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7094,13 +7100,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>84</v>
+        <v>472</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7114,7 +7120,7 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>8</v>
@@ -7134,13 +7140,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7154,10 +7160,10 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>5</v>
@@ -7174,7 +7180,7 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>26</v>
@@ -7194,7 +7200,7 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>26</v>
@@ -7214,10 +7220,10 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>5</v>
@@ -7234,7 +7240,7 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>29</v>
@@ -7254,7 +7260,7 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>29</v>
@@ -7274,10 +7280,10 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>5</v>
@@ -7294,7 +7300,7 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>11</v>
@@ -7314,7 +7320,7 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>11</v>
@@ -7334,10 +7340,10 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>5</v>
@@ -7354,7 +7360,7 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>34</v>
@@ -7374,7 +7380,7 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>34</v>
@@ -7394,10 +7400,10 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>5</v>
@@ -7414,33 +7420,33 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>515</v>
+        <v>471</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B242" s="1" t="s">
+      <c r="C242" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="C242" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="E242" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7454,10 +7460,10 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>5</v>
@@ -7474,10 +7480,10 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>5</v>
@@ -7494,13 +7500,13 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7514,13 +7520,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7534,30 +7540,30 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B248" s="1" t="s">
+      <c r="C248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="C248" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>528</v>
-      </c>
       <c r="E248" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>5</v>
@@ -7574,10 +7580,10 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>5</v>
@@ -7594,13 +7600,13 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7614,13 +7620,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7634,13 +7640,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7654,13 +7660,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7674,33 +7680,33 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>543</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="B255" s="1" t="s">
+      <c r="C255" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F255" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="C255" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D255" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="E255" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F255" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7714,30 +7720,30 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B257" s="1" t="s">
+      <c r="C257" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="C257" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="E257" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>5</v>
@@ -7754,10 +7760,10 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>5</v>
@@ -7774,13 +7780,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7794,10 +7800,10 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>23</v>
@@ -7814,13 +7820,13 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7834,33 +7840,33 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>561</v>
+        <v>84</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B263" s="1" t="s">
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F263" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="E263" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F263" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7874,13 +7880,13 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7894,13 +7900,13 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7914,13 +7920,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7934,10 +7940,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -7954,33 +7960,33 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>574</v>
+        <v>550</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="B269" s="1" t="s">
+      <c r="C269" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="C269" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>574</v>
-      </c>
       <c r="E269" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7994,10 +8000,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>84</v>
@@ -8014,10 +8020,10 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>84</v>
@@ -8034,10 +8040,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>84</v>
@@ -8054,33 +8060,33 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>585</v>
+        <v>84</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="B274" s="1" t="s">
+      <c r="C274" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F274" s="1" t="s">
         <v>587</v>
-      </c>
-      <c r="C274" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D274" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="E274" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F274" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -8094,13 +8100,13 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -8114,30 +8120,30 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>12</v>
@@ -8145,19 +8151,19 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="B278" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D278" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="C278" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>592</v>
-      </c>
       <c r="E278" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>12</v>
@@ -8174,10 +8180,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>12</v>
@@ -8194,13 +8200,13 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -8214,10 +8220,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8234,10 +8240,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8254,13 +8260,13 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8274,33 +8280,33 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>608</v>
+        <v>12</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D285" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="B285" s="1" t="s">
+      <c r="E285" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F285" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="C285" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E285" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F285" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8314,10 +8320,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>12</v>
@@ -8334,10 +8340,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>12</v>
@@ -8354,10 +8360,10 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>12</v>
@@ -8374,13 +8380,13 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8394,13 +8400,13 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8414,10 +8420,10 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>12</v>
@@ -8434,10 +8440,10 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>12</v>
@@ -8454,10 +8460,10 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>12</v>
@@ -8474,13 +8480,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8494,13 +8500,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8514,13 +8520,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8534,13 +8540,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8554,10 +8560,10 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>637</v>
+        <v>609</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>12</v>
@@ -8565,22 +8571,22 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="B299" s="1" t="s">
+      <c r="C299" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D299" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="C299" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="E299" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8594,13 +8600,13 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8614,10 +8620,10 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>12</v>
@@ -8634,10 +8640,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>12</v>
@@ -8654,10 +8660,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>12</v>
@@ -8674,10 +8680,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>12</v>
@@ -8694,13 +8700,13 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -8714,10 +8720,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>654</v>
+        <v>639</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8725,19 +8731,19 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="B307" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="B307" s="1" t="s">
+      <c r="C307" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D307" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="C307" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>654</v>
-      </c>
       <c r="E307" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8754,10 +8760,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8774,13 +8780,13 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -8794,10 +8800,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>12</v>
@@ -8814,10 +8820,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>12</v>
@@ -8834,10 +8840,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>12</v>
@@ -8854,10 +8860,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>12</v>
@@ -8874,10 +8880,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>12</v>
@@ -8894,10 +8900,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>673</v>
+        <v>656</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>12</v>
@@ -8905,19 +8911,19 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B316" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="B316" s="1" t="s">
+      <c r="C316" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D316" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="C316" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>673</v>
-      </c>
       <c r="E316" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>12</v>
@@ -8934,13 +8940,13 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -8954,13 +8960,13 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>443</v>
+        <v>84</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -8974,13 +8980,13 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>12</v>
+        <v>445</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -8994,50 +9000,50 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>684</v>
+        <v>12</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B321" s="1" t="s">
+      <c r="C321" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="E321" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F321" s="1" t="s">
         <v>686</v>
-      </c>
-      <c r="C321" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="E321" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F321" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="B322" s="1" t="s">
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="C322" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>687</v>
-      </c>
       <c r="E322" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>12</v>
@@ -9054,13 +9060,13 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -9074,13 +9080,13 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -9094,13 +9100,13 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -9114,13 +9120,13 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -9134,30 +9140,30 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="B328" s="1" t="s">
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>700</v>
-      </c>
       <c r="E328" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>84</v>
@@ -9174,10 +9180,10 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>84</v>
@@ -9194,10 +9200,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>84</v>
@@ -9214,10 +9220,10 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>84</v>
@@ -9234,10 +9240,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>84</v>
@@ -9245,19 +9251,19 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B333" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="B333" s="1" t="s">
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="C333" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>711</v>
-      </c>
       <c r="E333" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>84</v>
@@ -9274,10 +9280,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>84</v>
@@ -9294,10 +9300,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>84</v>
@@ -9314,13 +9320,13 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -9334,33 +9340,33 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>723</v>
+        <v>12</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="B338" s="1" t="s">
+      <c r="E338" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F338" s="1" t="s">
         <v>725</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="E338" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F338" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -9374,13 +9380,13 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9394,12 +9400,32 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E340" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F340" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E341" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F340" s="1" t="s">
+      <c r="F341" s="1" t="s">
         <v>84</v>
       </c>
     </row>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="731">
   <si>
     <t/>
   </si>
@@ -1379,9 +1379,6 @@
   </si>
   <si>
     <t>SUN KARA TPK 110ML</t>
-  </si>
-  <si>
-    <t>,(E-2B)</t>
   </si>
   <si>
     <t>10036806</t>
@@ -6866,15 +6863,15 @@
         <v>34</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>456</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>458</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
@@ -6891,10 +6888,10 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
@@ -6911,10 +6908,10 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>462</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
@@ -6931,10 +6928,10 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
@@ -6951,10 +6948,10 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
@@ -6971,10 +6968,10 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>468</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
@@ -6991,76 +6988,76 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B220" s="1" t="s">
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>18</v>
@@ -7071,16 +7068,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>18</v>
@@ -7091,36 +7088,36 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>482</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>8</v>
@@ -7131,16 +7128,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>486</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>8</v>
@@ -7151,16 +7148,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>8</v>
@@ -7171,16 +7168,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>26</v>
@@ -7191,16 +7188,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>26</v>
@@ -7211,16 +7208,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>26</v>
@@ -7231,16 +7228,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>29</v>
@@ -7251,16 +7248,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>29</v>
@@ -7271,16 +7268,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>29</v>
@@ -7291,16 +7288,16 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>11</v>
@@ -7311,16 +7308,16 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>504</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>11</v>
@@ -7331,16 +7328,16 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>506</v>
-      </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>11</v>
@@ -7351,16 +7348,16 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>508</v>
-      </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>34</v>
@@ -7371,16 +7368,16 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="B239" s="1" t="s">
-        <v>510</v>
-      </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>34</v>
@@ -7391,16 +7388,16 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>512</v>
-      </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>34</v>
@@ -7411,16 +7408,16 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>15</v>
@@ -7431,16 +7428,16 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B242" s="1" t="s">
+      <c r="C242" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>517</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>4</v>
@@ -7451,16 +7448,16 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B243" s="1" t="s">
-        <v>519</v>
-      </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>18</v>
@@ -7471,16 +7468,16 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B244" s="1" t="s">
-        <v>521</v>
-      </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>8</v>
@@ -7491,16 +7488,16 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>523</v>
-      </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>26</v>
@@ -7511,16 +7508,16 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>525</v>
-      </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>29</v>
@@ -7531,16 +7528,16 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>527</v>
-      </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>11</v>
@@ -7551,16 +7548,16 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="B248" s="1" t="s">
+      <c r="C248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="C248" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>4</v>
@@ -7571,16 +7568,16 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>18</v>
@@ -7591,16 +7588,16 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B250" s="1" t="s">
-        <v>534</v>
-      </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>8</v>
@@ -7611,16 +7608,16 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>26</v>
@@ -7631,16 +7628,16 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>29</v>
@@ -7651,16 +7648,16 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>11</v>
@@ -7671,16 +7668,16 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="B254" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>34</v>
@@ -7691,36 +7688,36 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>547</v>
-      </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>94</v>
@@ -7731,16 +7728,16 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B257" s="1" t="s">
+      <c r="C257" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="C257" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>550</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>4</v>
@@ -7751,16 +7748,16 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B258" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>552</v>
-      </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>18</v>
@@ -7771,16 +7768,16 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>554</v>
-      </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>8</v>
@@ -7791,16 +7788,16 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>556</v>
-      </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>26</v>
@@ -7811,16 +7808,16 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>558</v>
-      </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>29</v>
@@ -7831,16 +7828,16 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>560</v>
-      </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>11</v>
@@ -7851,36 +7848,36 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>562</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>94</v>
@@ -7891,16 +7888,16 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>97</v>
@@ -7911,16 +7908,16 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="B266" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>100</v>
@@ -7931,16 +7928,16 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>173</v>
@@ -7951,16 +7948,16 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>573</v>
-      </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>176</v>
@@ -7971,16 +7968,16 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B269" s="1" t="s">
+      <c r="C269" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>575</v>
-      </c>
-      <c r="C269" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>576</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>4</v>
@@ -7991,16 +7988,16 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>18</v>
@@ -8011,16 +8008,16 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>8</v>
@@ -8031,16 +8028,16 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>26</v>
@@ -8051,16 +8048,16 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B273" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>29</v>
@@ -8071,36 +8068,36 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B274" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="B275" s="1" t="s">
-        <v>589</v>
-      </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>15</v>
@@ -8111,16 +8108,16 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B276" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="B276" s="1" t="s">
-        <v>591</v>
-      </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>94</v>
@@ -8131,16 +8128,16 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B277" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="B277" s="1" t="s">
+      <c r="C277" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D277" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="C277" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>594</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>4</v>
@@ -8151,16 +8148,16 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B278" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B278" s="1" t="s">
-        <v>575</v>
-      </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>18</v>
@@ -8171,16 +8168,16 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B279" s="1" t="s">
-        <v>596</v>
-      </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>8</v>
@@ -8191,16 +8188,16 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="B280" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>26</v>
@@ -8211,16 +8208,16 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>29</v>
@@ -8231,16 +8228,16 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>11</v>
@@ -8251,16 +8248,16 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="B283" s="1" t="s">
-        <v>604</v>
-      </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>34</v>
@@ -8271,16 +8268,16 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="B284" s="1" t="s">
-        <v>606</v>
-      </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>15</v>
@@ -8291,36 +8288,36 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B285" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="B285" s="1" t="s">
+      <c r="C285" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D285" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="C285" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>609</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B286" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B286" s="1" t="s">
-        <v>612</v>
-      </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>18</v>
@@ -8331,16 +8328,16 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>614</v>
-      </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>8</v>
@@ -8351,16 +8348,16 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="B288" s="1" t="s">
-        <v>616</v>
-      </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>26</v>
@@ -8371,16 +8368,16 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="B289" s="1" t="s">
-        <v>618</v>
-      </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>29</v>
@@ -8391,16 +8388,16 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B290" s="1" t="s">
-        <v>620</v>
-      </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>11</v>
@@ -8411,16 +8408,16 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B291" s="1" t="s">
-        <v>622</v>
-      </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>34</v>
@@ -8431,16 +8428,16 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>15</v>
@@ -8451,16 +8448,16 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="B293" s="1" t="s">
-        <v>626</v>
-      </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>94</v>
@@ -8471,16 +8468,16 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>97</v>
@@ -8491,16 +8488,16 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B295" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="B295" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>100</v>
@@ -8511,16 +8508,16 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B296" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="B296" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>173</v>
@@ -8531,16 +8528,16 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>634</v>
-      </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>176</v>
@@ -8551,16 +8548,16 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="B298" s="1" t="s">
-        <v>636</v>
-      </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>225</v>
@@ -8571,16 +8568,16 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="B299" s="1" t="s">
+      <c r="C299" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D299" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>639</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>4</v>
@@ -8591,16 +8588,16 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>641</v>
-      </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>18</v>
@@ -8611,16 +8608,16 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>8</v>
@@ -8631,16 +8628,16 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>645</v>
-      </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>26</v>
@@ -8651,16 +8648,16 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B303" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B303" s="1" t="s">
-        <v>647</v>
-      </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>29</v>
@@ -8671,16 +8668,16 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B304" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B304" s="1" t="s">
-        <v>649</v>
-      </c>
       <c r="C304" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>34</v>
@@ -8691,16 +8688,16 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B305" s="1" t="s">
-        <v>651</v>
-      </c>
       <c r="C305" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>15</v>
@@ -8711,16 +8708,16 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B306" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="B306" s="1" t="s">
-        <v>653</v>
-      </c>
       <c r="C306" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>94</v>
@@ -8731,16 +8728,16 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B307" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="B307" s="1" t="s">
+      <c r="C307" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D307" s="1" t="s">
         <v>655</v>
-      </c>
-      <c r="C307" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>656</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>4</v>
@@ -8751,16 +8748,16 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B308" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="B308" s="1" t="s">
-        <v>658</v>
-      </c>
       <c r="C308" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>18</v>
@@ -8771,16 +8768,16 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B309" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="B309" s="1" t="s">
-        <v>660</v>
-      </c>
       <c r="C309" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>8</v>
@@ -8791,16 +8788,16 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="B310" s="1" t="s">
-        <v>662</v>
-      </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>26</v>
@@ -8811,16 +8808,16 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>664</v>
-      </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>29</v>
@@ -8831,16 +8828,16 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>666</v>
-      </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>11</v>
@@ -8851,16 +8848,16 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B313" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B313" s="1" t="s">
-        <v>668</v>
-      </c>
       <c r="C313" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>34</v>
@@ -8871,16 +8868,16 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B314" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="B314" s="1" t="s">
-        <v>670</v>
-      </c>
       <c r="C314" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>15</v>
@@ -8891,16 +8888,16 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B315" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="B315" s="1" t="s">
-        <v>672</v>
-      </c>
       <c r="C315" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>94</v>
@@ -8911,16 +8908,16 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B316" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="B316" s="1" t="s">
+      <c r="C316" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D316" s="1" t="s">
         <v>674</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>675</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>4</v>
@@ -8931,16 +8928,16 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="B317" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="B317" s="1" t="s">
-        <v>677</v>
-      </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>18</v>
@@ -8951,16 +8948,16 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="B318" s="1" t="s">
-        <v>679</v>
-      </c>
       <c r="C318" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>8</v>
@@ -8971,16 +8968,16 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>681</v>
-      </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>26</v>
@@ -8991,16 +8988,16 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>683</v>
-      </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>29</v>
@@ -9011,36 +9008,36 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="B321" s="1" t="s">
-        <v>685</v>
-      </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="B322" s="1" t="s">
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>688</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>689</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>4</v>
@@ -9051,16 +9048,16 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B323" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="B323" s="1" t="s">
-        <v>691</v>
-      </c>
       <c r="C323" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>18</v>
@@ -9071,16 +9068,16 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="B324" s="1" t="s">
-        <v>693</v>
-      </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>8</v>
@@ -9091,16 +9088,16 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B325" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="B325" s="1" t="s">
-        <v>695</v>
-      </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>26</v>
@@ -9111,16 +9108,16 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B326" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="B326" s="1" t="s">
-        <v>697</v>
-      </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>29</v>
@@ -9131,16 +9128,16 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B327" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="B327" s="1" t="s">
-        <v>699</v>
-      </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>11</v>
@@ -9151,16 +9148,16 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B328" s="1" t="s">
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>701</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>702</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>4</v>
@@ -9171,16 +9168,16 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>704</v>
-      </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>18</v>
@@ -9191,16 +9188,16 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B330" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="B330" s="1" t="s">
-        <v>706</v>
-      </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>8</v>
@@ -9211,16 +9208,16 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B331" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="B331" s="1" t="s">
-        <v>708</v>
-      </c>
       <c r="C331" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>26</v>
@@ -9231,16 +9228,16 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B332" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="B332" s="1" t="s">
-        <v>710</v>
-      </c>
       <c r="C332" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>29</v>
@@ -9251,16 +9248,16 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B333" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="B333" s="1" t="s">
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>713</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>4</v>
@@ -9271,16 +9268,16 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B334" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="B334" s="1" t="s">
-        <v>715</v>
-      </c>
       <c r="C334" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>18</v>
@@ -9291,16 +9288,16 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B335" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="B335" s="1" t="s">
-        <v>717</v>
-      </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>8</v>
@@ -9311,16 +9308,16 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="B336" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="B336" s="1" t="s">
-        <v>719</v>
-      </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>26</v>
@@ -9331,16 +9328,16 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B337" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="B337" s="1" t="s">
-        <v>721</v>
-      </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>29</v>
@@ -9351,36 +9348,36 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="B338" s="1" t="s">
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>723</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>724</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B339" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="B339" s="1" t="s">
-        <v>727</v>
-      </c>
       <c r="C339" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>18</v>
@@ -9391,16 +9388,16 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B340" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="B340" s="1" t="s">
-        <v>729</v>
-      </c>
       <c r="C340" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>8</v>
@@ -9411,16 +9408,16 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B341" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="B341" s="1" t="s">
-        <v>731</v>
-      </c>
       <c r="C341" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>26</v>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="738">
   <si>
     <t/>
   </si>
@@ -130,6 +130,21 @@
     <t>KOBE TPG TEMPE KR200</t>
   </si>
   <si>
+    <t>20137035</t>
+  </si>
+  <si>
+    <t>LARISST TPG BMB 200G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20137045</t>
+  </si>
+  <si>
+    <t>LARIST TP BMB RTI200</t>
+  </si>
+  <si>
     <t>20022639</t>
   </si>
   <si>
@@ -142,15 +157,6 @@
     <t>KOBE TEPUNG ROTI 200</t>
   </si>
   <si>
-    <t>20137045</t>
-  </si>
-  <si>
-    <t>LARIST TP BMB RTI200</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
     <t>20128248</t>
   </si>
   <si>
@@ -187,10 +193,40 @@
     <t>MAMASUKA TPG BKW 225</t>
   </si>
   <si>
-    <t>20137035</t>
-  </si>
-  <si>
-    <t>LARISST TPG BMB 200G</t>
+    <t>20065236</t>
+  </si>
+  <si>
+    <t>SASA TPNG BKWAN 225G</t>
+  </si>
+  <si>
+    <t>20123095</t>
+  </si>
+  <si>
+    <t>MMSUKA TP.KTUCKY 210</t>
+  </si>
+  <si>
+    <t>20052439</t>
+  </si>
+  <si>
+    <t>KOBE TP KNTKY SC 200</t>
+  </si>
+  <si>
+    <t>20037353</t>
+  </si>
+  <si>
+    <t>SAJIKU TPG G.CRSP200</t>
+  </si>
+  <si>
+    <t>20041881</t>
+  </si>
+  <si>
+    <t>SASA T.BMB KENTKY200</t>
+  </si>
+  <si>
+    <t>20128246</t>
+  </si>
+  <si>
+    <t>INDF TP BMB RC AK210</t>
   </si>
   <si>
     <t>20128245</t>
@@ -199,48 +235,60 @@
     <t>RACIK TB BAKWAN 210G</t>
   </si>
   <si>
-    <t>20128246</t>
-  </si>
-  <si>
-    <t>INDF TP BMB RC AK210</t>
-  </si>
-  <si>
-    <t>20123095</t>
-  </si>
-  <si>
-    <t>MMSUKA TP.KTUCKY 210</t>
-  </si>
-  <si>
-    <t>20052439</t>
-  </si>
-  <si>
-    <t>KOBE TP KNTKY SC 200</t>
-  </si>
-  <si>
-    <t>20037353</t>
-  </si>
-  <si>
-    <t>SAJIKU TPG G.CRSP200</t>
-  </si>
-  <si>
-    <t>20041881</t>
-  </si>
-  <si>
-    <t>SASA T.BMB KENTKY200</t>
-  </si>
-  <si>
-    <t>20065236</t>
-  </si>
-  <si>
-    <t>SASA TPNG BKWAN 225G</t>
-  </si>
-  <si>
     <t>20025701</t>
   </si>
   <si>
     <t>DOLPIN GARAM BTL 200</t>
   </si>
   <si>
+    <t>20093266</t>
+  </si>
+  <si>
+    <t>LARIST GRM YODIUM500</t>
+  </si>
+  <si>
+    <t>20026676</t>
+  </si>
+  <si>
+    <t>INDOMARET GARAM 500G</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10006168</t>
+  </si>
+  <si>
+    <t>REFINA GARAM 500GR</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20139346</t>
+  </si>
+  <si>
+    <t>LARISST GRM KASAR500</t>
+  </si>
+  <si>
+    <t>20036713</t>
+  </si>
+  <si>
+    <t>IDM CUKA BTL150ML</t>
+  </si>
+  <si>
+    <t>20005008</t>
+  </si>
+  <si>
+    <t>ABC TERASI UDG 20'S</t>
+  </si>
+  <si>
+    <t>20025757</t>
+  </si>
+  <si>
+    <t>PRONAS NS GRG SP 110</t>
+  </si>
+  <si>
     <t>20140350</t>
   </si>
   <si>
@@ -265,267 +313,219 @@
     <t>SASA BUMBU MSK 250GR</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
     <t>10003697</t>
   </si>
   <si>
     <t>AJINOMOTO BB.MSK 250</t>
   </si>
   <si>
-    <t>20026676</t>
-  </si>
-  <si>
-    <t>INDOMARET GARAM 500G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20093266</t>
-  </si>
-  <si>
-    <t>LARIST GRM YODIUM500</t>
-  </si>
-  <si>
-    <t>10006168</t>
-  </si>
-  <si>
-    <t>REFINA GARAM 500GR</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
-    <t>20139346</t>
-  </si>
-  <si>
-    <t>LARISST GRM KASAR500</t>
+    <t>20134507</t>
+  </si>
+  <si>
+    <t>TUDUNG BMB NS UDUK27</t>
+  </si>
+  <si>
+    <t>20134777</t>
+  </si>
+  <si>
+    <t>SASA KARI JPG ORI 40</t>
+  </si>
+  <si>
+    <t>20136577</t>
+  </si>
+  <si>
+    <t>TUDUNG BMB PRLDK 50G</t>
+  </si>
+  <si>
+    <t>20136743</t>
+  </si>
+  <si>
+    <t>TDUNG BMB NP.RDNG 27</t>
+  </si>
+  <si>
+    <t>20134778</t>
+  </si>
+  <si>
+    <t>SASA KARI JPG PDS 40</t>
+  </si>
+  <si>
+    <t>20137258</t>
+  </si>
+  <si>
+    <t>RASA/M GULAI AYAM40G</t>
+  </si>
+  <si>
+    <t>20138072</t>
+  </si>
+  <si>
+    <t>RASA/M OPOR AYAM 40G</t>
+  </si>
+  <si>
+    <t>20138843</t>
+  </si>
+  <si>
+    <t>R/MASA SYR LODEH 25G</t>
+  </si>
+  <si>
+    <t>20025563</t>
+  </si>
+  <si>
+    <t>SASA BMB LUMUR AYM26</t>
+  </si>
+  <si>
+    <t>20057290</t>
+  </si>
+  <si>
+    <t>SASA BU AYAM KNG 25G</t>
+  </si>
+  <si>
+    <t>20059859</t>
+  </si>
+  <si>
+    <t>KOBE BMB N/GRG PDS20</t>
+  </si>
+  <si>
+    <t>20136397</t>
+  </si>
+  <si>
+    <t>KB BMB AYM LNGKS 80G</t>
+  </si>
+  <si>
+    <t>10007775</t>
+  </si>
+  <si>
+    <t>A/SAJIKU NASI G.AY20</t>
+  </si>
+  <si>
+    <t>10013821</t>
+  </si>
+  <si>
+    <t>A/SAJIKU NASI G.PD20</t>
+  </si>
+  <si>
+    <t>10013823</t>
+  </si>
+  <si>
+    <t>A/SAJIKU BB.AYM GR24</t>
+  </si>
+  <si>
+    <t>20103449</t>
+  </si>
+  <si>
+    <t>SAJIKU NSI GRG SPL20</t>
+  </si>
+  <si>
+    <t>10035898</t>
+  </si>
+  <si>
+    <t>A/MASAKO AYAM 100GR</t>
+  </si>
+  <si>
+    <t>20038548</t>
+  </si>
+  <si>
+    <t>MASAKO SAPI 250GR</t>
+  </si>
+  <si>
+    <t>20038549</t>
+  </si>
+  <si>
+    <t>A/MASAKO AYAM 250GR</t>
+  </si>
+  <si>
+    <t>20098663</t>
+  </si>
+  <si>
+    <t>TOTOLE KLD JMUR 40G</t>
+  </si>
+  <si>
+    <t>10035899</t>
+  </si>
+  <si>
+    <t>A/MASAKO SAPI 100GR</t>
+  </si>
+  <si>
+    <t>20135316</t>
+  </si>
+  <si>
+    <t>LARISST BMB JMR 40G</t>
+  </si>
+  <si>
+    <t>20104719</t>
+  </si>
+  <si>
+    <t>TOTOLE KLD JMUR 80G</t>
+  </si>
+  <si>
+    <t>10006884</t>
+  </si>
+  <si>
+    <t>ABC MINYAK WIJEN.195</t>
+  </si>
+  <si>
+    <t>20031771</t>
+  </si>
+  <si>
+    <t>LKK PURE SSME OIL115</t>
+  </si>
+  <si>
+    <t>20085784</t>
+  </si>
+  <si>
+    <t>LKK OYSTER SAUCE 145</t>
+  </si>
+  <si>
+    <t>10036703</t>
+  </si>
+  <si>
+    <t>INDOFOOD KCP ASIN140</t>
+  </si>
+  <si>
+    <t>10000324</t>
+  </si>
+  <si>
+    <t>ABC KECAP ASIN 131ML</t>
+  </si>
+  <si>
+    <t>20009966</t>
+  </si>
+  <si>
+    <t>SAORI SAUS TIRAM 133</t>
+  </si>
+  <si>
+    <t>20009973</t>
+  </si>
+  <si>
+    <t>SAORI SAUS TERIYK135</t>
+  </si>
+  <si>
+    <t>20103453</t>
+  </si>
+  <si>
+    <t>SAORI SAUS LD HTM133</t>
+  </si>
+  <si>
+    <t>20044599</t>
+  </si>
+  <si>
+    <t>SAORI SAUS TIRAM 270</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>20036713</t>
-  </si>
-  <si>
-    <t>IDM CUKA BTL150ML</t>
+    <t>20038236</t>
+  </si>
+  <si>
+    <t>ABC SAUS TIRAM 135</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>20005008</t>
-  </si>
-  <si>
-    <t>ABC TERASI UDG 20'S</t>
-  </si>
-  <si>
-    <t>20025757</t>
-  </si>
-  <si>
-    <t>PRONAS NS GRG SP 110</t>
-  </si>
-  <si>
-    <t>20134507</t>
-  </si>
-  <si>
-    <t>TUDUNG BMB NS UDUK27</t>
-  </si>
-  <si>
-    <t>20134777</t>
-  </si>
-  <si>
-    <t>SASA KARI JPG ORI 40</t>
-  </si>
-  <si>
-    <t>20136577</t>
-  </si>
-  <si>
-    <t>TUDUNG BMB PRLDK 50G</t>
-  </si>
-  <si>
-    <t>20136743</t>
-  </si>
-  <si>
-    <t>TDUNG BMB NP.RDNG 27</t>
-  </si>
-  <si>
-    <t>20134778</t>
-  </si>
-  <si>
-    <t>SASA KARI JPG PDS 40</t>
-  </si>
-  <si>
-    <t>20137258</t>
-  </si>
-  <si>
-    <t>RASA/M GULAI AYAM40G</t>
-  </si>
-  <si>
-    <t>20138072</t>
-  </si>
-  <si>
-    <t>RASA/M OPOR AYAM 40G</t>
-  </si>
-  <si>
-    <t>20138843</t>
-  </si>
-  <si>
-    <t>R/MASA SYR LODEH 25G</t>
-  </si>
-  <si>
-    <t>20025563</t>
-  </si>
-  <si>
-    <t>SASA BMB LUMUR AYM26</t>
-  </si>
-  <si>
-    <t>20057290</t>
-  </si>
-  <si>
-    <t>SASA BU AYAM KNG 25G</t>
-  </si>
-  <si>
-    <t>20059859</t>
-  </si>
-  <si>
-    <t>KOBE BMB N/GRG PDS20</t>
-  </si>
-  <si>
-    <t>20136397</t>
-  </si>
-  <si>
-    <t>KB BMB AYM LNGKS 80G</t>
-  </si>
-  <si>
-    <t>10007775</t>
-  </si>
-  <si>
-    <t>A/SAJIKU NASI G.AY20</t>
-  </si>
-  <si>
-    <t>10013821</t>
-  </si>
-  <si>
-    <t>A/SAJIKU NASI G.PD20</t>
-  </si>
-  <si>
-    <t>10013823</t>
-  </si>
-  <si>
-    <t>A/SAJIKU BB.AYM GR24</t>
-  </si>
-  <si>
-    <t>20103449</t>
-  </si>
-  <si>
-    <t>SAJIKU NSI GRG SPL20</t>
-  </si>
-  <si>
-    <t>10035898</t>
-  </si>
-  <si>
-    <t>A/MASAKO AYAM 100GR</t>
-  </si>
-  <si>
-    <t>20038548</t>
-  </si>
-  <si>
-    <t>MASAKO SAPI 250GR</t>
-  </si>
-  <si>
-    <t>20038549</t>
-  </si>
-  <si>
-    <t>A/MASAKO AYAM 250GR</t>
-  </si>
-  <si>
-    <t>20098663</t>
-  </si>
-  <si>
-    <t>TOTOLE KLD JMUR 40G</t>
-  </si>
-  <si>
-    <t>10035899</t>
-  </si>
-  <si>
-    <t>A/MASAKO SAPI 100GR</t>
-  </si>
-  <si>
-    <t>20135316</t>
-  </si>
-  <si>
-    <t>LARISST BMB JMR 40G</t>
-  </si>
-  <si>
-    <t>20104719</t>
-  </si>
-  <si>
-    <t>TOTOLE KLD JMUR 80G</t>
-  </si>
-  <si>
-    <t>10006884</t>
-  </si>
-  <si>
-    <t>ABC MINYAK WIJEN.195</t>
-  </si>
-  <si>
-    <t>20031771</t>
-  </si>
-  <si>
-    <t>LKK PURE SSME OIL115</t>
-  </si>
-  <si>
-    <t>20085784</t>
-  </si>
-  <si>
-    <t>LKK OYSTER SAUCE 145</t>
-  </si>
-  <si>
-    <t>10036703</t>
-  </si>
-  <si>
-    <t>INDOFOOD KCP ASIN140</t>
-  </si>
-  <si>
-    <t>10000324</t>
-  </si>
-  <si>
-    <t>ABC KECAP ASIN 131ML</t>
-  </si>
-  <si>
-    <t>20009966</t>
-  </si>
-  <si>
-    <t>SAORI SAUS TIRAM 133</t>
-  </si>
-  <si>
-    <t>20009973</t>
-  </si>
-  <si>
-    <t>SAORI SAUS TERIYK135</t>
-  </si>
-  <si>
-    <t>20103453</t>
-  </si>
-  <si>
-    <t>SAORI SAUS LD HTM133</t>
-  </si>
-  <si>
-    <t>20044599</t>
-  </si>
-  <si>
-    <t>SAORI SAUS TIRAM 270</t>
-  </si>
-  <si>
-    <t>20038236</t>
-  </si>
-  <si>
-    <t>ABC SAUS TIRAM 135</t>
-  </si>
-  <si>
     <t>20071507</t>
   </si>
   <si>
@@ -778,18 +778,24 @@
     <t>ABC SMAL TERASI 10'S</t>
   </si>
   <si>
+    <t>20142587</t>
+  </si>
+  <si>
+    <t>INDF SMB COBEK TER5S</t>
+  </si>
+  <si>
+    <t>20142586</t>
+  </si>
+  <si>
+    <t>INDF SMB CBK LIMAU5S</t>
+  </si>
+  <si>
     <t>20054028</t>
   </si>
   <si>
     <t>INDO/F SMBL BLDO 200</t>
   </si>
   <si>
-    <t>20142586</t>
-  </si>
-  <si>
-    <t>INDF SMB CBK LIMAU5S</t>
-  </si>
-  <si>
     <t>20048582</t>
   </si>
   <si>
@@ -826,12 +832,6 @@
     <t>KOBE BMB RNDANG 3X20</t>
   </si>
   <si>
-    <t>20142587</t>
-  </si>
-  <si>
-    <t>INDF SMB COBEK TER5S</t>
-  </si>
-  <si>
     <t>20128243</t>
   </si>
   <si>
@@ -1081,16 +1081,73 @@
     <t>ROYCO OPOR AYAM 45G</t>
   </si>
   <si>
+    <t>20142448</t>
+  </si>
+  <si>
+    <t>ROYCO KALDU AYAM 210</t>
+  </si>
+  <si>
     <t>20142447</t>
   </si>
   <si>
     <t>ROYCO KALDU SAPI 210</t>
   </si>
   <si>
-    <t>20142448</t>
-  </si>
-  <si>
-    <t>ROYCO KALDU AYAM 210</t>
+    <t>20096440</t>
+  </si>
+  <si>
+    <t>ROSE/B GULA HLS 500</t>
+  </si>
+  <si>
+    <t>20141513</t>
+  </si>
+  <si>
+    <t>IDM KCG TNH KPS 250G</t>
+  </si>
+  <si>
+    <t>20061785</t>
+  </si>
+  <si>
+    <t>IDM POP CORN PCK200G</t>
+  </si>
+  <si>
+    <t>20000412</t>
+  </si>
+  <si>
+    <t>IDM KACANG HIJAU 500</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10000509</t>
+  </si>
+  <si>
+    <t>ROSE TEPUNG BERAS500</t>
+  </si>
+  <si>
+    <t>20138253</t>
+  </si>
+  <si>
+    <t>SANIA TPG BERAS 500G</t>
+  </si>
+  <si>
+    <t>20038013</t>
+  </si>
+  <si>
+    <t>P/TANI TAPIOKA 500G</t>
+  </si>
+  <si>
+    <t>10008819</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 685G</t>
+  </si>
+  <si>
+    <t>20117107</t>
+  </si>
+  <si>
+    <t>BANGO KECAP MNS 920G</t>
   </si>
   <si>
     <t>10022534</t>
@@ -1114,13 +1171,13 @@
     <t>20123088</t>
   </si>
   <si>
-    <t>SEDAAP KCP MNS 720ML</t>
+    <t>SEDAAP KCP MS 720 ML</t>
   </si>
   <si>
     <t>20104077</t>
   </si>
   <si>
-    <t>SEDAP KCP SPCL 725G</t>
+    <t>SEDAP KCP SPCL 725 G</t>
   </si>
   <si>
     <t>20019249</t>
@@ -1129,51 +1186,39 @@
     <t>SEDAAP KECAP PCH700G</t>
   </si>
   <si>
+    <t>20134927</t>
+  </si>
+  <si>
+    <t>SEDAP KCP MNS 270G</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20068238</t>
+  </si>
+  <si>
+    <t>SEDAAP KECAP PCH 250</t>
+  </si>
+  <si>
+    <t>20064956</t>
+  </si>
+  <si>
+    <t>INDOF KCP MNS RF280G</t>
+  </si>
+  <si>
     <t>10016646</t>
   </si>
   <si>
     <t>INDO/F KECAP MN.R725</t>
   </si>
   <si>
-    <t>10008819</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 685G</t>
-  </si>
-  <si>
-    <t>20117107</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 920G</t>
-  </si>
-  <si>
-    <t>20134927</t>
-  </si>
-  <si>
-    <t>SEDAP KCP MNS 270G</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20064956</t>
-  </si>
-  <si>
-    <t>INDOF KCP MNS RF280G</t>
-  </si>
-  <si>
     <t>20138101</t>
   </si>
   <si>
     <t>BANGO KCP MNS 380G</t>
   </si>
   <si>
-    <t>20068238</t>
-  </si>
-  <si>
-    <t>SEDAAP KECAP PCH 250</t>
-  </si>
-  <si>
     <t>10002983</t>
   </si>
   <si>
@@ -1555,45 +1600,39 @@
     <t>NUTRIJELL DRK.CHO 24</t>
   </si>
   <si>
+    <t>10005601</t>
+  </si>
+  <si>
+    <t>CAKRA KEMBAR TPG 1KG</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>10005599</t>
+  </si>
+  <si>
+    <t>SEGITIGA BIRU 1 KG</t>
+  </si>
+  <si>
+    <t>10005600</t>
+  </si>
+  <si>
+    <t>KUNCI BIRU TEPUNG 1K</t>
+  </si>
+  <si>
+    <t>20086392</t>
+  </si>
+  <si>
+    <t>SANIA TPNG TRGU 1KG</t>
+  </si>
+  <si>
     <t>20026090</t>
   </si>
   <si>
     <t>L/MRH TRIGU TRANS1KG</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>10005601</t>
-  </si>
-  <si>
-    <t>CAKRA KEMBAR TPG 1KG</t>
-  </si>
-  <si>
-    <t>10005599</t>
-  </si>
-  <si>
-    <t>SEGITIGA BIRU 1 KG</t>
-  </si>
-  <si>
-    <t>10005600</t>
-  </si>
-  <si>
-    <t>KUNCI BIRU TEPUNG 1K</t>
-  </si>
-  <si>
-    <t>20086392</t>
-  </si>
-  <si>
-    <t>SANIA TPNG TRGU 1KG</t>
-  </si>
-  <si>
-    <t>20138253</t>
-  </si>
-  <si>
-    <t>SANIA TPG BERAS 500G</t>
-  </si>
-  <si>
     <t>20014623</t>
   </si>
   <si>
@@ -1615,43 +1654,28 @@
     <t>ABC SARDINES TMT 425</t>
   </si>
   <si>
-    <t>20096440</t>
-  </si>
-  <si>
-    <t>ROSE/B GULA HLS 500</t>
-  </si>
-  <si>
-    <t>10000509</t>
-  </si>
-  <si>
-    <t>ROSE TEPUNG BERAS500</t>
-  </si>
-  <si>
-    <t>20038013</t>
-  </si>
-  <si>
-    <t>P/TANI TAPIOKA 500G</t>
-  </si>
-  <si>
-    <t>20061785</t>
-  </si>
-  <si>
-    <t>IDM POP CORN PCK200G</t>
-  </si>
-  <si>
-    <t>20000412</t>
-  </si>
-  <si>
-    <t>IDM KACANG HIJAU 500</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20141513</t>
-  </si>
-  <si>
-    <t>IDM KCG TNH KPS 250G</t>
+    <t>10005980</t>
+  </si>
+  <si>
+    <t>BOTAN SRDN PR TMT425</t>
+  </si>
+  <si>
+    <t>10000102</t>
+  </si>
+  <si>
+    <t>BOTAN MACKEREL 425G</t>
+  </si>
+  <si>
+    <t>10003682</t>
+  </si>
+  <si>
+    <t>MAYA SARDINE TMT 425</t>
+  </si>
+  <si>
+    <t>10036563</t>
+  </si>
+  <si>
+    <t>GAGA TMT&amp;CHILI 425GR</t>
   </si>
   <si>
     <t>10036569</t>
@@ -1720,16 +1744,70 @@
     <t>MAYA TN MYK KDL185G</t>
   </si>
   <si>
-    <t>10005980</t>
-  </si>
-  <si>
-    <t>BOTAN SRDN PR TMT425</t>
-  </si>
-  <si>
-    <t>10000102</t>
-  </si>
-  <si>
-    <t>BOTAN MACKEREL 425G</t>
+    <t>20029222</t>
+  </si>
+  <si>
+    <t>PRONAS CORNED BEEF50</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>10000135</t>
+  </si>
+  <si>
+    <t>PRONAS CORNED BF.198</t>
+  </si>
+  <si>
+    <t>10036553</t>
+  </si>
+  <si>
+    <t>PRONAS CORNED BF.340</t>
+  </si>
+  <si>
+    <t>20025825</t>
+  </si>
+  <si>
+    <t>PRONAS KORNETKU 200G</t>
+  </si>
+  <si>
+    <t>20025756</t>
+  </si>
+  <si>
+    <t>PRONAS KORNETKU 340G</t>
+  </si>
+  <si>
+    <t>RT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20143796</t>
+  </si>
+  <si>
+    <t>ETIRA TUNA RTE PDS75</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20143797</t>
+  </si>
+  <si>
+    <t>ETIRA TUNA RTE ORI75</t>
+  </si>
+  <si>
+    <t>20143798</t>
+  </si>
+  <si>
+    <t>DLT/FD TONGKOL 125</t>
+  </si>
+  <si>
+    <t>10000210</t>
+  </si>
+  <si>
+    <t>BLUE BAND CUP 230G</t>
+  </si>
+  <si>
+    <t>27</t>
   </si>
   <si>
     <t>20138100</t>
@@ -1738,63 +1816,6 @@
     <t>FVTA MRGN TUB 200G</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20029222</t>
-  </si>
-  <si>
-    <t>PRONAS CORNED BEEF50</t>
-  </si>
-  <si>
-    <t>10000135</t>
-  </si>
-  <si>
-    <t>PRONAS CORNED BF.198</t>
-  </si>
-  <si>
-    <t>10036553</t>
-  </si>
-  <si>
-    <t>PRONAS CORNED BF.340</t>
-  </si>
-  <si>
-    <t>20025825</t>
-  </si>
-  <si>
-    <t>PRONAS KORNETKU 200G</t>
-  </si>
-  <si>
-    <t>20025756</t>
-  </si>
-  <si>
-    <t>PRONAS KORNETKU 340G</t>
-  </si>
-  <si>
-    <t>RT,(E-5B)</t>
-  </si>
-  <si>
-    <t>10036563</t>
-  </si>
-  <si>
-    <t>GAGA TMT&amp;CHILI 425GR</t>
-  </si>
-  <si>
-    <t>10003682</t>
-  </si>
-  <si>
-    <t>MAYA SARDINE TMT 425</t>
-  </si>
-  <si>
-    <t>10000210</t>
-  </si>
-  <si>
-    <t>BLUE BAND CUP 230G</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
     <t>10005073</t>
   </si>
   <si>
@@ -2161,13 +2182,13 @@
     <t>20016512</t>
   </si>
   <si>
-    <t>SUNCO MNYK GORENG 2L</t>
+    <t>SUNCO MNYK GR 2 L</t>
   </si>
   <si>
     <t>10000442</t>
   </si>
   <si>
-    <t>FORTUNE MYK.GRG RF2L</t>
+    <t>FORTUNE MYK.GR R 2 L</t>
   </si>
   <si>
     <t>10012753</t>
@@ -2596,7 +2617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F341"/>
+  <dimension ref="A1:F343"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2903,15 +2924,15 @@
         <v>18</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -2923,15 +2944,15 @@
         <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -2943,7 +2964,7 @@
         <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2957,13 +2978,13 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2980,10 +3001,10 @@
         <v>26</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3000,7 +3021,7 @@
         <v>26</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>23</v>
@@ -3020,10 +3041,10 @@
         <v>26</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3040,10 +3061,10 @@
         <v>26</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3060,10 +3081,10 @@
         <v>26</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3080,10 +3101,10 @@
         <v>26</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -3097,13 +3118,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -3120,10 +3141,10 @@
         <v>29</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -3140,10 +3161,10 @@
         <v>29</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -3160,10 +3181,10 @@
         <v>29</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -3180,10 +3201,10 @@
         <v>29</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3200,10 +3221,10 @@
         <v>29</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3220,10 +3241,10 @@
         <v>29</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3263,7 +3284,7 @@
         <v>18</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3283,15 +3304,15 @@
         <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -3303,15 +3324,15 @@
         <v>26</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -3323,15 +3344,15 @@
         <v>29</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -3343,27 +3364,27 @@
         <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3377,13 +3398,13 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3397,61 +3418,61 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -3460,18 +3481,18 @@
         <v>34</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -3480,18 +3501,18 @@
         <v>34</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -3508,10 +3529,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -3528,10 +3549,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -3548,10 +3569,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -3568,10 +3589,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -3588,10 +3609,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -3608,10 +3629,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -3628,10 +3649,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -3648,10 +3669,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -3668,10 +3689,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -3688,10 +3709,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -3708,10 +3729,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -3728,10 +3749,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -3748,10 +3769,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -3768,10 +3789,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -3788,10 +3809,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -3808,10 +3829,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -3828,10 +3849,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -3848,10 +3869,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -3868,10 +3889,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -3888,10 +3909,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -3908,10 +3929,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -3923,15 +3944,15 @@
         <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -3948,16 +3969,16 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>4</v>
@@ -3968,16 +3989,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>18</v>
@@ -3988,16 +4009,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>8</v>
@@ -4008,16 +4029,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>26</v>
@@ -4028,16 +4049,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>11</v>
@@ -4048,16 +4069,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>34</v>
@@ -4068,16 +4089,16 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>15</v>
@@ -4088,19 +4109,19 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>12</v>
@@ -4108,19 +4129,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>12</v>
@@ -4128,19 +4149,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -4157,7 +4178,7 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>173</v>
@@ -4177,7 +4198,7 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>176</v>
@@ -4197,7 +4218,7 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>4</v>
@@ -4217,7 +4238,7 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>18</v>
@@ -4237,7 +4258,7 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>8</v>
@@ -4257,7 +4278,7 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>26</v>
@@ -4277,7 +4298,7 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>29</v>
@@ -4297,7 +4318,7 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>11</v>
@@ -4317,7 +4338,7 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>34</v>
@@ -4337,10 +4358,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -4357,10 +4378,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>23</v>
@@ -4377,10 +4398,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>23</v>
@@ -4397,7 +4418,7 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>173</v>
@@ -4417,7 +4438,7 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>18</v>
@@ -4437,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>8</v>
@@ -4457,7 +4478,7 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>26</v>
@@ -4477,7 +4498,7 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>29</v>
@@ -4497,7 +4518,7 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>11</v>
@@ -4517,7 +4538,7 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>34</v>
@@ -4537,7 +4558,7 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>15</v>
@@ -4557,10 +4578,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>23</v>
@@ -4577,10 +4598,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>23</v>
@@ -4597,10 +4618,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>12</v>
@@ -4617,7 +4638,7 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>173</v>
@@ -4637,7 +4658,7 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>176</v>
@@ -4657,7 +4678,7 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>225</v>
@@ -4677,7 +4698,7 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>228</v>
@@ -4697,7 +4718,7 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>231</v>
@@ -4717,7 +4738,7 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>234</v>
@@ -4900,7 +4921,7 @@
         <v>173</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -4943,7 +4964,7 @@
         <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4983,7 +5004,7 @@
         <v>26</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -5080,7 +5101,7 @@
         <v>176</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>12</v>
@@ -5100,7 +5121,7 @@
         <v>176</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>12</v>
@@ -5280,7 +5301,7 @@
         <v>225</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>23</v>
@@ -5300,10 +5321,10 @@
         <v>225</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -5323,7 +5344,7 @@
         <v>173</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -5343,7 +5364,7 @@
         <v>176</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5363,7 +5384,7 @@
         <v>225</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -5383,7 +5404,7 @@
         <v>228</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -5983,7 +6004,7 @@
         <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -6003,7 +6024,7 @@
         <v>18</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -6043,15 +6064,15 @@
         <v>26</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>12</v>
+        <v>368</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
@@ -6063,15 +6084,15 @@
         <v>29</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
@@ -6088,19 +6109,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>23</v>
@@ -6108,10 +6129,10 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
@@ -6120,7 +6141,7 @@
         <v>234</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>351</v>
@@ -6128,10 +6149,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
@@ -6140,7 +6161,7 @@
         <v>234</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>351</v>
@@ -6148,22 +6169,22 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>380</v>
+        <v>234</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6177,13 +6198,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>380</v>
+        <v>234</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6197,13 +6218,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>380</v>
+        <v>234</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6217,10 +6238,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>380</v>
+        <v>234</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>12</v>
@@ -6237,13 +6258,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>380</v>
+        <v>234</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6257,13 +6278,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>380</v>
+        <v>234</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>351</v>
+        <v>12</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6277,73 +6298,73 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="E185" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>351</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6357,13 +6378,13 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6377,13 +6398,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6397,13 +6418,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>5</v>
+        <v>351</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6417,10 +6438,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -6437,13 +6458,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>23</v>
+        <v>351</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6457,13 +6478,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>34</v>
+        <v>167</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6477,70 +6498,70 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="E195" s="1" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -6548,22 +6569,22 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6577,13 +6598,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6597,13 +6618,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6617,13 +6638,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6637,10 +6658,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>12</v>
@@ -6657,10 +6678,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>12</v>
@@ -6677,33 +6698,33 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>435</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="E205" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6717,13 +6738,13 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6737,13 +6758,13 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6757,170 +6778,170 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>445</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F211" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F211" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>455</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>34</v>
+        <v>167</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="E215" s="1" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>23</v>
+        <v>460</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -6928,19 +6949,19 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -6948,39 +6969,39 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>173</v>
+        <v>29</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>23</v>
@@ -6988,319 +7009,319 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>471</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>473</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>471</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>475</v>
-      </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>471</v>
+        <v>23</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>477</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>18</v>
+        <v>167</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>18</v>
+        <v>173</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>471</v>
+        <v>23</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>8</v>
+        <v>176</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B227" s="1" t="s">
+      <c r="C227" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D227" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="C227" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="E227" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>84</v>
+        <v>486</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F228" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D228" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="E228" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F228" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>5</v>
+        <v>486</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>5</v>
+        <v>486</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>5</v>
@@ -7308,19 +7329,19 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>5</v>
@@ -7328,19 +7349,19 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>5</v>
@@ -7348,19 +7369,19 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>5</v>
@@ -7368,19 +7389,19 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>5</v>
@@ -7388,19 +7409,19 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>5</v>
@@ -7408,19 +7429,19 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>5</v>
@@ -7428,22 +7449,22 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>516</v>
+        <v>485</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7457,10 +7478,10 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>516</v>
+        <v>485</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>5</v>
@@ -7477,10 +7498,10 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>516</v>
+        <v>485</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>5</v>
@@ -7497,10 +7518,10 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>516</v>
+        <v>485</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>5</v>
@@ -7517,13 +7538,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>516</v>
+        <v>485</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7537,13 +7558,13 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>516</v>
+        <v>485</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7557,10 +7578,10 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>529</v>
+        <v>485</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>5</v>
@@ -7568,19 +7589,19 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B249" s="1" t="s">
+      <c r="C249" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D249" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C249" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>529</v>
-      </c>
       <c r="E249" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>5</v>
@@ -7597,10 +7618,10 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>5</v>
@@ -7617,13 +7638,13 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7637,13 +7658,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7657,13 +7678,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7677,10 +7698,10 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>5</v>
@@ -7688,22 +7709,22 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D255" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C255" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D255" s="1" t="s">
-        <v>529</v>
-      </c>
       <c r="E255" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>544</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7717,13 +7738,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7737,50 +7758,50 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B258" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>551</v>
-      </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>5</v>
@@ -7788,42 +7809,42 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>555</v>
-      </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="B261" s="1" t="s">
+      <c r="C261" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D261" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="C261" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>549</v>
-      </c>
       <c r="E261" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7837,13 +7858,13 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -7857,30 +7878,30 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>562</v>
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>564</v>
-      </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>23</v>
@@ -7888,62 +7909,62 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>566</v>
-      </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B266" s="1" t="s">
-        <v>568</v>
-      </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="B267" s="1" t="s">
+      <c r="C267" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F267" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="C267" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D267" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="E267" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F267" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7957,10 +7978,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -7977,53 +7998,53 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>577</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="C271" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>575</v>
-      </c>
       <c r="E271" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -8037,13 +8058,13 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -8057,13 +8078,13 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -8077,33 +8098,33 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>586</v>
+        <v>83</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="B275" s="1" t="s">
+      <c r="C275" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F275" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="C275" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="E275" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F275" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -8117,70 +8138,70 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>5</v>
+        <v>591</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F277" s="1" t="s">
         <v>591</v>
-      </c>
-      <c r="B277" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="C277" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="E277" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F277" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>12</v>
+        <v>591</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>12</v>
@@ -8188,19 +8209,19 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>12</v>
@@ -8208,59 +8229,59 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D281" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="C281" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>593</v>
-      </c>
       <c r="E281" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8268,59 +8289,59 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>609</v>
+        <v>23</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>12</v>
@@ -8328,39 +8349,39 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>12</v>
+        <v>616</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B288" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D288" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="C288" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>608</v>
-      </c>
       <c r="E288" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>12</v>
@@ -8368,19 +8389,19 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>12</v>
@@ -8388,39 +8409,39 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>12</v>
@@ -8428,39 +8449,39 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>12</v>
@@ -8468,19 +8489,19 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="F294" s="1" t="s">
         <v>12</v>
@@ -8488,39 +8509,39 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>12</v>
@@ -8528,19 +8549,19 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>23</v>
@@ -8548,19 +8569,19 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>12</v>
@@ -8568,59 +8589,59 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>638</v>
+        <v>615</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>638</v>
+        <v>615</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>18</v>
+        <v>225</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>12</v>
@@ -8628,39 +8649,39 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D303" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="B303" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="C303" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>638</v>
-      </c>
       <c r="E303" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>12</v>
@@ -8668,19 +8689,19 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>12</v>
@@ -8688,19 +8709,19 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>12</v>
@@ -8708,59 +8729,59 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8768,19 +8789,19 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8788,59 +8809,59 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>655</v>
-      </c>
       <c r="E311" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>12</v>
@@ -8848,19 +8869,19 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>12</v>
@@ -8868,19 +8889,19 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>12</v>
@@ -8888,19 +8909,19 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>12</v>
@@ -8908,19 +8929,19 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>12</v>
@@ -8928,19 +8949,19 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>12</v>
@@ -8948,99 +8969,99 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>445</v>
+        <v>12</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D320" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>674</v>
-      </c>
       <c r="E320" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>685</v>
+        <v>460</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>12</v>
@@ -9048,339 +9069,339 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>12</v>
+        <v>692</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D326" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="B326" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="C326" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D326" s="1" t="s">
-        <v>688</v>
-      </c>
       <c r="E326" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D332" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="B332" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="E332" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D337" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="B337" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="C337" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D337" s="1" t="s">
-        <v>712</v>
-      </c>
       <c r="E337" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>724</v>
+        <v>83</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>12</v>
@@ -9388,42 +9409,82 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>84</v>
+        <v>731</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B341" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D341" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="C341" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>723</v>
-      </c>
       <c r="E341" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F341" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F342" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="E343" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F341" s="1" t="s">
-        <v>84</v>
+      <c r="F343" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/BFD05D.xlsx
+++ b/BFD05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="745">
   <si>
     <t/>
   </si>
@@ -319,153 +319,171 @@
     <t>AJINOMOTO BB.MSK 250</t>
   </si>
   <si>
+    <t>20134507</t>
+  </si>
+  <si>
+    <t>TUDUNG BMB NS UDUK27</t>
+  </si>
+  <si>
+    <t>20134777</t>
+  </si>
+  <si>
+    <t>SASA KARI JPG ORI 40</t>
+  </si>
+  <si>
+    <t>20136577</t>
+  </si>
+  <si>
+    <t>TUDUNG BMB PRLDK 50G</t>
+  </si>
+  <si>
+    <t>20136743</t>
+  </si>
+  <si>
+    <t>TDUNG BMB NP.RDNG 27</t>
+  </si>
+  <si>
+    <t>20134778</t>
+  </si>
+  <si>
+    <t>SASA KARI JPG PDS 40</t>
+  </si>
+  <si>
+    <t>20137258</t>
+  </si>
+  <si>
+    <t>RASA/M GULAI AYAM40G</t>
+  </si>
+  <si>
+    <t>20138072</t>
+  </si>
+  <si>
+    <t>RASA/M OPOR AYAM 40G</t>
+  </si>
+  <si>
+    <t>20138843</t>
+  </si>
+  <si>
+    <t>R/MASA SYR LODEH 25G</t>
+  </si>
+  <si>
+    <t>20025563</t>
+  </si>
+  <si>
+    <t>SASA BMB LUMUR AYM26</t>
+  </si>
+  <si>
+    <t>20057290</t>
+  </si>
+  <si>
+    <t>SASA BU AYAM KNG 25G</t>
+  </si>
+  <si>
+    <t>20059859</t>
+  </si>
+  <si>
+    <t>KOBE BMB N/GRG PDS20</t>
+  </si>
+  <si>
+    <t>20136397</t>
+  </si>
+  <si>
+    <t>KB BMB AYM LNGKS 80G</t>
+  </si>
+  <si>
+    <t>10007775</t>
+  </si>
+  <si>
+    <t>A/SAJIKU NASI G.AY20</t>
+  </si>
+  <si>
+    <t>10013821</t>
+  </si>
+  <si>
+    <t>A/SAJIKU NASI G.PD20</t>
+  </si>
+  <si>
+    <t>10013823</t>
+  </si>
+  <si>
+    <t>A/SAJIKU BB.AYM GR24</t>
+  </si>
+  <si>
+    <t>20103449</t>
+  </si>
+  <si>
+    <t>SAJIKU NSI GRG SPL20</t>
+  </si>
+  <si>
+    <t>10035898</t>
+  </si>
+  <si>
+    <t>A/MASAKO AYAM 94GR</t>
+  </si>
+  <si>
+    <t>20038548</t>
+  </si>
+  <si>
+    <t>MASAKO SAPI 230GR</t>
+  </si>
+  <si>
+    <t>20038549</t>
+  </si>
+  <si>
+    <t>A/MASAKO AYAM 230GR</t>
+  </si>
+  <si>
+    <t>20143858</t>
+  </si>
+  <si>
+    <t>AJNMTO SJKU RNDNG60</t>
+  </si>
+  <si>
+    <t>10035899</t>
+  </si>
+  <si>
+    <t>A/MASAKO SAPI 94GR</t>
+  </si>
+  <si>
+    <t>20135316</t>
+  </si>
+  <si>
+    <t>LARISST BMB JMR 40G</t>
+  </si>
+  <si>
+    <t>20143857</t>
+  </si>
+  <si>
+    <t>AJNMTO SJIKU GULAI50</t>
+  </si>
+  <si>
+    <t>20104719</t>
+  </si>
+  <si>
+    <t>TOTOLE KLD JMUR 80G</t>
+  </si>
+  <si>
+    <t>20143860</t>
+  </si>
+  <si>
+    <t>KPOE B/R KLDU JMR 80</t>
+  </si>
+  <si>
+    <t>20098663</t>
+  </si>
+  <si>
+    <t>TOTOLE KLD JMUR 40G</t>
+  </si>
+  <si>
+    <t>10006884</t>
+  </si>
+  <si>
+    <t>ABC MINYAK WIJEN.195</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
-    <t>20134507</t>
-  </si>
-  <si>
-    <t>TUDUNG BMB NS UDUK27</t>
-  </si>
-  <si>
-    <t>20134777</t>
-  </si>
-  <si>
-    <t>SASA KARI JPG ORI 40</t>
-  </si>
-  <si>
-    <t>20136577</t>
-  </si>
-  <si>
-    <t>TUDUNG BMB PRLDK 50G</t>
-  </si>
-  <si>
-    <t>20136743</t>
-  </si>
-  <si>
-    <t>TDUNG BMB NP.RDNG 27</t>
-  </si>
-  <si>
-    <t>20134778</t>
-  </si>
-  <si>
-    <t>SASA KARI JPG PDS 40</t>
-  </si>
-  <si>
-    <t>20137258</t>
-  </si>
-  <si>
-    <t>RASA/M GULAI AYAM40G</t>
-  </si>
-  <si>
-    <t>20138072</t>
-  </si>
-  <si>
-    <t>RASA/M OPOR AYAM 40G</t>
-  </si>
-  <si>
-    <t>20138843</t>
-  </si>
-  <si>
-    <t>R/MASA SYR LODEH 25G</t>
-  </si>
-  <si>
-    <t>20025563</t>
-  </si>
-  <si>
-    <t>SASA BMB LUMUR AYM26</t>
-  </si>
-  <si>
-    <t>20057290</t>
-  </si>
-  <si>
-    <t>SASA BU AYAM KNG 25G</t>
-  </si>
-  <si>
-    <t>20059859</t>
-  </si>
-  <si>
-    <t>KOBE BMB N/GRG PDS20</t>
-  </si>
-  <si>
-    <t>20136397</t>
-  </si>
-  <si>
-    <t>KB BMB AYM LNGKS 80G</t>
-  </si>
-  <si>
-    <t>10007775</t>
-  </si>
-  <si>
-    <t>A/SAJIKU NASI G.AY20</t>
-  </si>
-  <si>
-    <t>10013821</t>
-  </si>
-  <si>
-    <t>A/SAJIKU NASI G.PD20</t>
-  </si>
-  <si>
-    <t>10013823</t>
-  </si>
-  <si>
-    <t>A/SAJIKU BB.AYM GR24</t>
-  </si>
-  <si>
-    <t>20103449</t>
-  </si>
-  <si>
-    <t>SAJIKU NSI GRG SPL20</t>
-  </si>
-  <si>
-    <t>10035898</t>
-  </si>
-  <si>
-    <t>A/MASAKO AYAM 100GR</t>
-  </si>
-  <si>
-    <t>20038548</t>
-  </si>
-  <si>
-    <t>MASAKO SAPI 250GR</t>
-  </si>
-  <si>
-    <t>20038549</t>
-  </si>
-  <si>
-    <t>A/MASAKO AYAM 250GR</t>
-  </si>
-  <si>
-    <t>20098663</t>
-  </si>
-  <si>
-    <t>TOTOLE KLD JMUR 40G</t>
-  </si>
-  <si>
-    <t>10035899</t>
-  </si>
-  <si>
-    <t>A/MASAKO SAPI 100GR</t>
-  </si>
-  <si>
-    <t>20135316</t>
-  </si>
-  <si>
-    <t>LARISST BMB JMR 40G</t>
-  </si>
-  <si>
-    <t>20104719</t>
-  </si>
-  <si>
-    <t>TOTOLE KLD JMUR 80G</t>
-  </si>
-  <si>
-    <t>10006884</t>
-  </si>
-  <si>
-    <t>ABC MINYAK WIJEN.195</t>
-  </si>
-  <si>
     <t>20031771</t>
   </si>
   <si>
@@ -508,13 +526,22 @@
     <t>SAORI SAUS LD HTM133</t>
   </si>
   <si>
+    <t>20142668</t>
+  </si>
+  <si>
+    <t>SAORI SS YAKINIKU133</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>20044599</t>
   </si>
   <si>
     <t>SAORI SAUS TIRAM 270</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t>20038236</t>
@@ -523,7 +550,7 @@
     <t>ABC SAUS TIRAM 135</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>20071507</t>
@@ -532,7 +559,7 @@
     <t>MAGGI SAUS TIRAM 150</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>20117166</t>
@@ -541,7 +568,7 @@
     <t>MAESTRO SS TIRAM 270</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>20015850</t>
@@ -688,9 +715,6 @@
     <t>2 BELIBIS EX/PDS 235</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>20132660</t>
   </si>
   <si>
@@ -2087,9 +2111,6 @@
   </si>
   <si>
     <t>GRANDCO MYK GRG1.8L</t>
-  </si>
-  <si>
-    <t>,(E-3B)</t>
   </si>
   <si>
     <t>10012338</t>
@@ -2617,7 +2638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F343"/>
+  <dimension ref="A1:F347"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3461,7 +3482,7 @@
         <v>34</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>23</v>
@@ -3481,7 +3502,7 @@
         <v>34</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>83</v>
@@ -3501,7 +3522,7 @@
         <v>34</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>12</v>
@@ -3509,10 +3530,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -3529,10 +3550,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -3549,10 +3570,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -3569,10 +3590,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -3589,10 +3610,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -3609,10 +3630,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -3629,10 +3650,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -3649,10 +3670,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -3669,10 +3690,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -3689,10 +3710,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -3709,10 +3730,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -3729,10 +3750,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -3749,10 +3770,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -3769,10 +3790,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -3789,10 +3810,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -3809,10 +3830,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -3829,10 +3850,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -3849,10 +3870,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -3869,10 +3890,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -3889,10 +3910,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -3904,15 +3925,15 @@
         <v>29</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -3929,10 +3950,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -3949,10 +3970,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -3961,27 +3982,27 @@
         <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3989,62 +4010,62 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="E71" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -4058,13 +4079,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4078,10 +4099,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>12</v>
@@ -4098,13 +4119,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4118,13 +4139,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -4138,10 +4159,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>167</v>
+        <v>34</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>12</v>
@@ -4149,122 +4170,122 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>170</v>
+        <v>15</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F81" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F82" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -4278,10 +4299,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>26</v>
+        <v>185</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>23</v>
@@ -4289,139 +4310,139 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>167</v>
+        <v>29</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>170</v>
+        <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -4429,19 +4450,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -4449,59 +4470,59 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -4509,99 +4530,99 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>23</v>
@@ -4609,82 +4630,82 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>173</v>
+        <v>15</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -4698,70 +4719,70 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>234</v>
+        <v>182</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>185</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -4769,19 +4790,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>18</v>
+        <v>236</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -4789,19 +4810,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>23</v>
@@ -4809,19 +4830,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>23</v>
@@ -4838,13 +4859,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4858,13 +4879,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4878,10 +4899,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -4898,13 +4919,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4918,10 +4939,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -4938,13 +4959,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4958,13 +4979,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4978,10 +4999,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>12</v>
@@ -4998,10 +5019,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>23</v>
@@ -5018,13 +5039,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -5038,10 +5059,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>12</v>
@@ -5058,10 +5079,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>12</v>
@@ -5078,13 +5099,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -5098,10 +5119,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>12</v>
@@ -5118,10 +5139,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>12</v>
@@ -5138,10 +5159,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>12</v>
@@ -5158,10 +5179,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>12</v>
@@ -5178,10 +5199,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>12</v>
@@ -5198,13 +5219,13 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -5218,10 +5239,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>12</v>
@@ -5238,10 +5259,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>12</v>
@@ -5258,10 +5279,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>12</v>
@@ -5278,10 +5299,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -5298,13 +5319,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -5318,13 +5339,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>170</v>
+        <v>11</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -5338,13 +5359,13 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -5358,13 +5379,13 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5378,13 +5399,13 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>225</v>
+        <v>156</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -5398,10 +5419,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>41</v>
@@ -5418,13 +5439,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -5438,13 +5459,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>4</v>
+        <v>182</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5458,13 +5479,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>185</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5478,13 +5499,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>236</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -5498,10 +5519,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>23</v>
@@ -5518,10 +5539,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>23</v>
@@ -5538,10 +5559,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>23</v>
@@ -5558,10 +5579,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>23</v>
@@ -5578,10 +5599,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>23</v>
@@ -5598,10 +5619,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>23</v>
@@ -5618,10 +5639,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>23</v>
@@ -5638,10 +5659,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>23</v>
@@ -5658,10 +5679,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>23</v>
@@ -5678,10 +5699,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>23</v>
@@ -5698,10 +5719,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>23</v>
@@ -5718,13 +5739,13 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5738,10 +5759,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>23</v>
@@ -5758,10 +5779,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>23</v>
@@ -5778,10 +5799,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>23</v>
@@ -5798,13 +5819,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5818,10 +5839,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>23</v>
@@ -5838,10 +5859,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>23</v>
@@ -5858,10 +5879,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>23</v>
@@ -5878,13 +5899,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5898,70 +5919,70 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>351</v>
+        <v>23</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>357</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>12</v>
@@ -5969,22 +5990,22 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="C168" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F168" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5998,13 +6019,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -6018,10 +6039,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>12</v>
@@ -6038,13 +6059,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -6058,50 +6079,50 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>368</v>
+        <v>12</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>12</v>
@@ -6109,42 +6130,42 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F176" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F176" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6158,13 +6179,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>351</v>
+        <v>83</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -6178,13 +6199,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6198,13 +6219,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6218,13 +6239,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>5</v>
+        <v>359</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6238,13 +6259,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>12</v>
+        <v>359</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6258,13 +6279,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6278,13 +6299,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6298,30 +6319,30 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>393</v>
+        <v>242</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>393</v>
+        <v>242</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>12</v>
@@ -6329,59 +6350,59 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>393</v>
+        <v>242</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>393</v>
+        <v>242</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>12</v>
@@ -6398,13 +6419,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6418,13 +6439,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>351</v>
+        <v>23</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6438,13 +6459,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6458,13 +6479,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>351</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6478,13 +6499,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6498,30 +6519,30 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>5</v>
+        <v>359</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>416</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -6529,39 +6550,39 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>5</v>
+        <v>359</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -6569,19 +6590,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="E198" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -6598,13 +6619,13 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6618,13 +6639,13 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6638,13 +6659,13 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6658,13 +6679,13 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6678,13 +6699,13 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6698,13 +6719,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6718,30 +6739,30 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>12</v>
@@ -6749,39 +6770,39 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>26</v>
+        <v>176</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6789,22 +6810,22 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B209" s="1" t="s">
+      <c r="C209" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="C209" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>437</v>
-      </c>
       <c r="E209" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -6818,10 +6839,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>12</v>
@@ -6838,30 +6859,30 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>450</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6869,39 +6890,39 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>454</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>167</v>
+        <v>29</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>170</v>
+        <v>11</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>12</v>
@@ -6909,79 +6930,79 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F215" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F215" s="1" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>12</v>
@@ -6989,22 +7010,22 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B219" s="1" t="s">
+      <c r="E219" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F219" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F219" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -7018,13 +7039,13 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -7038,13 +7059,13 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -7058,13 +7079,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7078,10 +7099,10 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>23</v>
@@ -7098,13 +7119,13 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7118,13 +7139,13 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>173</v>
+        <v>15</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -7138,10 +7159,10 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>23</v>
@@ -7158,93 +7179,93 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>4</v>
+        <v>173</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>486</v>
+        <v>23</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>486</v>
+        <v>23</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>486</v>
+        <v>23</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D231" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B231" s="1" t="s">
+      <c r="E231" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F231" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="E231" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F231" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7258,13 +7279,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7278,13 +7299,13 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>83</v>
+        <v>494</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7298,10 +7319,10 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>83</v>
@@ -7318,13 +7339,13 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -7338,13 +7359,13 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>5</v>
+        <v>494</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -7358,13 +7379,13 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7378,13 +7399,13 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7398,10 +7419,10 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>5</v>
@@ -7418,10 +7439,10 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>5</v>
@@ -7438,10 +7459,10 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>5</v>
@@ -7458,10 +7479,10 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>5</v>
@@ -7478,10 +7499,10 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>5</v>
@@ -7498,10 +7519,10 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>5</v>
@@ -7518,10 +7539,10 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>5</v>
@@ -7538,10 +7559,10 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>5</v>
@@ -7558,10 +7579,10 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>5</v>
@@ -7578,10 +7599,10 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>5</v>
@@ -7598,10 +7619,10 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>531</v>
+        <v>493</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>5</v>
@@ -7609,19 +7630,19 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="B250" s="1" t="s">
-        <v>533</v>
-      </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>531</v>
+        <v>493</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>5</v>
@@ -7629,19 +7650,19 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>535</v>
-      </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>531</v>
+        <v>493</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>5</v>
@@ -7649,42 +7670,42 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>537</v>
-      </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>531</v>
+        <v>493</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="B253" s="1" t="s">
+      <c r="C253" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D253" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="C253" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D253" s="1" t="s">
-        <v>531</v>
-      </c>
       <c r="E253" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7698,10 +7719,10 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>5</v>
@@ -7709,19 +7730,19 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>5</v>
@@ -7729,62 +7750,62 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>546</v>
-      </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="C257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B258" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B258" s="1" t="s">
+      <c r="C258" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D258" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="C258" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D258" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="E258" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7798,10 +7819,10 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>5</v>
@@ -7818,13 +7839,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7838,50 +7859,50 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>559</v>
-      </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>5</v>
@@ -7889,42 +7910,42 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>563</v>
-      </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B265" s="1" t="s">
+      <c r="C265" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D265" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="C265" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D265" s="1" t="s">
-        <v>557</v>
-      </c>
       <c r="E265" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7938,13 +7959,13 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7958,30 +7979,30 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>570</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>572</v>
-      </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -7989,302 +8010,302 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="B269" s="1" t="s">
-        <v>574</v>
-      </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>167</v>
+        <v>29</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>576</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>170</v>
+        <v>11</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F271" s="1" t="s">
         <v>578</v>
-      </c>
-      <c r="C271" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="E271" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F271" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>581</v>
-      </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="B273" s="1" t="s">
-        <v>583</v>
-      </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="B274" s="1" t="s">
-        <v>585</v>
-      </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>26</v>
+        <v>176</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="B275" s="1" t="s">
+      <c r="C275" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D275" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="C275" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>579</v>
-      </c>
       <c r="E275" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>588</v>
+        <v>83</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B276" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="B276" s="1" t="s">
-        <v>590</v>
-      </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>591</v>
+        <v>83</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>591</v>
+        <v>83</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>591</v>
+        <v>83</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F279" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="B279" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="C279" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="E279" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F279" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F280" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="B280" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="C280" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="E280" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F280" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>12</v>
+        <v>599</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>604</v>
-      </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>12</v>
+        <v>599</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="B283" s="1" t="s">
+      <c r="C283" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D283" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="C283" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="E283" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -8298,13 +8319,13 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -8318,13 +8339,13 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8338,10 +8359,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>12</v>
@@ -8358,70 +8379,70 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>616</v>
+        <v>23</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>12</v>
@@ -8429,22 +8450,22 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D291" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B291" s="1" t="s">
+      <c r="E291" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F291" s="1" t="s">
         <v>624</v>
-      </c>
-      <c r="C291" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D291" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="E291" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F291" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8458,13 +8479,13 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8478,10 +8499,10 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>12</v>
@@ -8498,10 +8519,10 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F294" s="1" t="s">
         <v>12</v>
@@ -8518,10 +8539,10 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>12</v>
@@ -8538,13 +8559,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8558,13 +8579,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8578,10 +8599,10 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>173</v>
+        <v>15</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>12</v>
@@ -8598,13 +8619,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8618,10 +8639,10 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>12</v>
@@ -8638,70 +8659,70 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>645</v>
+        <v>623</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>647</v>
-      </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>645</v>
+        <v>623</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>18</v>
+        <v>179</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B303" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B303" s="1" t="s">
-        <v>649</v>
-      </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>645</v>
+        <v>623</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>8</v>
+        <v>182</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B304" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B304" s="1" t="s">
-        <v>651</v>
-      </c>
       <c r="C304" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>645</v>
+        <v>623</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>26</v>
+        <v>185</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>12</v>
@@ -8709,19 +8730,19 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="B305" s="1" t="s">
+      <c r="C305" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D305" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="C305" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>645</v>
-      </c>
       <c r="E305" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>12</v>
@@ -8738,13 +8759,13 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -8758,10 +8779,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>12</v>
@@ -8778,13 +8799,13 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -8798,93 +8819,93 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="B310" s="1" t="s">
-        <v>664</v>
-      </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="B311" s="1" t="s">
-        <v>666</v>
-      </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>668</v>
-      </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B313" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="B313" s="1" t="s">
+      <c r="C313" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D313" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="C313" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>662</v>
-      </c>
       <c r="E313" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -8898,13 +8919,13 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -8918,13 +8939,13 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -8938,10 +8959,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>12</v>
@@ -8958,10 +8979,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>12</v>
@@ -8978,10 +8999,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>12</v>
@@ -8989,19 +9010,19 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>683</v>
-      </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>12</v>
@@ -9009,59 +9030,59 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>685</v>
-      </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="B321" s="1" t="s">
-        <v>687</v>
-      </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>460</v>
+        <v>12</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="B322" s="1" t="s">
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="C322" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>681</v>
-      </c>
       <c r="E322" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>12</v>
@@ -9078,90 +9099,90 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>692</v>
+        <v>12</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="B324" s="1" t="s">
-        <v>694</v>
-      </c>
       <c r="C324" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>12</v>
+        <v>468</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>23</v>
@@ -9169,39 +9190,39 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>695</v>
-      </c>
       <c r="E328" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>12</v>
@@ -9209,19 +9230,19 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B330" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="B330" s="1" t="s">
-        <v>707</v>
-      </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>83</v>
@@ -9229,39 +9250,39 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>83</v>
@@ -9269,39 +9290,39 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D334" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="B334" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="C334" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D334" s="1" t="s">
-        <v>708</v>
-      </c>
       <c r="E334" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>83</v>
@@ -9309,19 +9330,19 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B335" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="B335" s="1" t="s">
-        <v>718</v>
-      </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>83</v>
@@ -9329,19 +9350,19 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>83</v>
@@ -9349,19 +9370,19 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>83</v>
@@ -9369,19 +9390,19 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>83</v>
@@ -9389,79 +9410,79 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D339" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="B339" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="C339" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>719</v>
-      </c>
       <c r="E339" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B340" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="B340" s="1" t="s">
-        <v>729</v>
-      </c>
       <c r="C340" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>731</v>
+        <v>83</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>83</v>
@@ -9469,21 +9490,101 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F343" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A344" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B344" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="B343" s="1" t="s">
+      <c r="C344" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D344" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="C343" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D343" s="1" t="s">
-        <v>730</v>
-      </c>
-      <c r="E343" s="1" t="s">
+      <c r="E344" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F344" s="1" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A345" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="E345" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F345" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A346" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F346" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A347" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="E347" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F343" s="1" t="s">
+      <c r="F347" s="1" t="s">
         <v>83</v>
       </c>
     </row>
